--- a/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C780"/>
+  <dimension ref="A1:C856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>2.2e-05</v>
+        <v>0.000452</v>
       </c>
       <c r="C287" t="n">
         <v>1</v>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.00011</v>
+        <v>0.000461</v>
       </c>
       <c r="C288" t="n">
-        <v>0.995918</v>
+        <v>0.996491</v>
       </c>
     </row>
     <row r="289">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.000973</v>
+        <v>0.001574</v>
       </c>
       <c r="C289" t="n">
-        <v>0.991837</v>
+        <v>0.992982</v>
       </c>
     </row>
     <row r="290">
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.001354</v>
+        <v>0.001754</v>
       </c>
       <c r="C290" t="n">
-        <v>0.987755</v>
+        <v>0.989474</v>
       </c>
     </row>
     <row r="291">
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.001412</v>
+        <v>0.00229</v>
       </c>
       <c r="C291" t="n">
-        <v>0.983673</v>
+        <v>0.985965</v>
       </c>
     </row>
     <row r="292">
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.001425</v>
+        <v>0.002344</v>
       </c>
       <c r="C292" t="n">
-        <v>0.979592</v>
+        <v>0.982456</v>
       </c>
     </row>
     <row r="293">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.001471</v>
+        <v>0.002605</v>
       </c>
       <c r="C293" t="n">
-        <v>0.97551</v>
+        <v>0.978947</v>
       </c>
     </row>
     <row r="294">
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.001554</v>
+        <v>0.003438</v>
       </c>
       <c r="C294" t="n">
-        <v>0.971429</v>
+        <v>0.9754389999999999</v>
       </c>
     </row>
     <row r="295">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.001635</v>
+        <v>0.003515</v>
       </c>
       <c r="C295" t="n">
-        <v>0.967347</v>
+        <v>0.97193</v>
       </c>
     </row>
     <row r="296">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.002083</v>
+        <v>0.003736</v>
       </c>
       <c r="C296" t="n">
-        <v>0.963265</v>
+        <v>0.968421</v>
       </c>
     </row>
     <row r="297">
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.002348</v>
+        <v>0.003777</v>
       </c>
       <c r="C297" t="n">
-        <v>0.959184</v>
+        <v>0.964912</v>
       </c>
     </row>
     <row r="298">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.002366</v>
+        <v>0.003927</v>
       </c>
       <c r="C298" t="n">
-        <v>0.955102</v>
+        <v>0.961404</v>
       </c>
     </row>
     <row r="299">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.002448</v>
+        <v>0.003982</v>
       </c>
       <c r="C299" t="n">
-        <v>0.95102</v>
+        <v>0.9578950000000001</v>
       </c>
     </row>
     <row r="300">
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.00246</v>
+        <v>0.004287</v>
       </c>
       <c r="C300" t="n">
-        <v>0.946939</v>
+        <v>0.954386</v>
       </c>
     </row>
     <row r="301">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.002518</v>
+        <v>0.004487</v>
       </c>
       <c r="C301" t="n">
-        <v>0.9428569999999999</v>
+        <v>0.950877</v>
       </c>
     </row>
     <row r="302">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.0027</v>
+        <v>0.004577</v>
       </c>
       <c r="C302" t="n">
-        <v>0.9387760000000001</v>
+        <v>0.947368</v>
       </c>
     </row>
     <row r="303">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.003288</v>
+        <v>0.004769</v>
       </c>
       <c r="C303" t="n">
-        <v>0.934694</v>
+        <v>0.94386</v>
       </c>
     </row>
     <row r="304">
@@ -4366,10 +4366,10 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>0.003602</v>
+        <v>0.004844</v>
       </c>
       <c r="C304" t="n">
-        <v>0.930612</v>
+        <v>0.940351</v>
       </c>
     </row>
     <row r="305">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.00361</v>
+        <v>0.004879</v>
       </c>
       <c r="C305" t="n">
-        <v>0.926531</v>
+        <v>0.936842</v>
       </c>
     </row>
     <row r="306">
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.003871</v>
+        <v>0.004948</v>
       </c>
       <c r="C306" t="n">
-        <v>0.922449</v>
+        <v>0.933333</v>
       </c>
     </row>
     <row r="307">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>0.004201</v>
+        <v>0.005247</v>
       </c>
       <c r="C307" t="n">
-        <v>0.918367</v>
+        <v>0.929825</v>
       </c>
     </row>
     <row r="308">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>0.004348</v>
+        <v>0.005301</v>
       </c>
       <c r="C308" t="n">
-        <v>0.914286</v>
+        <v>0.926316</v>
       </c>
     </row>
     <row r="309">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.004562</v>
+        <v>0.005524</v>
       </c>
       <c r="C309" t="n">
-        <v>0.910204</v>
+        <v>0.922807</v>
       </c>
     </row>
     <row r="310">
@@ -4444,10 +4444,10 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.004655</v>
+        <v>0.007061</v>
       </c>
       <c r="C310" t="n">
-        <v>0.906122</v>
+        <v>0.9192979999999999</v>
       </c>
     </row>
     <row r="311">
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>0.004861</v>
+        <v>0.007527</v>
       </c>
       <c r="C311" t="n">
-        <v>0.902041</v>
+        <v>0.915789</v>
       </c>
     </row>
     <row r="312">
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.004872</v>
+        <v>0.007687</v>
       </c>
       <c r="C312" t="n">
-        <v>0.897959</v>
+        <v>0.912281</v>
       </c>
     </row>
     <row r="313">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>0.005185</v>
+        <v>0.007752</v>
       </c>
       <c r="C313" t="n">
-        <v>0.893878</v>
+        <v>0.908772</v>
       </c>
     </row>
     <row r="314">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>0.005419</v>
+        <v>0.008522999999999999</v>
       </c>
       <c r="C314" t="n">
-        <v>0.889796</v>
+        <v>0.905263</v>
       </c>
     </row>
     <row r="315">
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.005601</v>
+        <v>0.008739</v>
       </c>
       <c r="C315" t="n">
-        <v>0.885714</v>
+        <v>0.9017539999999999</v>
       </c>
     </row>
     <row r="316">
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.006023</v>
+        <v>0.008802000000000001</v>
       </c>
       <c r="C316" t="n">
-        <v>0.881633</v>
+        <v>0.898246</v>
       </c>
     </row>
     <row r="317">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.006137</v>
+        <v>0.008887000000000001</v>
       </c>
       <c r="C317" t="n">
-        <v>0.877551</v>
+        <v>0.894737</v>
       </c>
     </row>
     <row r="318">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.006169</v>
+        <v>0.008964</v>
       </c>
       <c r="C318" t="n">
-        <v>0.8734690000000001</v>
+        <v>0.891228</v>
       </c>
     </row>
     <row r="319">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.006392</v>
+        <v>0.009266999999999999</v>
       </c>
       <c r="C319" t="n">
-        <v>0.869388</v>
+        <v>0.887719</v>
       </c>
     </row>
     <row r="320">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.006438</v>
+        <v>0.009604</v>
       </c>
       <c r="C320" t="n">
-        <v>0.865306</v>
+        <v>0.884211</v>
       </c>
     </row>
     <row r="321">
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.006698</v>
+        <v>0.009705999999999999</v>
       </c>
       <c r="C321" t="n">
-        <v>0.861224</v>
+        <v>0.880702</v>
       </c>
     </row>
     <row r="322">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.00689</v>
+        <v>0.009861</v>
       </c>
       <c r="C322" t="n">
-        <v>0.857143</v>
+        <v>0.877193</v>
       </c>
     </row>
     <row r="323">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.006904</v>
+        <v>0.009946999999999999</v>
       </c>
       <c r="C323" t="n">
-        <v>0.853061</v>
+        <v>0.873684</v>
       </c>
     </row>
     <row r="324">
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.007396</v>
+        <v>0.009959000000000001</v>
       </c>
       <c r="C324" t="n">
-        <v>0.84898</v>
+        <v>0.870175</v>
       </c>
     </row>
     <row r="325">
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.007495</v>
+        <v>0.010126</v>
       </c>
       <c r="C325" t="n">
-        <v>0.844898</v>
+        <v>0.866667</v>
       </c>
     </row>
     <row r="326">
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.007496</v>
+        <v>0.010293</v>
       </c>
       <c r="C326" t="n">
-        <v>0.840816</v>
+        <v>0.863158</v>
       </c>
     </row>
     <row r="327">
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.007592</v>
+        <v>0.011219</v>
       </c>
       <c r="C327" t="n">
-        <v>0.836735</v>
+        <v>0.859649</v>
       </c>
     </row>
     <row r="328">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.007698</v>
+        <v>0.011329</v>
       </c>
       <c r="C328" t="n">
-        <v>0.832653</v>
+        <v>0.85614</v>
       </c>
     </row>
     <row r="329">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.00775</v>
+        <v>0.012007</v>
       </c>
       <c r="C329" t="n">
-        <v>0.8285709999999999</v>
+        <v>0.8526319999999999</v>
       </c>
     </row>
     <row r="330">
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.008033999999999999</v>
+        <v>0.012232</v>
       </c>
       <c r="C330" t="n">
-        <v>0.8244899999999999</v>
+        <v>0.849123</v>
       </c>
     </row>
     <row r="331">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.008193000000000001</v>
+        <v>0.012299</v>
       </c>
       <c r="C331" t="n">
-        <v>0.820408</v>
+        <v>0.845614</v>
       </c>
     </row>
     <row r="332">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.008435</v>
+        <v>0.012304</v>
       </c>
       <c r="C332" t="n">
-        <v>0.816327</v>
+        <v>0.842105</v>
       </c>
     </row>
     <row r="333">
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.008454</v>
+        <v>0.013077</v>
       </c>
       <c r="C333" t="n">
-        <v>0.812245</v>
+        <v>0.838596</v>
       </c>
     </row>
     <row r="334">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.008539</v>
+        <v>0.013501</v>
       </c>
       <c r="C334" t="n">
-        <v>0.808163</v>
+        <v>0.8350880000000001</v>
       </c>
     </row>
     <row r="335">
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.008578000000000001</v>
+        <v>0.013505</v>
       </c>
       <c r="C335" t="n">
-        <v>0.804082</v>
+        <v>0.831579</v>
       </c>
     </row>
     <row r="336">
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.008682</v>
+        <v>0.014035</v>
       </c>
       <c r="C336" t="n">
-        <v>0.8</v>
+        <v>0.82807</v>
       </c>
     </row>
     <row r="337">
@@ -4795,10 +4795,10 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.008976</v>
+        <v>0.014144</v>
       </c>
       <c r="C337" t="n">
-        <v>0.795918</v>
+        <v>0.824561</v>
       </c>
     </row>
     <row r="338">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.009186</v>
+        <v>0.014565</v>
       </c>
       <c r="C338" t="n">
-        <v>0.791837</v>
+        <v>0.821053</v>
       </c>
     </row>
     <row r="339">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.009394</v>
+        <v>0.01468</v>
       </c>
       <c r="C339" t="n">
-        <v>0.787755</v>
+        <v>0.817544</v>
       </c>
     </row>
     <row r="340">
@@ -4834,10 +4834,10 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.009468000000000001</v>
+        <v>0.014743</v>
       </c>
       <c r="C340" t="n">
-        <v>0.783673</v>
+        <v>0.814035</v>
       </c>
     </row>
     <row r="341">
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.009821</v>
+        <v>0.015002</v>
       </c>
       <c r="C341" t="n">
-        <v>0.779592</v>
+        <v>0.810526</v>
       </c>
     </row>
     <row r="342">
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.009874000000000001</v>
+        <v>0.0155</v>
       </c>
       <c r="C342" t="n">
-        <v>0.77551</v>
+        <v>0.807018</v>
       </c>
     </row>
     <row r="343">
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.009904</v>
+        <v>0.015672</v>
       </c>
       <c r="C343" t="n">
-        <v>0.771429</v>
+        <v>0.803509</v>
       </c>
     </row>
     <row r="344">
@@ -4886,10 +4886,10 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.010009</v>
+        <v>0.015774</v>
       </c>
       <c r="C344" t="n">
-        <v>0.767347</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="345">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.010105</v>
+        <v>0.016348</v>
       </c>
       <c r="C345" t="n">
-        <v>0.763265</v>
+        <v>0.7964909999999999</v>
       </c>
     </row>
     <row r="346">
@@ -4912,10 +4912,10 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.01021</v>
+        <v>0.01652</v>
       </c>
       <c r="C346" t="n">
-        <v>0.759184</v>
+        <v>0.792982</v>
       </c>
     </row>
     <row r="347">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.010347</v>
+        <v>0.016694</v>
       </c>
       <c r="C347" t="n">
-        <v>0.7551020000000001</v>
+        <v>0.789474</v>
       </c>
     </row>
     <row r="348">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.010502</v>
+        <v>0.017046</v>
       </c>
       <c r="C348" t="n">
-        <v>0.75102</v>
+        <v>0.785965</v>
       </c>
     </row>
     <row r="349">
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.010687</v>
+        <v>0.017107</v>
       </c>
       <c r="C349" t="n">
-        <v>0.746939</v>
+        <v>0.782456</v>
       </c>
     </row>
     <row r="350">
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.010703</v>
+        <v>0.017743</v>
       </c>
       <c r="C350" t="n">
-        <v>0.742857</v>
+        <v>0.7789469999999999</v>
       </c>
     </row>
     <row r="351">
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.011095</v>
+        <v>0.01794</v>
       </c>
       <c r="C351" t="n">
-        <v>0.738776</v>
+        <v>0.775439</v>
       </c>
     </row>
     <row r="352">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.011177</v>
+        <v>0.018148</v>
       </c>
       <c r="C352" t="n">
-        <v>0.734694</v>
+        <v>0.77193</v>
       </c>
     </row>
     <row r="353">
@@ -5003,10 +5003,10 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>0.011186</v>
+        <v>0.018696</v>
       </c>
       <c r="C353" t="n">
-        <v>0.730612</v>
+        <v>0.768421</v>
       </c>
     </row>
     <row r="354">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.01167</v>
+        <v>0.019133</v>
       </c>
       <c r="C354" t="n">
-        <v>0.726531</v>
+        <v>0.764912</v>
       </c>
     </row>
     <row r="355">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.01171</v>
+        <v>0.019373</v>
       </c>
       <c r="C355" t="n">
-        <v>0.722449</v>
+        <v>0.761404</v>
       </c>
     </row>
     <row r="356">
@@ -5042,10 +5042,10 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.011723</v>
+        <v>0.019565</v>
       </c>
       <c r="C356" t="n">
-        <v>0.718367</v>
+        <v>0.757895</v>
       </c>
     </row>
     <row r="357">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.011736</v>
+        <v>0.019806</v>
       </c>
       <c r="C357" t="n">
-        <v>0.714286</v>
+        <v>0.754386</v>
       </c>
     </row>
     <row r="358">
@@ -5068,10 +5068,10 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.011939</v>
+        <v>0.020446</v>
       </c>
       <c r="C358" t="n">
-        <v>0.7102039999999999</v>
+        <v>0.750877</v>
       </c>
     </row>
     <row r="359">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.012376</v>
+        <v>0.020682</v>
       </c>
       <c r="C359" t="n">
-        <v>0.706122</v>
+        <v>0.747368</v>
       </c>
     </row>
     <row r="360">
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.013163</v>
+        <v>0.021539</v>
       </c>
       <c r="C360" t="n">
-        <v>0.702041</v>
+        <v>0.74386</v>
       </c>
     </row>
     <row r="361">
@@ -5107,10 +5107,10 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.013556</v>
+        <v>0.022018</v>
       </c>
       <c r="C361" t="n">
-        <v>0.697959</v>
+        <v>0.740351</v>
       </c>
     </row>
     <row r="362">
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.013596</v>
+        <v>0.022099</v>
       </c>
       <c r="C362" t="n">
-        <v>0.693878</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="363">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.013899</v>
+        <v>0.022296</v>
       </c>
       <c r="C363" t="n">
-        <v>0.689796</v>
+        <v>0.733333</v>
       </c>
     </row>
     <row r="364">
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.01432</v>
+        <v>0.022435</v>
       </c>
       <c r="C364" t="n">
-        <v>0.685714</v>
+        <v>0.7298249999999999</v>
       </c>
     </row>
     <row r="365">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.014402</v>
+        <v>0.022533</v>
       </c>
       <c r="C365" t="n">
-        <v>0.681633</v>
+        <v>0.726316</v>
       </c>
     </row>
     <row r="366">
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.014474</v>
+        <v>0.022693</v>
       </c>
       <c r="C366" t="n">
-        <v>0.677551</v>
+        <v>0.722807</v>
       </c>
     </row>
     <row r="367">
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.01451</v>
+        <v>0.023044</v>
       </c>
       <c r="C367" t="n">
-        <v>0.673469</v>
+        <v>0.719298</v>
       </c>
     </row>
     <row r="368">
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.014902</v>
+        <v>0.024604</v>
       </c>
       <c r="C368" t="n">
-        <v>0.669388</v>
+        <v>0.715789</v>
       </c>
     </row>
     <row r="369">
@@ -5211,10 +5211,10 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.01505</v>
+        <v>0.024963</v>
       </c>
       <c r="C369" t="n">
-        <v>0.665306</v>
+        <v>0.7122810000000001</v>
       </c>
     </row>
     <row r="370">
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.015424</v>
+        <v>0.025119</v>
       </c>
       <c r="C370" t="n">
-        <v>0.661224</v>
+        <v>0.708772</v>
       </c>
     </row>
     <row r="371">
@@ -5237,10 +5237,10 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.015471</v>
+        <v>0.025607</v>
       </c>
       <c r="C371" t="n">
-        <v>0.657143</v>
+        <v>0.705263</v>
       </c>
     </row>
     <row r="372">
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.016198</v>
+        <v>0.025761</v>
       </c>
       <c r="C372" t="n">
-        <v>0.653061</v>
+        <v>0.701754</v>
       </c>
     </row>
     <row r="373">
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.016384</v>
+        <v>0.025857</v>
       </c>
       <c r="C373" t="n">
-        <v>0.64898</v>
+        <v>0.698246</v>
       </c>
     </row>
     <row r="374">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.016469</v>
+        <v>0.025901</v>
       </c>
       <c r="C374" t="n">
-        <v>0.644898</v>
+        <v>0.694737</v>
       </c>
     </row>
     <row r="375">
@@ -5289,10 +5289,10 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.016476</v>
+        <v>0.026283</v>
       </c>
       <c r="C375" t="n">
-        <v>0.6408160000000001</v>
+        <v>0.691228</v>
       </c>
     </row>
     <row r="376">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.016746</v>
+        <v>0.027242</v>
       </c>
       <c r="C376" t="n">
-        <v>0.6367350000000001</v>
+        <v>0.687719</v>
       </c>
     </row>
     <row r="377">
@@ -5315,10 +5315,10 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.0169</v>
+        <v>0.027324</v>
       </c>
       <c r="C377" t="n">
-        <v>0.632653</v>
+        <v>0.684211</v>
       </c>
     </row>
     <row r="378">
@@ -5328,10 +5328,10 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.017083</v>
+        <v>0.027749</v>
       </c>
       <c r="C378" t="n">
-        <v>0.628571</v>
+        <v>0.680702</v>
       </c>
     </row>
     <row r="379">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.017158</v>
+        <v>0.027976</v>
       </c>
       <c r="C379" t="n">
-        <v>0.62449</v>
+        <v>0.677193</v>
       </c>
     </row>
     <row r="380">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.01729</v>
+        <v>0.028675</v>
       </c>
       <c r="C380" t="n">
-        <v>0.620408</v>
+        <v>0.6736839999999999</v>
       </c>
     </row>
     <row r="381">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.017325</v>
+        <v>0.028688</v>
       </c>
       <c r="C381" t="n">
-        <v>0.616327</v>
+        <v>0.670175</v>
       </c>
     </row>
     <row r="382">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.017425</v>
+        <v>0.028841</v>
       </c>
       <c r="C382" t="n">
-        <v>0.612245</v>
+        <v>0.666667</v>
       </c>
     </row>
     <row r="383">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.017523</v>
+        <v>0.028896</v>
       </c>
       <c r="C383" t="n">
-        <v>0.608163</v>
+        <v>0.663158</v>
       </c>
     </row>
     <row r="384">
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.017913</v>
+        <v>0.029059</v>
       </c>
       <c r="C384" t="n">
-        <v>0.604082</v>
+        <v>0.659649</v>
       </c>
     </row>
     <row r="385">
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.017969</v>
+        <v>0.029677</v>
       </c>
       <c r="C385" t="n">
-        <v>0.6</v>
+        <v>0.6561399999999999</v>
       </c>
     </row>
     <row r="386">
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.018248</v>
+        <v>0.029725</v>
       </c>
       <c r="C386" t="n">
-        <v>0.5959179999999999</v>
+        <v>0.652632</v>
       </c>
     </row>
     <row r="387">
@@ -5445,10 +5445,10 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.018405</v>
+        <v>0.030268</v>
       </c>
       <c r="C387" t="n">
-        <v>0.5918369999999999</v>
+        <v>0.649123</v>
       </c>
     </row>
     <row r="388">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>0.018882</v>
+        <v>0.030607</v>
       </c>
       <c r="C388" t="n">
-        <v>0.587755</v>
+        <v>0.645614</v>
       </c>
     </row>
     <row r="389">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.019363</v>
+        <v>0.03104</v>
       </c>
       <c r="C389" t="n">
-        <v>0.583673</v>
+        <v>0.642105</v>
       </c>
     </row>
     <row r="390">
@@ -5484,10 +5484,10 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.019403</v>
+        <v>0.031389</v>
       </c>
       <c r="C390" t="n">
-        <v>0.579592</v>
+        <v>0.6385960000000001</v>
       </c>
     </row>
     <row r="391">
@@ -5497,10 +5497,10 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.019859</v>
+        <v>0.031453</v>
       </c>
       <c r="C391" t="n">
-        <v>0.57551</v>
+        <v>0.635088</v>
       </c>
     </row>
     <row r="392">
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.019903</v>
+        <v>0.032231</v>
       </c>
       <c r="C392" t="n">
-        <v>0.571429</v>
+        <v>0.631579</v>
       </c>
     </row>
     <row r="393">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.020173</v>
+        <v>0.03226</v>
       </c>
       <c r="C393" t="n">
-        <v>0.567347</v>
+        <v>0.62807</v>
       </c>
     </row>
     <row r="394">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>0.020338</v>
+        <v>0.032269</v>
       </c>
       <c r="C394" t="n">
-        <v>0.563265</v>
+        <v>0.624561</v>
       </c>
     </row>
     <row r="395">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.020536</v>
+        <v>0.03275</v>
       </c>
       <c r="C395" t="n">
-        <v>0.559184</v>
+        <v>0.621053</v>
       </c>
     </row>
     <row r="396">
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.020582</v>
+        <v>0.033198</v>
       </c>
       <c r="C396" t="n">
-        <v>0.555102</v>
+        <v>0.617544</v>
       </c>
     </row>
     <row r="397">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.020823</v>
+        <v>0.033267</v>
       </c>
       <c r="C397" t="n">
-        <v>0.55102</v>
+        <v>0.614035</v>
       </c>
     </row>
     <row r="398">
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>0.020882</v>
+        <v>0.033661</v>
       </c>
       <c r="C398" t="n">
-        <v>0.546939</v>
+        <v>0.610526</v>
       </c>
     </row>
     <row r="399">
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.021148</v>
+        <v>0.033966</v>
       </c>
       <c r="C399" t="n">
-        <v>0.542857</v>
+        <v>0.6070179999999999</v>
       </c>
     </row>
     <row r="400">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>0.021414</v>
+        <v>0.034033</v>
       </c>
       <c r="C400" t="n">
-        <v>0.538776</v>
+        <v>0.603509</v>
       </c>
     </row>
     <row r="401">
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.021777</v>
+        <v>0.034366</v>
       </c>
       <c r="C401" t="n">
-        <v>0.534694</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="402">
@@ -5640,10 +5640,10 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.021828</v>
+        <v>0.034545</v>
       </c>
       <c r="C402" t="n">
-        <v>0.530612</v>
+        <v>0.596491</v>
       </c>
     </row>
     <row r="403">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>0.02187</v>
+        <v>0.035126</v>
       </c>
       <c r="C403" t="n">
-        <v>0.526531</v>
+        <v>0.592982</v>
       </c>
     </row>
     <row r="404">
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>0.022573</v>
+        <v>0.035887</v>
       </c>
       <c r="C404" t="n">
-        <v>0.5224490000000001</v>
+        <v>0.5894740000000001</v>
       </c>
     </row>
     <row r="405">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.023488</v>
+        <v>0.036121</v>
       </c>
       <c r="C405" t="n">
-        <v>0.518367</v>
+        <v>0.585965</v>
       </c>
     </row>
     <row r="406">
@@ -5692,10 +5692,10 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.023758</v>
+        <v>0.036244</v>
       </c>
       <c r="C406" t="n">
-        <v>0.514286</v>
+        <v>0.582456</v>
       </c>
     </row>
     <row r="407">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.02382</v>
+        <v>0.036398</v>
       </c>
       <c r="C407" t="n">
-        <v>0.510204</v>
+        <v>0.578947</v>
       </c>
     </row>
     <row r="408">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.023993</v>
+        <v>0.036643</v>
       </c>
       <c r="C408" t="n">
-        <v>0.506122</v>
+        <v>0.575439</v>
       </c>
     </row>
     <row r="409">
@@ -5731,10 +5731,10 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.024297</v>
+        <v>0.037064</v>
       </c>
       <c r="C409" t="n">
-        <v>0.502041</v>
+        <v>0.57193</v>
       </c>
     </row>
     <row r="410">
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.024584</v>
+        <v>0.037339</v>
       </c>
       <c r="C410" t="n">
-        <v>0.497959</v>
+        <v>0.568421</v>
       </c>
     </row>
     <row r="411">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.025067</v>
+        <v>0.03744</v>
       </c>
       <c r="C411" t="n">
-        <v>0.493878</v>
+        <v>0.564912</v>
       </c>
     </row>
     <row r="412">
@@ -5770,10 +5770,10 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.025282</v>
+        <v>0.037479</v>
       </c>
       <c r="C412" t="n">
-        <v>0.489796</v>
+        <v>0.561404</v>
       </c>
     </row>
     <row r="413">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>0.025669</v>
+        <v>0.037994</v>
       </c>
       <c r="C413" t="n">
-        <v>0.485714</v>
+        <v>0.557895</v>
       </c>
     </row>
     <row r="414">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.026051</v>
+        <v>0.038082</v>
       </c>
       <c r="C414" t="n">
-        <v>0.481633</v>
+        <v>0.554386</v>
       </c>
     </row>
     <row r="415">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.026054</v>
+        <v>0.038506</v>
       </c>
       <c r="C415" t="n">
-        <v>0.477551</v>
+        <v>0.550877</v>
       </c>
     </row>
     <row r="416">
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.026435</v>
+        <v>0.038556</v>
       </c>
       <c r="C416" t="n">
-        <v>0.473469</v>
+        <v>0.547368</v>
       </c>
     </row>
     <row r="417">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.026701</v>
+        <v>0.038648</v>
       </c>
       <c r="C417" t="n">
-        <v>0.469388</v>
+        <v>0.54386</v>
       </c>
     </row>
     <row r="418">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.026748</v>
+        <v>0.03868</v>
       </c>
       <c r="C418" t="n">
-        <v>0.465306</v>
+        <v>0.540351</v>
       </c>
     </row>
     <row r="419">
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.026885</v>
+        <v>0.038692</v>
       </c>
       <c r="C419" t="n">
-        <v>0.461224</v>
+        <v>0.536842</v>
       </c>
     </row>
     <row r="420">
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.026943</v>
+        <v>0.038935</v>
       </c>
       <c r="C420" t="n">
-        <v>0.457143</v>
+        <v>0.5333329999999999</v>
       </c>
     </row>
     <row r="421">
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.027245</v>
+        <v>0.038951</v>
       </c>
       <c r="C421" t="n">
-        <v>0.453061</v>
+        <v>0.529825</v>
       </c>
     </row>
     <row r="422">
@@ -5900,10 +5900,10 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>0.027987</v>
+        <v>0.040034</v>
       </c>
       <c r="C422" t="n">
-        <v>0.44898</v>
+        <v>0.526316</v>
       </c>
     </row>
     <row r="423">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.028182</v>
+        <v>0.040038</v>
       </c>
       <c r="C423" t="n">
-        <v>0.444898</v>
+        <v>0.522807</v>
       </c>
     </row>
     <row r="424">
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.028269</v>
+        <v>0.040736</v>
       </c>
       <c r="C424" t="n">
-        <v>0.440816</v>
+        <v>0.519298</v>
       </c>
     </row>
     <row r="425">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.028736</v>
+        <v>0.040938</v>
       </c>
       <c r="C425" t="n">
-        <v>0.436735</v>
+        <v>0.5157890000000001</v>
       </c>
     </row>
     <row r="426">
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.028956</v>
+        <v>0.041031</v>
       </c>
       <c r="C426" t="n">
-        <v>0.432653</v>
+        <v>0.512281</v>
       </c>
     </row>
     <row r="427">
@@ -5965,10 +5965,10 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.029126</v>
+        <v>0.041347</v>
       </c>
       <c r="C427" t="n">
-        <v>0.428571</v>
+        <v>0.508772</v>
       </c>
     </row>
     <row r="428">
@@ -5978,10 +5978,10 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.029377</v>
+        <v>0.041894</v>
       </c>
       <c r="C428" t="n">
-        <v>0.42449</v>
+        <v>0.505263</v>
       </c>
     </row>
     <row r="429">
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.029599</v>
+        <v>0.042205</v>
       </c>
       <c r="C429" t="n">
-        <v>0.420408</v>
+        <v>0.501754</v>
       </c>
     </row>
     <row r="430">
@@ -6004,10 +6004,10 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.029869</v>
+        <v>0.042692</v>
       </c>
       <c r="C430" t="n">
-        <v>0.416327</v>
+        <v>0.498246</v>
       </c>
     </row>
     <row r="431">
@@ -6017,10 +6017,10 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.030116</v>
+        <v>0.042771</v>
       </c>
       <c r="C431" t="n">
-        <v>0.412245</v>
+        <v>0.494737</v>
       </c>
     </row>
     <row r="432">
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.030255</v>
+        <v>0.043087</v>
       </c>
       <c r="C432" t="n">
-        <v>0.408163</v>
+        <v>0.491228</v>
       </c>
     </row>
     <row r="433">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.030581</v>
+        <v>0.043245</v>
       </c>
       <c r="C433" t="n">
-        <v>0.404082</v>
+        <v>0.487719</v>
       </c>
     </row>
     <row r="434">
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.030616</v>
+        <v>0.043647</v>
       </c>
       <c r="C434" t="n">
-        <v>0.4</v>
+        <v>0.484211</v>
       </c>
     </row>
     <row r="435">
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.030678</v>
+        <v>0.044492</v>
       </c>
       <c r="C435" t="n">
-        <v>0.395918</v>
+        <v>0.480702</v>
       </c>
     </row>
     <row r="436">
@@ -6082,10 +6082,10 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>0.030781</v>
+        <v>0.044609</v>
       </c>
       <c r="C436" t="n">
-        <v>0.391837</v>
+        <v>0.477193</v>
       </c>
     </row>
     <row r="437">
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.031745</v>
+        <v>0.044755</v>
       </c>
       <c r="C437" t="n">
-        <v>0.387755</v>
+        <v>0.473684</v>
       </c>
     </row>
     <row r="438">
@@ -6108,10 +6108,10 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.031934</v>
+        <v>0.045164</v>
       </c>
       <c r="C438" t="n">
-        <v>0.383673</v>
+        <v>0.470175</v>
       </c>
     </row>
     <row r="439">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.032162</v>
+        <v>0.045556</v>
       </c>
       <c r="C439" t="n">
-        <v>0.379592</v>
+        <v>0.466667</v>
       </c>
     </row>
     <row r="440">
@@ -6134,10 +6134,10 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.032185</v>
+        <v>0.045758</v>
       </c>
       <c r="C440" t="n">
-        <v>0.37551</v>
+        <v>0.463158</v>
       </c>
     </row>
     <row r="441">
@@ -6147,10 +6147,10 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.032224</v>
+        <v>0.046124</v>
       </c>
       <c r="C441" t="n">
-        <v>0.371429</v>
+        <v>0.459649</v>
       </c>
     </row>
     <row r="442">
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.03231</v>
+        <v>0.046142</v>
       </c>
       <c r="C442" t="n">
-        <v>0.367347</v>
+        <v>0.45614</v>
       </c>
     </row>
     <row r="443">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.032833</v>
+        <v>0.046645</v>
       </c>
       <c r="C443" t="n">
-        <v>0.363265</v>
+        <v>0.452632</v>
       </c>
     </row>
     <row r="444">
@@ -6186,10 +6186,10 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.03304</v>
+        <v>0.04699</v>
       </c>
       <c r="C444" t="n">
-        <v>0.359184</v>
+        <v>0.449123</v>
       </c>
     </row>
     <row r="445">
@@ -6199,10 +6199,10 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.033169</v>
+        <v>0.047072</v>
       </c>
       <c r="C445" t="n">
-        <v>0.355102</v>
+        <v>0.445614</v>
       </c>
     </row>
     <row r="446">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.033449</v>
+        <v>0.047104</v>
       </c>
       <c r="C446" t="n">
-        <v>0.35102</v>
+        <v>0.442105</v>
       </c>
     </row>
     <row r="447">
@@ -6225,10 +6225,10 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.033794</v>
+        <v>0.047467</v>
       </c>
       <c r="C447" t="n">
-        <v>0.346939</v>
+        <v>0.438596</v>
       </c>
     </row>
     <row r="448">
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.033828</v>
+        <v>0.047863</v>
       </c>
       <c r="C448" t="n">
-        <v>0.342857</v>
+        <v>0.435088</v>
       </c>
     </row>
     <row r="449">
@@ -6251,10 +6251,10 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.03412</v>
+        <v>0.048008</v>
       </c>
       <c r="C449" t="n">
-        <v>0.338776</v>
+        <v>0.431579</v>
       </c>
     </row>
     <row r="450">
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.034726</v>
+        <v>0.048228</v>
       </c>
       <c r="C450" t="n">
-        <v>0.334694</v>
+        <v>0.42807</v>
       </c>
     </row>
     <row r="451">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.035027</v>
+        <v>0.048519</v>
       </c>
       <c r="C451" t="n">
-        <v>0.330612</v>
+        <v>0.424561</v>
       </c>
     </row>
     <row r="452">
@@ -6290,10 +6290,10 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.035812</v>
+        <v>0.049583</v>
       </c>
       <c r="C452" t="n">
-        <v>0.326531</v>
+        <v>0.421053</v>
       </c>
     </row>
     <row r="453">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.036437</v>
+        <v>0.052319</v>
       </c>
       <c r="C453" t="n">
-        <v>0.322449</v>
+        <v>0.417544</v>
       </c>
     </row>
     <row r="454">
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.036503</v>
+        <v>0.052671</v>
       </c>
       <c r="C454" t="n">
-        <v>0.318367</v>
+        <v>0.414035</v>
       </c>
     </row>
     <row r="455">
@@ -6329,10 +6329,10 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.036617</v>
+        <v>0.053622</v>
       </c>
       <c r="C455" t="n">
-        <v>0.314286</v>
+        <v>0.410526</v>
       </c>
     </row>
     <row r="456">
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.036663</v>
+        <v>0.054094</v>
       </c>
       <c r="C456" t="n">
-        <v>0.310204</v>
+        <v>0.407018</v>
       </c>
     </row>
     <row r="457">
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.036886</v>
+        <v>0.054436</v>
       </c>
       <c r="C457" t="n">
-        <v>0.306122</v>
+        <v>0.403509</v>
       </c>
     </row>
     <row r="458">
@@ -6368,10 +6368,10 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.036911</v>
+        <v>0.054892</v>
       </c>
       <c r="C458" t="n">
-        <v>0.302041</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="459">
@@ -6381,10 +6381,10 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.037927</v>
+        <v>0.055026</v>
       </c>
       <c r="C459" t="n">
-        <v>0.297959</v>
+        <v>0.396491</v>
       </c>
     </row>
     <row r="460">
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.038785</v>
+        <v>0.055452</v>
       </c>
       <c r="C460" t="n">
-        <v>0.293878</v>
+        <v>0.392982</v>
       </c>
     </row>
     <row r="461">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.039428</v>
+        <v>0.055659</v>
       </c>
       <c r="C461" t="n">
-        <v>0.289796</v>
+        <v>0.389474</v>
       </c>
     </row>
     <row r="462">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.039677</v>
+        <v>0.05597</v>
       </c>
       <c r="C462" t="n">
-        <v>0.285714</v>
+        <v>0.385965</v>
       </c>
     </row>
     <row r="463">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.040093</v>
+        <v>0.056232</v>
       </c>
       <c r="C463" t="n">
-        <v>0.281633</v>
+        <v>0.382456</v>
       </c>
     </row>
     <row r="464">
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.040198</v>
+        <v>0.05658</v>
       </c>
       <c r="C464" t="n">
-        <v>0.277551</v>
+        <v>0.378947</v>
       </c>
     </row>
     <row r="465">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.040359</v>
+        <v>0.056651</v>
       </c>
       <c r="C465" t="n">
-        <v>0.273469</v>
+        <v>0.375439</v>
       </c>
     </row>
     <row r="466">
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.040386</v>
+        <v>0.056749</v>
       </c>
       <c r="C466" t="n">
-        <v>0.269388</v>
+        <v>0.37193</v>
       </c>
     </row>
     <row r="467">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.041434</v>
+        <v>0.057165</v>
       </c>
       <c r="C467" t="n">
-        <v>0.265306</v>
+        <v>0.368421</v>
       </c>
     </row>
     <row r="468">
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.041858</v>
+        <v>0.057551</v>
       </c>
       <c r="C468" t="n">
-        <v>0.261224</v>
+        <v>0.364912</v>
       </c>
     </row>
     <row r="469">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.044093</v>
+        <v>0.059257</v>
       </c>
       <c r="C469" t="n">
-        <v>0.257143</v>
+        <v>0.361404</v>
       </c>
     </row>
     <row r="470">
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.044155</v>
+        <v>0.059655</v>
       </c>
       <c r="C470" t="n">
-        <v>0.253061</v>
+        <v>0.357895</v>
       </c>
     </row>
     <row r="471">
@@ -6537,10 +6537,10 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.044606</v>
+        <v>0.059707</v>
       </c>
       <c r="C471" t="n">
-        <v>0.24898</v>
+        <v>0.354386</v>
       </c>
     </row>
     <row r="472">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.046074</v>
+        <v>0.060872</v>
       </c>
       <c r="C472" t="n">
-        <v>0.244898</v>
+        <v>0.350877</v>
       </c>
     </row>
     <row r="473">
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.046472</v>
+        <v>0.061358</v>
       </c>
       <c r="C473" t="n">
-        <v>0.240816</v>
+        <v>0.347368</v>
       </c>
     </row>
     <row r="474">
@@ -6576,10 +6576,10 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.046755</v>
+        <v>0.061387</v>
       </c>
       <c r="C474" t="n">
-        <v>0.236735</v>
+        <v>0.34386</v>
       </c>
     </row>
     <row r="475">
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.04738</v>
+        <v>0.062085</v>
       </c>
       <c r="C475" t="n">
-        <v>0.232653</v>
+        <v>0.340351</v>
       </c>
     </row>
     <row r="476">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.047669</v>
+        <v>0.06267300000000001</v>
       </c>
       <c r="C476" t="n">
-        <v>0.228571</v>
+        <v>0.336842</v>
       </c>
     </row>
     <row r="477">
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.048278</v>
+        <v>0.06267499999999999</v>
       </c>
       <c r="C477" t="n">
-        <v>0.22449</v>
+        <v>0.333333</v>
       </c>
     </row>
     <row r="478">
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.049686</v>
+        <v>0.06379600000000001</v>
       </c>
       <c r="C478" t="n">
-        <v>0.220408</v>
+        <v>0.329825</v>
       </c>
     </row>
     <row r="479">
@@ -6641,10 +6641,10 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.050192</v>
+        <v>0.064073</v>
       </c>
       <c r="C479" t="n">
-        <v>0.216327</v>
+        <v>0.326316</v>
       </c>
     </row>
     <row r="480">
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.050352</v>
+        <v>0.064293</v>
       </c>
       <c r="C480" t="n">
-        <v>0.212245</v>
+        <v>0.322807</v>
       </c>
     </row>
     <row r="481">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.051384</v>
+        <v>0.06522</v>
       </c>
       <c r="C481" t="n">
-        <v>0.208163</v>
+        <v>0.319298</v>
       </c>
     </row>
     <row r="482">
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.05139</v>
+        <v>0.065396</v>
       </c>
       <c r="C482" t="n">
-        <v>0.204082</v>
+        <v>0.315789</v>
       </c>
     </row>
     <row r="483">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.051947</v>
+        <v>0.06540899999999999</v>
       </c>
       <c r="C483" t="n">
-        <v>0.2</v>
+        <v>0.312281</v>
       </c>
     </row>
     <row r="484">
@@ -6706,10 +6706,10 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.052199</v>
+        <v>0.065549</v>
       </c>
       <c r="C484" t="n">
-        <v>0.195918</v>
+        <v>0.308772</v>
       </c>
     </row>
     <row r="485">
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.052256</v>
+        <v>0.065835</v>
       </c>
       <c r="C485" t="n">
-        <v>0.191837</v>
+        <v>0.305263</v>
       </c>
     </row>
     <row r="486">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.052602</v>
+        <v>0.065854</v>
       </c>
       <c r="C486" t="n">
-        <v>0.187755</v>
+        <v>0.301754</v>
       </c>
     </row>
     <row r="487">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.052804</v>
+        <v>0.066054</v>
       </c>
       <c r="C487" t="n">
-        <v>0.183673</v>
+        <v>0.298246</v>
       </c>
     </row>
     <row r="488">
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.054048</v>
+        <v>0.066236</v>
       </c>
       <c r="C488" t="n">
-        <v>0.179592</v>
+        <v>0.294737</v>
       </c>
     </row>
     <row r="489">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.054273</v>
+        <v>0.066301</v>
       </c>
       <c r="C489" t="n">
-        <v>0.17551</v>
+        <v>0.291228</v>
       </c>
     </row>
     <row r="490">
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.055704</v>
+        <v>0.06659</v>
       </c>
       <c r="C490" t="n">
-        <v>0.171429</v>
+        <v>0.287719</v>
       </c>
     </row>
     <row r="491">
@@ -6797,10 +6797,10 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.056461</v>
+        <v>0.06712700000000001</v>
       </c>
       <c r="C491" t="n">
-        <v>0.167347</v>
+        <v>0.284211</v>
       </c>
     </row>
     <row r="492">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.056525</v>
+        <v>0.067445</v>
       </c>
       <c r="C492" t="n">
-        <v>0.163265</v>
+        <v>0.280702</v>
       </c>
     </row>
     <row r="493">
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.056937</v>
+        <v>0.067527</v>
       </c>
       <c r="C493" t="n">
-        <v>0.159184</v>
+        <v>0.277193</v>
       </c>
     </row>
     <row r="494">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.059473</v>
+        <v>0.068061</v>
       </c>
       <c r="C494" t="n">
-        <v>0.155102</v>
+        <v>0.273684</v>
       </c>
     </row>
     <row r="495">
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.060802</v>
+        <v>0.068568</v>
       </c>
       <c r="C495" t="n">
-        <v>0.15102</v>
+        <v>0.270175</v>
       </c>
     </row>
     <row r="496">
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.063125</v>
+        <v>0.07224899999999999</v>
       </c>
       <c r="C496" t="n">
-        <v>0.146939</v>
+        <v>0.266667</v>
       </c>
     </row>
     <row r="497">
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.065479</v>
+        <v>0.07235900000000001</v>
       </c>
       <c r="C497" t="n">
-        <v>0.142857</v>
+        <v>0.263158</v>
       </c>
     </row>
     <row r="498">
@@ -6888,10 +6888,10 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.06578199999999999</v>
+        <v>0.073559</v>
       </c>
       <c r="C498" t="n">
-        <v>0.138776</v>
+        <v>0.259649</v>
       </c>
     </row>
     <row r="499">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.068022</v>
+        <v>0.073989</v>
       </c>
       <c r="C499" t="n">
-        <v>0.134694</v>
+        <v>0.25614</v>
       </c>
     </row>
     <row r="500">
@@ -6914,10 +6914,10 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.070881</v>
+        <v>0.075611</v>
       </c>
       <c r="C500" t="n">
-        <v>0.130612</v>
+        <v>0.252632</v>
       </c>
     </row>
     <row r="501">
@@ -6927,10 +6927,10 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.07101200000000001</v>
+        <v>0.07609100000000001</v>
       </c>
       <c r="C501" t="n">
-        <v>0.126531</v>
+        <v>0.249123</v>
       </c>
     </row>
     <row r="502">
@@ -6940,10 +6940,10 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.073532</v>
+        <v>0.07639799999999999</v>
       </c>
       <c r="C502" t="n">
-        <v>0.122449</v>
+        <v>0.245614</v>
       </c>
     </row>
     <row r="503">
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.074841</v>
+        <v>0.07662099999999999</v>
       </c>
       <c r="C503" t="n">
-        <v>0.118367</v>
+        <v>0.242105</v>
       </c>
     </row>
     <row r="504">
@@ -6966,10 +6966,10 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.07573000000000001</v>
+        <v>0.077016</v>
       </c>
       <c r="C504" t="n">
-        <v>0.114286</v>
+        <v>0.238596</v>
       </c>
     </row>
     <row r="505">
@@ -6979,10 +6979,10 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.077164</v>
+        <v>0.077292</v>
       </c>
       <c r="C505" t="n">
-        <v>0.110204</v>
+        <v>0.235088</v>
       </c>
     </row>
     <row r="506">
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.077178</v>
+        <v>0.07875799999999999</v>
       </c>
       <c r="C506" t="n">
-        <v>0.106122</v>
+        <v>0.231579</v>
       </c>
     </row>
     <row r="507">
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.079801</v>
+        <v>0.079572</v>
       </c>
       <c r="C507" t="n">
-        <v>0.102041</v>
+        <v>0.22807</v>
       </c>
     </row>
     <row r="508">
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.081141</v>
+        <v>0.081721</v>
       </c>
       <c r="C508" t="n">
-        <v>0.097959</v>
+        <v>0.224561</v>
       </c>
     </row>
     <row r="509">
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.089948</v>
+        <v>0.08204</v>
       </c>
       <c r="C509" t="n">
-        <v>0.093878</v>
+        <v>0.221053</v>
       </c>
     </row>
     <row r="510">
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.090404</v>
+        <v>0.082191</v>
       </c>
       <c r="C510" t="n">
-        <v>0.089796</v>
+        <v>0.217544</v>
       </c>
     </row>
     <row r="511">
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.090902</v>
+        <v>0.082369</v>
       </c>
       <c r="C511" t="n">
-        <v>0.085714</v>
+        <v>0.214035</v>
       </c>
     </row>
     <row r="512">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.09255099999999999</v>
+        <v>0.084845</v>
       </c>
       <c r="C512" t="n">
-        <v>0.081633</v>
+        <v>0.210526</v>
       </c>
     </row>
     <row r="513">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.09404800000000001</v>
+        <v>0.08505699999999999</v>
       </c>
       <c r="C513" t="n">
-        <v>0.07755099999999999</v>
+        <v>0.207018</v>
       </c>
     </row>
     <row r="514">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.095627</v>
+        <v>0.085952</v>
       </c>
       <c r="C514" t="n">
-        <v>0.07346900000000001</v>
+        <v>0.203509</v>
       </c>
     </row>
     <row r="515">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.097673</v>
+        <v>0.086106</v>
       </c>
       <c r="C515" t="n">
-        <v>0.06938800000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="516">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.102613</v>
+        <v>0.08666</v>
       </c>
       <c r="C516" t="n">
-        <v>0.065306</v>
+        <v>0.196491</v>
       </c>
     </row>
     <row r="517">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.103855</v>
+        <v>0.088506</v>
       </c>
       <c r="C517" t="n">
-        <v>0.061224</v>
+        <v>0.192982</v>
       </c>
     </row>
     <row r="518">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.11022</v>
+        <v>0.089291</v>
       </c>
       <c r="C518" t="n">
-        <v>0.057143</v>
+        <v>0.189474</v>
       </c>
     </row>
     <row r="519">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.114933</v>
+        <v>0.09160600000000001</v>
       </c>
       <c r="C519" t="n">
-        <v>0.053061</v>
+        <v>0.185965</v>
       </c>
     </row>
     <row r="520">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.117592</v>
+        <v>0.092195</v>
       </c>
       <c r="C520" t="n">
-        <v>0.04898</v>
+        <v>0.182456</v>
       </c>
     </row>
     <row r="521">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.121006</v>
+        <v>0.09248000000000001</v>
       </c>
       <c r="C521" t="n">
-        <v>0.044898</v>
+        <v>0.178947</v>
       </c>
     </row>
     <row r="522">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.12411</v>
+        <v>0.09504600000000001</v>
       </c>
       <c r="C522" t="n">
-        <v>0.040816</v>
+        <v>0.175439</v>
       </c>
     </row>
     <row r="523">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.1412</v>
+        <v>0.096599</v>
       </c>
       <c r="C523" t="n">
-        <v>0.036735</v>
+        <v>0.17193</v>
       </c>
     </row>
     <row r="524">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.147889</v>
+        <v>0.09758699999999999</v>
       </c>
       <c r="C524" t="n">
-        <v>0.032653</v>
+        <v>0.168421</v>
       </c>
     </row>
     <row r="525">
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.158456</v>
+        <v>0.09983599999999999</v>
       </c>
       <c r="C525" t="n">
-        <v>0.028571</v>
+        <v>0.164912</v>
       </c>
     </row>
     <row r="526">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.159842</v>
+        <v>0.103271</v>
       </c>
       <c r="C526" t="n">
-        <v>0.02449</v>
+        <v>0.161404</v>
       </c>
     </row>
     <row r="527">
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.231725</v>
+        <v>0.106162</v>
       </c>
       <c r="C527" t="n">
-        <v>0.020408</v>
+        <v>0.157895</v>
       </c>
     </row>
     <row r="528">
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.265458</v>
+        <v>0.108018</v>
       </c>
       <c r="C528" t="n">
-        <v>0.016327</v>
+        <v>0.154386</v>
       </c>
     </row>
     <row r="529">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.292037</v>
+        <v>0.108468</v>
       </c>
       <c r="C529" t="n">
-        <v>0.012245</v>
+        <v>0.150877</v>
       </c>
     </row>
     <row r="530">
@@ -7304,10 +7304,10 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.295023</v>
+        <v>0.110991</v>
       </c>
       <c r="C530" t="n">
-        <v>0.008163</v>
+        <v>0.147368</v>
       </c>
     </row>
     <row r="531">
@@ -7317,530 +7317,530 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.434987</v>
+        <v>0.111192</v>
       </c>
       <c r="C531" t="n">
-        <v>0.004082</v>
+        <v>0.14386</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.000393</v>
+        <v>0.111406</v>
       </c>
       <c r="C532" t="n">
-        <v>1</v>
+        <v>0.140351</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.00044</v>
+        <v>0.111661</v>
       </c>
       <c r="C533" t="n">
-        <v>0.995984</v>
+        <v>0.136842</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.00135</v>
+        <v>0.111915</v>
       </c>
       <c r="C534" t="n">
-        <v>0.991968</v>
+        <v>0.133333</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.001558</v>
+        <v>0.114749</v>
       </c>
       <c r="C535" t="n">
-        <v>0.9879520000000001</v>
+        <v>0.129825</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.00162</v>
+        <v>0.119806</v>
       </c>
       <c r="C536" t="n">
-        <v>0.983936</v>
+        <v>0.126316</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.001657</v>
+        <v>0.120543</v>
       </c>
       <c r="C537" t="n">
-        <v>0.97992</v>
+        <v>0.122807</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.001705</v>
+        <v>0.121385</v>
       </c>
       <c r="C538" t="n">
-        <v>0.975904</v>
+        <v>0.119298</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.001811</v>
+        <v>0.121551</v>
       </c>
       <c r="C539" t="n">
-        <v>0.971888</v>
+        <v>0.115789</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.001859</v>
+        <v>0.12327</v>
       </c>
       <c r="C540" t="n">
-        <v>0.967871</v>
+        <v>0.112281</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.002103</v>
+        <v>0.124229</v>
       </c>
       <c r="C541" t="n">
-        <v>0.963855</v>
+        <v>0.108772</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.002846</v>
+        <v>0.125255</v>
       </c>
       <c r="C542" t="n">
-        <v>0.959839</v>
+        <v>0.105263</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.002868</v>
+        <v>0.125971</v>
       </c>
       <c r="C543" t="n">
-        <v>0.955823</v>
+        <v>0.101754</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.002967</v>
+        <v>0.128853</v>
       </c>
       <c r="C544" t="n">
-        <v>0.951807</v>
+        <v>0.098246</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.002982</v>
+        <v>0.13469</v>
       </c>
       <c r="C545" t="n">
-        <v>0.9477910000000001</v>
+        <v>0.094737</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.003053</v>
+        <v>0.13761</v>
       </c>
       <c r="C546" t="n">
-        <v>0.943775</v>
+        <v>0.091228</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.003273</v>
+        <v>0.138713</v>
       </c>
       <c r="C547" t="n">
-        <v>0.939759</v>
+        <v>0.08771900000000001</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.003431</v>
+        <v>0.141686</v>
       </c>
       <c r="C548" t="n">
-        <v>0.935743</v>
+        <v>0.08421099999999999</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.003935</v>
+        <v>0.143512</v>
       </c>
       <c r="C549" t="n">
-        <v>0.931727</v>
+        <v>0.080702</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.004109</v>
+        <v>0.14578</v>
       </c>
       <c r="C550" t="n">
-        <v>0.927711</v>
+        <v>0.077193</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.00415</v>
+        <v>0.160411</v>
       </c>
       <c r="C551" t="n">
-        <v>0.923695</v>
+        <v>0.073684</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.004377</v>
+        <v>0.162199</v>
       </c>
       <c r="C552" t="n">
-        <v>0.919679</v>
+        <v>0.070175</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.00464</v>
+        <v>0.164193</v>
       </c>
       <c r="C553" t="n">
-        <v>0.915663</v>
+        <v>0.066667</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.004692</v>
+        <v>0.164251</v>
       </c>
       <c r="C554" t="n">
-        <v>0.911647</v>
+        <v>0.06315800000000001</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.005028</v>
+        <v>0.165046</v>
       </c>
       <c r="C555" t="n">
-        <v>0.907631</v>
+        <v>0.059649</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.005531</v>
+        <v>0.170766</v>
       </c>
       <c r="C556" t="n">
-        <v>0.903614</v>
+        <v>0.05614</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.005643</v>
+        <v>0.185261</v>
       </c>
       <c r="C557" t="n">
-        <v>0.899598</v>
+        <v>0.052632</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.005893</v>
+        <v>0.198079</v>
       </c>
       <c r="C558" t="n">
-        <v>0.895582</v>
+        <v>0.049123</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.006437</v>
+        <v>0.221354</v>
       </c>
       <c r="C559" t="n">
-        <v>0.891566</v>
+        <v>0.045614</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.006614</v>
+        <v>0.223016</v>
       </c>
       <c r="C560" t="n">
-        <v>0.88755</v>
+        <v>0.042105</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.006745</v>
+        <v>0.241107</v>
       </c>
       <c r="C561" t="n">
-        <v>0.883534</v>
+        <v>0.038596</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.006791</v>
+        <v>0.272102</v>
       </c>
       <c r="C562" t="n">
-        <v>0.879518</v>
+        <v>0.035088</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.00744</v>
+        <v>0.288091</v>
       </c>
       <c r="C563" t="n">
-        <v>0.875502</v>
+        <v>0.031579</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.007479</v>
+        <v>0.305357</v>
       </c>
       <c r="C564" t="n">
-        <v>0.871486</v>
+        <v>0.02807</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.007749</v>
+        <v>0.330018</v>
       </c>
       <c r="C565" t="n">
-        <v>0.86747</v>
+        <v>0.024561</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.007804</v>
+        <v>0.361398</v>
       </c>
       <c r="C566" t="n">
-        <v>0.8634540000000001</v>
+        <v>0.021053</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.00812</v>
+        <v>0.373207</v>
       </c>
       <c r="C567" t="n">
-        <v>0.859438</v>
+        <v>0.017544</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.008144999999999999</v>
+        <v>0.486711</v>
       </c>
       <c r="C568" t="n">
-        <v>0.855422</v>
+        <v>0.014035</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.008246</v>
+        <v>0.61993</v>
       </c>
       <c r="C569" t="n">
-        <v>0.851406</v>
+        <v>0.010526</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.008370000000000001</v>
+        <v>0.870505</v>
       </c>
       <c r="C570" t="n">
-        <v>0.84739</v>
+        <v>0.007018</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Adjusted new profile</t>
+          <t>Adjusted old profile</t>
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.008966</v>
+        <v>0.880089</v>
       </c>
       <c r="C571" t="n">
-        <v>0.843373</v>
+        <v>0.003509</v>
       </c>
     </row>
     <row r="572">
@@ -7850,10 +7850,10 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.008971</v>
+        <v>0.000487</v>
       </c>
       <c r="C572" t="n">
-        <v>0.839357</v>
+        <v>1</v>
       </c>
     </row>
     <row r="573">
@@ -7863,10 +7863,10 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.009084999999999999</v>
+        <v>0.000497</v>
       </c>
       <c r="C573" t="n">
-        <v>0.835341</v>
+        <v>0.996491</v>
       </c>
     </row>
     <row r="574">
@@ -7876,10 +7876,10 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.009087</v>
+        <v>0.001697</v>
       </c>
       <c r="C574" t="n">
-        <v>0.831325</v>
+        <v>0.992982</v>
       </c>
     </row>
     <row r="575">
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.009332999999999999</v>
+        <v>0.001891</v>
       </c>
       <c r="C575" t="n">
-        <v>0.827309</v>
+        <v>0.989474</v>
       </c>
     </row>
     <row r="576">
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.009395000000000001</v>
+        <v>0.002469</v>
       </c>
       <c r="C576" t="n">
-        <v>0.8232930000000001</v>
+        <v>0.985965</v>
       </c>
     </row>
     <row r="577">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.009651</v>
+        <v>0.002527</v>
       </c>
       <c r="C577" t="n">
-        <v>0.819277</v>
+        <v>0.982456</v>
       </c>
     </row>
     <row r="578">
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.009663</v>
+        <v>0.002808</v>
       </c>
       <c r="C578" t="n">
-        <v>0.815261</v>
+        <v>0.978947</v>
       </c>
     </row>
     <row r="579">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.00974</v>
+        <v>0.003707</v>
       </c>
       <c r="C579" t="n">
-        <v>0.811245</v>
+        <v>0.9754389999999999</v>
       </c>
     </row>
     <row r="580">
@@ -7954,10 +7954,10 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.010226</v>
+        <v>0.00379</v>
       </c>
       <c r="C580" t="n">
-        <v>0.807229</v>
+        <v>0.97193</v>
       </c>
     </row>
     <row r="581">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.010316</v>
+        <v>0.004029</v>
       </c>
       <c r="C581" t="n">
-        <v>0.803213</v>
+        <v>0.968421</v>
       </c>
     </row>
     <row r="582">
@@ -7980,10 +7980,10 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.01043</v>
+        <v>0.004072</v>
       </c>
       <c r="C582" t="n">
-        <v>0.799197</v>
+        <v>0.964912</v>
       </c>
     </row>
     <row r="583">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.010525</v>
+        <v>0.004235</v>
       </c>
       <c r="C583" t="n">
-        <v>0.795181</v>
+        <v>0.961404</v>
       </c>
     </row>
     <row r="584">
@@ -8006,10 +8006,10 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.010611</v>
+        <v>0.004293</v>
       </c>
       <c r="C584" t="n">
-        <v>0.791165</v>
+        <v>0.9578950000000001</v>
       </c>
     </row>
     <row r="585">
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.010743</v>
+        <v>0.004622</v>
       </c>
       <c r="C585" t="n">
-        <v>0.787149</v>
+        <v>0.954386</v>
       </c>
     </row>
     <row r="586">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.011307</v>
+        <v>0.004838</v>
       </c>
       <c r="C586" t="n">
-        <v>0.783133</v>
+        <v>0.950877</v>
       </c>
     </row>
     <row r="587">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.01133</v>
+        <v>0.004935</v>
       </c>
       <c r="C587" t="n">
-        <v>0.779116</v>
+        <v>0.947368</v>
       </c>
     </row>
     <row r="588">
@@ -8058,10 +8058,10 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.011563</v>
+        <v>0.005142</v>
       </c>
       <c r="C588" t="n">
-        <v>0.7751</v>
+        <v>0.94386</v>
       </c>
     </row>
     <row r="589">
@@ -8071,10 +8071,10 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.011852</v>
+        <v>0.005223</v>
       </c>
       <c r="C589" t="n">
-        <v>0.771084</v>
+        <v>0.940351</v>
       </c>
     </row>
     <row r="590">
@@ -8084,10 +8084,10 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.011856</v>
+        <v>0.00526</v>
       </c>
       <c r="C590" t="n">
-        <v>0.767068</v>
+        <v>0.936842</v>
       </c>
     </row>
     <row r="591">
@@ -8097,10 +8097,10 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.011907</v>
+        <v>0.005335</v>
       </c>
       <c r="C591" t="n">
-        <v>0.763052</v>
+        <v>0.933333</v>
       </c>
     </row>
     <row r="592">
@@ -8110,10 +8110,10 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.011971</v>
+        <v>0.005658</v>
       </c>
       <c r="C592" t="n">
-        <v>0.759036</v>
+        <v>0.929825</v>
       </c>
     </row>
     <row r="593">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.011978</v>
+        <v>0.005716</v>
       </c>
       <c r="C593" t="n">
-        <v>0.75502</v>
+        <v>0.926316</v>
       </c>
     </row>
     <row r="594">
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.012377</v>
+        <v>0.005957</v>
       </c>
       <c r="C594" t="n">
-        <v>0.751004</v>
+        <v>0.922807</v>
       </c>
     </row>
     <row r="595">
@@ -8149,10 +8149,10 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.012544</v>
+        <v>0.007614</v>
       </c>
       <c r="C595" t="n">
-        <v>0.746988</v>
+        <v>0.9192979999999999</v>
       </c>
     </row>
     <row r="596">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.012732</v>
+        <v>0.008116</v>
       </c>
       <c r="C596" t="n">
-        <v>0.742972</v>
+        <v>0.915789</v>
       </c>
     </row>
     <row r="597">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.012956</v>
+        <v>0.008288999999999999</v>
       </c>
       <c r="C597" t="n">
-        <v>0.7389559999999999</v>
+        <v>0.912281</v>
       </c>
     </row>
     <row r="598">
@@ -8188,10 +8188,10 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.012976</v>
+        <v>0.008359</v>
       </c>
       <c r="C598" t="n">
-        <v>0.73494</v>
+        <v>0.908772</v>
       </c>
     </row>
     <row r="599">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.01345</v>
+        <v>0.00919</v>
       </c>
       <c r="C599" t="n">
-        <v>0.730924</v>
+        <v>0.905263</v>
       </c>
     </row>
     <row r="600">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.013549</v>
+        <v>0.009423000000000001</v>
       </c>
       <c r="C600" t="n">
-        <v>0.726908</v>
+        <v>0.9017539999999999</v>
       </c>
     </row>
     <row r="601">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.013824</v>
+        <v>0.009490999999999999</v>
       </c>
       <c r="C601" t="n">
-        <v>0.722892</v>
+        <v>0.898246</v>
       </c>
     </row>
     <row r="602">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.014014</v>
+        <v>0.009582</v>
       </c>
       <c r="C602" t="n">
-        <v>0.718876</v>
+        <v>0.894737</v>
       </c>
     </row>
     <row r="603">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.01403</v>
+        <v>0.009665</v>
       </c>
       <c r="C603" t="n">
-        <v>0.714859</v>
+        <v>0.891228</v>
       </c>
     </row>
     <row r="604">
@@ -8266,10 +8266,10 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.014148</v>
+        <v>0.009991</v>
       </c>
       <c r="C604" t="n">
-        <v>0.710843</v>
+        <v>0.887719</v>
       </c>
     </row>
     <row r="605">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.014184</v>
+        <v>0.010355</v>
       </c>
       <c r="C605" t="n">
-        <v>0.706827</v>
+        <v>0.884211</v>
       </c>
     </row>
     <row r="606">
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.014446</v>
+        <v>0.010465</v>
       </c>
       <c r="C606" t="n">
-        <v>0.702811</v>
+        <v>0.880702</v>
       </c>
     </row>
     <row r="607">
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.014474</v>
+        <v>0.010633</v>
       </c>
       <c r="C607" t="n">
-        <v>0.6987950000000001</v>
+        <v>0.877193</v>
       </c>
     </row>
     <row r="608">
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.015235</v>
+        <v>0.010726</v>
       </c>
       <c r="C608" t="n">
-        <v>0.694779</v>
+        <v>0.873684</v>
       </c>
     </row>
     <row r="609">
@@ -8331,10 +8331,10 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.015581</v>
+        <v>0.010738</v>
       </c>
       <c r="C609" t="n">
-        <v>0.690763</v>
+        <v>0.870175</v>
       </c>
     </row>
     <row r="610">
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.015958</v>
+        <v>0.010919</v>
       </c>
       <c r="C610" t="n">
-        <v>0.686747</v>
+        <v>0.866667</v>
       </c>
     </row>
     <row r="611">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.016344</v>
+        <v>0.011099</v>
       </c>
       <c r="C611" t="n">
-        <v>0.682731</v>
+        <v>0.863158</v>
       </c>
     </row>
     <row r="612">
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.016434</v>
+        <v>0.012096</v>
       </c>
       <c r="C612" t="n">
-        <v>0.678715</v>
+        <v>0.859649</v>
       </c>
     </row>
     <row r="613">
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.016482</v>
+        <v>0.012216</v>
       </c>
       <c r="C613" t="n">
-        <v>0.674699</v>
+        <v>0.85614</v>
       </c>
     </row>
     <row r="614">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.01685</v>
+        <v>0.012946</v>
       </c>
       <c r="C614" t="n">
-        <v>0.670683</v>
+        <v>0.8526319999999999</v>
       </c>
     </row>
     <row r="615">
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.017116</v>
+        <v>0.013189</v>
       </c>
       <c r="C615" t="n">
-        <v>0.666667</v>
+        <v>0.849123</v>
       </c>
     </row>
     <row r="616">
@@ -8422,10 +8422,10 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.017131</v>
+        <v>0.013261</v>
       </c>
       <c r="C616" t="n">
-        <v>0.662651</v>
+        <v>0.845614</v>
       </c>
     </row>
     <row r="617">
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.017322</v>
+        <v>0.013266</v>
       </c>
       <c r="C617" t="n">
-        <v>0.658635</v>
+        <v>0.842105</v>
       </c>
     </row>
     <row r="618">
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.017365</v>
+        <v>0.0141</v>
       </c>
       <c r="C618" t="n">
-        <v>0.654618</v>
+        <v>0.838596</v>
       </c>
     </row>
     <row r="619">
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.01746</v>
+        <v>0.014558</v>
       </c>
       <c r="C619" t="n">
-        <v>0.650602</v>
+        <v>0.8350880000000001</v>
       </c>
     </row>
     <row r="620">
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.018011</v>
+        <v>0.014561</v>
       </c>
       <c r="C620" t="n">
-        <v>0.646586</v>
+        <v>0.831579</v>
       </c>
     </row>
     <row r="621">
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.018065</v>
+        <v>0.015133</v>
       </c>
       <c r="C621" t="n">
-        <v>0.64257</v>
+        <v>0.82807</v>
       </c>
     </row>
     <row r="622">
@@ -8500,10 +8500,10 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.018516</v>
+        <v>0.01525</v>
       </c>
       <c r="C622" t="n">
-        <v>0.638554</v>
+        <v>0.824561</v>
       </c>
     </row>
     <row r="623">
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.018698</v>
+        <v>0.015704</v>
       </c>
       <c r="C623" t="n">
-        <v>0.634538</v>
+        <v>0.821053</v>
       </c>
     </row>
     <row r="624">
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.019385</v>
+        <v>0.015829</v>
       </c>
       <c r="C624" t="n">
-        <v>0.630522</v>
+        <v>0.817544</v>
       </c>
     </row>
     <row r="625">
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.019637</v>
+        <v>0.015897</v>
       </c>
       <c r="C625" t="n">
-        <v>0.626506</v>
+        <v>0.814035</v>
       </c>
     </row>
     <row r="626">
@@ -8552,10 +8552,10 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.019862</v>
+        <v>0.016176</v>
       </c>
       <c r="C626" t="n">
-        <v>0.62249</v>
+        <v>0.810526</v>
       </c>
     </row>
     <row r="627">
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.019965</v>
+        <v>0.016713</v>
       </c>
       <c r="C627" t="n">
-        <v>0.618474</v>
+        <v>0.807018</v>
       </c>
     </row>
     <row r="628">
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.019973</v>
+        <v>0.016898</v>
       </c>
       <c r="C628" t="n">
-        <v>0.6144579999999999</v>
+        <v>0.803509</v>
       </c>
     </row>
     <row r="629">
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.020041</v>
+        <v>0.017008</v>
       </c>
       <c r="C629" t="n">
-        <v>0.610442</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="630">
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.020489</v>
+        <v>0.017627</v>
       </c>
       <c r="C630" t="n">
-        <v>0.606426</v>
+        <v>0.7964909999999999</v>
       </c>
     </row>
     <row r="631">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.02071</v>
+        <v>0.017812</v>
       </c>
       <c r="C631" t="n">
-        <v>0.60241</v>
+        <v>0.792982</v>
       </c>
     </row>
     <row r="632">
@@ -8630,10 +8630,10 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.020961</v>
+        <v>0.018</v>
       </c>
       <c r="C632" t="n">
-        <v>0.598394</v>
+        <v>0.789474</v>
       </c>
     </row>
     <row r="633">
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.021125</v>
+        <v>0.01838</v>
       </c>
       <c r="C633" t="n">
-        <v>0.594378</v>
+        <v>0.785965</v>
       </c>
     </row>
     <row r="634">
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.021326</v>
+        <v>0.018445</v>
       </c>
       <c r="C634" t="n">
-        <v>0.590361</v>
+        <v>0.782456</v>
       </c>
     </row>
     <row r="635">
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.02157</v>
+        <v>0.019131</v>
       </c>
       <c r="C635" t="n">
-        <v>0.586345</v>
+        <v>0.7789469999999999</v>
       </c>
     </row>
     <row r="636">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.022123</v>
+        <v>0.019344</v>
       </c>
       <c r="C636" t="n">
-        <v>0.582329</v>
+        <v>0.775439</v>
       </c>
     </row>
     <row r="637">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.022294</v>
+        <v>0.019568</v>
       </c>
       <c r="C637" t="n">
-        <v>0.578313</v>
+        <v>0.77193</v>
       </c>
     </row>
     <row r="638">
@@ -8708,10 +8708,10 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.022312</v>
+        <v>0.020159</v>
       </c>
       <c r="C638" t="n">
-        <v>0.5742969999999999</v>
+        <v>0.768421</v>
       </c>
     </row>
     <row r="639">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.022373</v>
+        <v>0.02063</v>
       </c>
       <c r="C639" t="n">
-        <v>0.570281</v>
+        <v>0.764912</v>
       </c>
     </row>
     <row r="640">
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.02263</v>
+        <v>0.020889</v>
       </c>
       <c r="C640" t="n">
-        <v>0.566265</v>
+        <v>0.761404</v>
       </c>
     </row>
     <row r="641">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.022891</v>
+        <v>0.021096</v>
       </c>
       <c r="C641" t="n">
-        <v>0.562249</v>
+        <v>0.757895</v>
       </c>
     </row>
     <row r="642">
@@ -8760,10 +8760,10 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.023474</v>
+        <v>0.021355</v>
       </c>
       <c r="C642" t="n">
-        <v>0.558233</v>
+        <v>0.754386</v>
       </c>
     </row>
     <row r="643">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.023523</v>
+        <v>0.022045</v>
       </c>
       <c r="C643" t="n">
-        <v>0.554217</v>
+        <v>0.750877</v>
       </c>
     </row>
     <row r="644">
@@ -8786,10 +8786,10 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.024075</v>
+        <v>0.0223</v>
       </c>
       <c r="C644" t="n">
-        <v>0.5502010000000001</v>
+        <v>0.747368</v>
       </c>
     </row>
     <row r="645">
@@ -8799,10 +8799,10 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.024129</v>
+        <v>0.023224</v>
       </c>
       <c r="C645" t="n">
-        <v>0.546185</v>
+        <v>0.74386</v>
       </c>
     </row>
     <row r="646">
@@ -8812,10 +8812,10 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.024456</v>
+        <v>0.02374</v>
       </c>
       <c r="C646" t="n">
-        <v>0.542169</v>
+        <v>0.740351</v>
       </c>
     </row>
     <row r="647">
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.024577</v>
+        <v>0.023828</v>
       </c>
       <c r="C647" t="n">
-        <v>0.538153</v>
+        <v>0.736842</v>
       </c>
     </row>
     <row r="648">
@@ -8838,10 +8838,10 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.024631</v>
+        <v>0.024041</v>
       </c>
       <c r="C648" t="n">
-        <v>0.534137</v>
+        <v>0.733333</v>
       </c>
     </row>
     <row r="649">
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.024814</v>
+        <v>0.02419</v>
       </c>
       <c r="C649" t="n">
-        <v>0.53012</v>
+        <v>0.7298249999999999</v>
       </c>
     </row>
     <row r="650">
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.025036</v>
+        <v>0.024295</v>
       </c>
       <c r="C650" t="n">
-        <v>0.526104</v>
+        <v>0.726316</v>
       </c>
     </row>
     <row r="651">
@@ -8877,10 +8877,10 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.025244</v>
+        <v>0.024468</v>
       </c>
       <c r="C651" t="n">
-        <v>0.522088</v>
+        <v>0.722807</v>
       </c>
     </row>
     <row r="652">
@@ -8890,10 +8890,10 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.025315</v>
+        <v>0.024847</v>
       </c>
       <c r="C652" t="n">
-        <v>0.518072</v>
+        <v>0.719298</v>
       </c>
     </row>
     <row r="653">
@@ -8903,10 +8903,10 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.025637</v>
+        <v>0.026529</v>
       </c>
       <c r="C653" t="n">
-        <v>0.514056</v>
+        <v>0.715789</v>
       </c>
     </row>
     <row r="654">
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.02636</v>
+        <v>0.026915</v>
       </c>
       <c r="C654" t="n">
-        <v>0.51004</v>
+        <v>0.7122810000000001</v>
       </c>
     </row>
     <row r="655">
@@ -8929,10 +8929,10 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.0264</v>
+        <v>0.027084</v>
       </c>
       <c r="C655" t="n">
-        <v>0.506024</v>
+        <v>0.708772</v>
       </c>
     </row>
     <row r="656">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.026462</v>
+        <v>0.02761</v>
       </c>
       <c r="C656" t="n">
-        <v>0.502008</v>
+        <v>0.705263</v>
       </c>
     </row>
     <row r="657">
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.026513</v>
+        <v>0.027777</v>
       </c>
       <c r="C657" t="n">
-        <v>0.497992</v>
+        <v>0.701754</v>
       </c>
     </row>
     <row r="658">
@@ -8968,10 +8968,10 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.027366</v>
+        <v>0.02788</v>
       </c>
       <c r="C658" t="n">
-        <v>0.493976</v>
+        <v>0.698246</v>
       </c>
     </row>
     <row r="659">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.027372</v>
+        <v>0.027927</v>
       </c>
       <c r="C659" t="n">
-        <v>0.48996</v>
+        <v>0.694737</v>
       </c>
     </row>
     <row r="660">
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.028877</v>
+        <v>0.028339</v>
       </c>
       <c r="C660" t="n">
-        <v>0.485944</v>
+        <v>0.691228</v>
       </c>
     </row>
     <row r="661">
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.029087</v>
+        <v>0.029373</v>
       </c>
       <c r="C661" t="n">
-        <v>0.481928</v>
+        <v>0.687719</v>
       </c>
     </row>
     <row r="662">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.029422</v>
+        <v>0.029462</v>
       </c>
       <c r="C662" t="n">
-        <v>0.477912</v>
+        <v>0.684211</v>
       </c>
     </row>
     <row r="663">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.030342</v>
+        <v>0.02992</v>
       </c>
       <c r="C663" t="n">
-        <v>0.473896</v>
+        <v>0.680702</v>
       </c>
     </row>
     <row r="664">
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.030389</v>
+        <v>0.030165</v>
       </c>
       <c r="C664" t="n">
-        <v>0.46988</v>
+        <v>0.677193</v>
       </c>
     </row>
     <row r="665">
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.030649</v>
+        <v>0.030918</v>
       </c>
       <c r="C665" t="n">
-        <v>0.465863</v>
+        <v>0.6736839999999999</v>
       </c>
     </row>
     <row r="666">
@@ -9072,10 +9072,10 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.030657</v>
+        <v>0.030932</v>
       </c>
       <c r="C666" t="n">
-        <v>0.461847</v>
+        <v>0.670175</v>
       </c>
     </row>
     <row r="667">
@@ -9085,10 +9085,10 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.031119</v>
+        <v>0.031097</v>
       </c>
       <c r="C667" t="n">
-        <v>0.457831</v>
+        <v>0.666667</v>
       </c>
     </row>
     <row r="668">
@@ -9098,10 +9098,10 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.031472</v>
+        <v>0.031157</v>
       </c>
       <c r="C668" t="n">
-        <v>0.453815</v>
+        <v>0.663158</v>
       </c>
     </row>
     <row r="669">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.031585</v>
+        <v>0.031333</v>
       </c>
       <c r="C669" t="n">
-        <v>0.449799</v>
+        <v>0.659649</v>
       </c>
     </row>
     <row r="670">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.031861</v>
+        <v>0.031999</v>
       </c>
       <c r="C670" t="n">
-        <v>0.445783</v>
+        <v>0.6561399999999999</v>
       </c>
     </row>
     <row r="671">
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.032011</v>
+        <v>0.03205</v>
       </c>
       <c r="C671" t="n">
-        <v>0.441767</v>
+        <v>0.652632</v>
       </c>
     </row>
     <row r="672">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.032048</v>
+        <v>0.032635</v>
       </c>
       <c r="C672" t="n">
-        <v>0.437751</v>
+        <v>0.649123</v>
       </c>
     </row>
     <row r="673">
@@ -9163,10 +9163,10 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.03237</v>
+        <v>0.033001</v>
       </c>
       <c r="C673" t="n">
-        <v>0.433735</v>
+        <v>0.645614</v>
       </c>
     </row>
     <row r="674">
@@ -9176,10 +9176,10 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.0325</v>
+        <v>0.033469</v>
       </c>
       <c r="C674" t="n">
-        <v>0.429719</v>
+        <v>0.642105</v>
       </c>
     </row>
     <row r="675">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.032663</v>
+        <v>0.033845</v>
       </c>
       <c r="C675" t="n">
-        <v>0.425703</v>
+        <v>0.6385960000000001</v>
       </c>
     </row>
     <row r="676">
@@ -9202,10 +9202,10 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.033538</v>
+        <v>0.033914</v>
       </c>
       <c r="C676" t="n">
-        <v>0.421687</v>
+        <v>0.635088</v>
       </c>
     </row>
     <row r="677">
@@ -9215,10 +9215,10 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.034112</v>
+        <v>0.034753</v>
       </c>
       <c r="C677" t="n">
-        <v>0.417671</v>
+        <v>0.631579</v>
       </c>
     </row>
     <row r="678">
@@ -9228,10 +9228,10 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.034451</v>
+        <v>0.034784</v>
       </c>
       <c r="C678" t="n">
-        <v>0.413655</v>
+        <v>0.62807</v>
       </c>
     </row>
     <row r="679">
@@ -9241,10 +9241,10 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.03469</v>
+        <v>0.034794</v>
       </c>
       <c r="C679" t="n">
-        <v>0.409639</v>
+        <v>0.624561</v>
       </c>
     </row>
     <row r="680">
@@ -9254,10 +9254,10 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.03486</v>
+        <v>0.035312</v>
       </c>
       <c r="C680" t="n">
-        <v>0.405622</v>
+        <v>0.621053</v>
       </c>
     </row>
     <row r="681">
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.034884</v>
+        <v>0.035795</v>
       </c>
       <c r="C681" t="n">
-        <v>0.401606</v>
+        <v>0.617544</v>
       </c>
     </row>
     <row r="682">
@@ -9280,10 +9280,10 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.034923</v>
+        <v>0.03587</v>
       </c>
       <c r="C682" t="n">
-        <v>0.39759</v>
+        <v>0.614035</v>
       </c>
     </row>
     <row r="683">
@@ -9293,10 +9293,10 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.035103</v>
+        <v>0.036294</v>
       </c>
       <c r="C683" t="n">
-        <v>0.393574</v>
+        <v>0.610526</v>
       </c>
     </row>
     <row r="684">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.035483</v>
+        <v>0.036623</v>
       </c>
       <c r="C684" t="n">
-        <v>0.389558</v>
+        <v>0.6070179999999999</v>
       </c>
     </row>
     <row r="685">
@@ -9319,10 +9319,10 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.035882</v>
+        <v>0.036695</v>
       </c>
       <c r="C685" t="n">
-        <v>0.385542</v>
+        <v>0.603509</v>
       </c>
     </row>
     <row r="686">
@@ -9332,10 +9332,10 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.036042</v>
+        <v>0.037054</v>
       </c>
       <c r="C686" t="n">
-        <v>0.381526</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="687">
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.036211</v>
+        <v>0.037247</v>
       </c>
       <c r="C687" t="n">
-        <v>0.37751</v>
+        <v>0.596491</v>
       </c>
     </row>
     <row r="688">
@@ -9358,10 +9358,10 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.036643</v>
+        <v>0.037874</v>
       </c>
       <c r="C688" t="n">
-        <v>0.373494</v>
+        <v>0.592982</v>
       </c>
     </row>
     <row r="689">
@@ -9371,10 +9371,10 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.036678</v>
+        <v>0.038695</v>
       </c>
       <c r="C689" t="n">
-        <v>0.369478</v>
+        <v>0.5894740000000001</v>
       </c>
     </row>
     <row r="690">
@@ -9384,10 +9384,10 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.036944</v>
+        <v>0.038946</v>
       </c>
       <c r="C690" t="n">
-        <v>0.365462</v>
+        <v>0.585965</v>
       </c>
     </row>
     <row r="691">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.037073</v>
+        <v>0.039079</v>
       </c>
       <c r="C691" t="n">
-        <v>0.361446</v>
+        <v>0.582456</v>
       </c>
     </row>
     <row r="692">
@@ -9410,10 +9410,10 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.037191</v>
+        <v>0.039245</v>
       </c>
       <c r="C692" t="n">
-        <v>0.35743</v>
+        <v>0.578947</v>
       </c>
     </row>
     <row r="693">
@@ -9423,10 +9423,10 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.037316</v>
+        <v>0.03951</v>
       </c>
       <c r="C693" t="n">
-        <v>0.353414</v>
+        <v>0.575439</v>
       </c>
     </row>
     <row r="694">
@@ -9436,10 +9436,10 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.037747</v>
+        <v>0.039963</v>
       </c>
       <c r="C694" t="n">
-        <v>0.349398</v>
+        <v>0.57193</v>
       </c>
     </row>
     <row r="695">
@@ -9449,10 +9449,10 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.03842</v>
+        <v>0.04026</v>
       </c>
       <c r="C695" t="n">
-        <v>0.345382</v>
+        <v>0.568421</v>
       </c>
     </row>
     <row r="696">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.038714</v>
+        <v>0.040369</v>
       </c>
       <c r="C696" t="n">
-        <v>0.341365</v>
+        <v>0.564912</v>
       </c>
     </row>
     <row r="697">
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.03899</v>
+        <v>0.040411</v>
       </c>
       <c r="C697" t="n">
-        <v>0.337349</v>
+        <v>0.561404</v>
       </c>
     </row>
     <row r="698">
@@ -9488,10 +9488,10 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.039065</v>
+        <v>0.040966</v>
       </c>
       <c r="C698" t="n">
-        <v>0.333333</v>
+        <v>0.557895</v>
       </c>
     </row>
     <row r="699">
@@ -9501,10 +9501,10 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.039169</v>
+        <v>0.041062</v>
       </c>
       <c r="C699" t="n">
-        <v>0.329317</v>
+        <v>0.554386</v>
       </c>
     </row>
     <row r="700">
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.039785</v>
+        <v>0.041518</v>
       </c>
       <c r="C700" t="n">
-        <v>0.325301</v>
+        <v>0.550877</v>
       </c>
     </row>
     <row r="701">
@@ -9527,10 +9527,10 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.039804</v>
+        <v>0.041572</v>
       </c>
       <c r="C701" t="n">
-        <v>0.321285</v>
+        <v>0.547368</v>
       </c>
     </row>
     <row r="702">
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.039871</v>
+        <v>0.041672</v>
       </c>
       <c r="C702" t="n">
-        <v>0.317269</v>
+        <v>0.54386</v>
       </c>
     </row>
     <row r="703">
@@ -9553,10 +9553,10 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.041009</v>
+        <v>0.041706</v>
       </c>
       <c r="C703" t="n">
-        <v>0.313253</v>
+        <v>0.540351</v>
       </c>
     </row>
     <row r="704">
@@ -9566,10 +9566,10 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.041599</v>
+        <v>0.041719</v>
       </c>
       <c r="C704" t="n">
-        <v>0.309237</v>
+        <v>0.536842</v>
       </c>
     </row>
     <row r="705">
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.042098</v>
+        <v>0.041981</v>
       </c>
       <c r="C705" t="n">
-        <v>0.305221</v>
+        <v>0.5333329999999999</v>
       </c>
     </row>
     <row r="706">
@@ -9592,10 +9592,10 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.04216</v>
+        <v>0.041998</v>
       </c>
       <c r="C706" t="n">
-        <v>0.301205</v>
+        <v>0.529825</v>
       </c>
     </row>
     <row r="707">
@@ -9605,10 +9605,10 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.042463</v>
+        <v>0.043166</v>
       </c>
       <c r="C707" t="n">
-        <v>0.297189</v>
+        <v>0.526316</v>
       </c>
     </row>
     <row r="708">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.044151</v>
+        <v>0.04317</v>
       </c>
       <c r="C708" t="n">
-        <v>0.293173</v>
+        <v>0.522807</v>
       </c>
     </row>
     <row r="709">
@@ -9631,10 +9631,10 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.044173</v>
+        <v>0.043922</v>
       </c>
       <c r="C709" t="n">
-        <v>0.289157</v>
+        <v>0.519298</v>
       </c>
     </row>
     <row r="710">
@@ -9644,10 +9644,10 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.044266</v>
+        <v>0.044141</v>
       </c>
       <c r="C710" t="n">
-        <v>0.285141</v>
+        <v>0.5157890000000001</v>
       </c>
     </row>
     <row r="711">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.044391</v>
+        <v>0.044241</v>
       </c>
       <c r="C711" t="n">
-        <v>0.281124</v>
+        <v>0.512281</v>
       </c>
     </row>
     <row r="712">
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.045406</v>
+        <v>0.044581</v>
       </c>
       <c r="C712" t="n">
-        <v>0.277108</v>
+        <v>0.508772</v>
       </c>
     </row>
     <row r="713">
@@ -9683,10 +9683,10 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.045657</v>
+        <v>0.045171</v>
       </c>
       <c r="C713" t="n">
-        <v>0.273092</v>
+        <v>0.505263</v>
       </c>
     </row>
     <row r="714">
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.045979</v>
+        <v>0.045507</v>
       </c>
       <c r="C714" t="n">
-        <v>0.269076</v>
+        <v>0.501754</v>
       </c>
     </row>
     <row r="715">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.047484</v>
+        <v>0.046032</v>
       </c>
       <c r="C715" t="n">
-        <v>0.26506</v>
+        <v>0.498246</v>
       </c>
     </row>
     <row r="716">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.048606</v>
+        <v>0.046117</v>
       </c>
       <c r="C716" t="n">
-        <v>0.261044</v>
+        <v>0.494737</v>
       </c>
     </row>
     <row r="717">
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.048925</v>
+        <v>0.046458</v>
       </c>
       <c r="C717" t="n">
-        <v>0.257028</v>
+        <v>0.491228</v>
       </c>
     </row>
     <row r="718">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.04895</v>
+        <v>0.046628</v>
       </c>
       <c r="C718" t="n">
-        <v>0.253012</v>
+        <v>0.487719</v>
       </c>
     </row>
     <row r="719">
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.048967</v>
+        <v>0.047062</v>
       </c>
       <c r="C719" t="n">
-        <v>0.248996</v>
+        <v>0.484211</v>
       </c>
     </row>
     <row r="720">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.049776</v>
+        <v>0.047973</v>
       </c>
       <c r="C720" t="n">
-        <v>0.24498</v>
+        <v>0.480702</v>
       </c>
     </row>
     <row r="721">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.05023</v>
+        <v>0.048098</v>
       </c>
       <c r="C721" t="n">
-        <v>0.240964</v>
+        <v>0.477193</v>
       </c>
     </row>
     <row r="722">
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.051482</v>
+        <v>0.048257</v>
       </c>
       <c r="C722" t="n">
-        <v>0.236948</v>
+        <v>0.473684</v>
       </c>
     </row>
     <row r="723">
@@ -9813,10 +9813,10 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.052844</v>
+        <v>0.048698</v>
       </c>
       <c r="C723" t="n">
-        <v>0.232932</v>
+        <v>0.470175</v>
       </c>
     </row>
     <row r="724">
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.05306</v>
+        <v>0.04912</v>
       </c>
       <c r="C724" t="n">
-        <v>0.228916</v>
+        <v>0.466667</v>
       </c>
     </row>
     <row r="725">
@@ -9839,10 +9839,10 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.053383</v>
+        <v>0.049338</v>
       </c>
       <c r="C725" t="n">
-        <v>0.2249</v>
+        <v>0.463158</v>
       </c>
     </row>
     <row r="726">
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.053454</v>
+        <v>0.049732</v>
       </c>
       <c r="C726" t="n">
-        <v>0.220884</v>
+        <v>0.459649</v>
       </c>
     </row>
     <row r="727">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.054234</v>
+        <v>0.049752</v>
       </c>
       <c r="C727" t="n">
-        <v>0.216867</v>
+        <v>0.45614</v>
       </c>
     </row>
     <row r="728">
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.05585</v>
+        <v>0.050294</v>
       </c>
       <c r="C728" t="n">
-        <v>0.212851</v>
+        <v>0.452632</v>
       </c>
     </row>
     <row r="729">
@@ -9891,10 +9891,10 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.05665</v>
+        <v>0.050666</v>
       </c>
       <c r="C729" t="n">
-        <v>0.208835</v>
+        <v>0.449123</v>
       </c>
     </row>
     <row r="730">
@@ -9904,10 +9904,10 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.056676</v>
+        <v>0.050755</v>
       </c>
       <c r="C730" t="n">
-        <v>0.204819</v>
+        <v>0.445614</v>
       </c>
     </row>
     <row r="731">
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.057916</v>
+        <v>0.050789</v>
       </c>
       <c r="C731" t="n">
-        <v>0.200803</v>
+        <v>0.442105</v>
       </c>
     </row>
     <row r="732">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.058528</v>
+        <v>0.05118</v>
       </c>
       <c r="C732" t="n">
-        <v>0.196787</v>
+        <v>0.438596</v>
       </c>
     </row>
     <row r="733">
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.058708</v>
+        <v>0.051607</v>
       </c>
       <c r="C733" t="n">
-        <v>0.192771</v>
+        <v>0.435088</v>
       </c>
     </row>
     <row r="734">
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.059462</v>
+        <v>0.051764</v>
       </c>
       <c r="C734" t="n">
-        <v>0.188755</v>
+        <v>0.431579</v>
       </c>
     </row>
     <row r="735">
@@ -9969,10 +9969,10 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.060848</v>
+        <v>0.052001</v>
       </c>
       <c r="C735" t="n">
-        <v>0.184739</v>
+        <v>0.42807</v>
       </c>
     </row>
     <row r="736">
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.061981</v>
+        <v>0.052315</v>
       </c>
       <c r="C736" t="n">
-        <v>0.180723</v>
+        <v>0.424561</v>
       </c>
     </row>
     <row r="737">
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.062293</v>
+        <v>0.053462</v>
       </c>
       <c r="C737" t="n">
-        <v>0.176707</v>
+        <v>0.421053</v>
       </c>
     </row>
     <row r="738">
@@ -10008,10 +10008,10 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.06237</v>
+        <v>0.056411</v>
       </c>
       <c r="C738" t="n">
-        <v>0.172691</v>
+        <v>0.417544</v>
       </c>
     </row>
     <row r="739">
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.062976</v>
+        <v>0.056792</v>
       </c>
       <c r="C739" t="n">
-        <v>0.168675</v>
+        <v>0.414035</v>
       </c>
     </row>
     <row r="740">
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.06328</v>
+        <v>0.057817</v>
       </c>
       <c r="C740" t="n">
-        <v>0.164659</v>
+        <v>0.410526</v>
       </c>
     </row>
     <row r="741">
@@ -10047,10 +10047,10 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.06376999999999999</v>
+        <v>0.058325</v>
       </c>
       <c r="C741" t="n">
-        <v>0.160643</v>
+        <v>0.407018</v>
       </c>
     </row>
     <row r="742">
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.064015</v>
+        <v>0.058695</v>
       </c>
       <c r="C742" t="n">
-        <v>0.156627</v>
+        <v>0.403509</v>
       </c>
     </row>
     <row r="743">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.064793</v>
+        <v>0.059187</v>
       </c>
       <c r="C743" t="n">
-        <v>0.15261</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="744">
@@ -10086,10 +10086,10 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.06579500000000001</v>
+        <v>0.059331</v>
       </c>
       <c r="C744" t="n">
-        <v>0.148594</v>
+        <v>0.396491</v>
       </c>
     </row>
     <row r="745">
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.06751600000000001</v>
+        <v>0.05979</v>
       </c>
       <c r="C745" t="n">
-        <v>0.144578</v>
+        <v>0.392982</v>
       </c>
     </row>
     <row r="746">
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.067647</v>
+        <v>0.060013</v>
       </c>
       <c r="C746" t="n">
-        <v>0.140562</v>
+        <v>0.389474</v>
       </c>
     </row>
     <row r="747">
@@ -10125,10 +10125,10 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.06846099999999999</v>
+        <v>0.060348</v>
       </c>
       <c r="C747" t="n">
-        <v>0.136546</v>
+        <v>0.385965</v>
       </c>
     </row>
     <row r="748">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.07009700000000001</v>
+        <v>0.060631</v>
       </c>
       <c r="C748" t="n">
-        <v>0.13253</v>
+        <v>0.382456</v>
       </c>
     </row>
     <row r="749">
@@ -10151,10 +10151,10 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.072502</v>
+        <v>0.061006</v>
       </c>
       <c r="C749" t="n">
-        <v>0.128514</v>
+        <v>0.378947</v>
       </c>
     </row>
     <row r="750">
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.073514</v>
+        <v>0.061083</v>
       </c>
       <c r="C750" t="n">
-        <v>0.124498</v>
+        <v>0.375439</v>
       </c>
     </row>
     <row r="751">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.076013</v>
+        <v>0.061189</v>
       </c>
       <c r="C751" t="n">
-        <v>0.120482</v>
+        <v>0.37193</v>
       </c>
     </row>
     <row r="752">
@@ -10190,10 +10190,10 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.078112</v>
+        <v>0.061637</v>
       </c>
       <c r="C752" t="n">
-        <v>0.116466</v>
+        <v>0.368421</v>
       </c>
     </row>
     <row r="753">
@@ -10203,10 +10203,10 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.079748</v>
+        <v>0.062053</v>
       </c>
       <c r="C753" t="n">
-        <v>0.11245</v>
+        <v>0.364912</v>
       </c>
     </row>
     <row r="754">
@@ -10216,10 +10216,10 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.086088</v>
+        <v>0.063892</v>
       </c>
       <c r="C754" t="n">
-        <v>0.108434</v>
+        <v>0.361404</v>
       </c>
     </row>
     <row r="755">
@@ -10229,10 +10229,10 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.088157</v>
+        <v>0.064322</v>
       </c>
       <c r="C755" t="n">
-        <v>0.104418</v>
+        <v>0.357895</v>
       </c>
     </row>
     <row r="756">
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.08956699999999999</v>
+        <v>0.064378</v>
       </c>
       <c r="C756" t="n">
-        <v>0.100402</v>
+        <v>0.354386</v>
       </c>
     </row>
     <row r="757">
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.09303599999999999</v>
+        <v>0.065635</v>
       </c>
       <c r="C757" t="n">
-        <v>0.096386</v>
+        <v>0.350877</v>
       </c>
     </row>
     <row r="758">
@@ -10268,10 +10268,10 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.094985</v>
+        <v>0.06615799999999999</v>
       </c>
       <c r="C758" t="n">
-        <v>0.09236900000000001</v>
+        <v>0.347368</v>
       </c>
     </row>
     <row r="759">
@@ -10281,10 +10281,10 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.097107</v>
+        <v>0.06619</v>
       </c>
       <c r="C759" t="n">
-        <v>0.088353</v>
+        <v>0.34386</v>
       </c>
     </row>
     <row r="760">
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.097742</v>
+        <v>0.066942</v>
       </c>
       <c r="C760" t="n">
-        <v>0.084337</v>
+        <v>0.340351</v>
       </c>
     </row>
     <row r="761">
@@ -10307,10 +10307,10 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.105341</v>
+        <v>0.067576</v>
       </c>
       <c r="C761" t="n">
-        <v>0.080321</v>
+        <v>0.336842</v>
       </c>
     </row>
     <row r="762">
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.109044</v>
+        <v>0.067578</v>
       </c>
       <c r="C762" t="n">
-        <v>0.076305</v>
+        <v>0.333333</v>
       </c>
     </row>
     <row r="763">
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.109588</v>
+        <v>0.068787</v>
       </c>
       <c r="C763" t="n">
-        <v>0.07228900000000001</v>
+        <v>0.329825</v>
       </c>
     </row>
     <row r="764">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.110202</v>
+        <v>0.06908499999999999</v>
       </c>
       <c r="C764" t="n">
-        <v>0.068273</v>
+        <v>0.326316</v>
       </c>
     </row>
     <row r="765">
@@ -10359,10 +10359,10 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.112577</v>
+        <v>0.06932199999999999</v>
       </c>
       <c r="C765" t="n">
-        <v>0.06425699999999999</v>
+        <v>0.322807</v>
       </c>
     </row>
     <row r="766">
@@ -10372,10 +10372,10 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.117432</v>
+        <v>0.070322</v>
       </c>
       <c r="C766" t="n">
-        <v>0.060241</v>
+        <v>0.319298</v>
       </c>
     </row>
     <row r="767">
@@ -10385,10 +10385,10 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.12429</v>
+        <v>0.07051200000000001</v>
       </c>
       <c r="C767" t="n">
-        <v>0.056225</v>
+        <v>0.315789</v>
       </c>
     </row>
     <row r="768">
@@ -10398,10 +10398,10 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.139334</v>
+        <v>0.07052600000000001</v>
       </c>
       <c r="C768" t="n">
-        <v>0.052209</v>
+        <v>0.312281</v>
       </c>
     </row>
     <row r="769">
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.142558</v>
+        <v>0.070677</v>
       </c>
       <c r="C769" t="n">
-        <v>0.048193</v>
+        <v>0.308772</v>
       </c>
     </row>
     <row r="770">
@@ -10424,10 +10424,10 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.146697</v>
+        <v>0.07098500000000001</v>
       </c>
       <c r="C770" t="n">
-        <v>0.044177</v>
+        <v>0.305263</v>
       </c>
     </row>
     <row r="771">
@@ -10437,10 +10437,10 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.148531</v>
+        <v>0.071005</v>
       </c>
       <c r="C771" t="n">
-        <v>0.040161</v>
+        <v>0.301754</v>
       </c>
     </row>
     <row r="772">
@@ -10450,10 +10450,10 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.150934</v>
+        <v>0.07122100000000001</v>
       </c>
       <c r="C772" t="n">
-        <v>0.036145</v>
+        <v>0.298246</v>
       </c>
     </row>
     <row r="773">
@@ -10463,10 +10463,10 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.153026</v>
+        <v>0.071418</v>
       </c>
       <c r="C773" t="n">
-        <v>0.032129</v>
+        <v>0.294737</v>
       </c>
     </row>
     <row r="774">
@@ -10476,10 +10476,10 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.173811</v>
+        <v>0.071488</v>
       </c>
       <c r="C774" t="n">
-        <v>0.028112</v>
+        <v>0.291228</v>
       </c>
     </row>
     <row r="775">
@@ -10489,10 +10489,10 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.179284</v>
+        <v>0.0718</v>
       </c>
       <c r="C775" t="n">
-        <v>0.024096</v>
+        <v>0.287719</v>
       </c>
     </row>
     <row r="776">
@@ -10502,10 +10502,10 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.220725</v>
+        <v>0.072379</v>
       </c>
       <c r="C776" t="n">
-        <v>0.02008</v>
+        <v>0.284211</v>
       </c>
     </row>
     <row r="777">
@@ -10515,10 +10515,10 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.281018</v>
+        <v>0.07272099999999999</v>
       </c>
       <c r="C777" t="n">
-        <v>0.016064</v>
+        <v>0.280702</v>
       </c>
     </row>
     <row r="778">
@@ -10528,10 +10528,10 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.321817</v>
+        <v>0.07281</v>
       </c>
       <c r="C778" t="n">
-        <v>0.012048</v>
+        <v>0.277193</v>
       </c>
     </row>
     <row r="779">
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.354039</v>
+        <v>0.07338600000000001</v>
       </c>
       <c r="C779" t="n">
-        <v>0.008031999999999999</v>
+        <v>0.273684</v>
       </c>
     </row>
     <row r="780">
@@ -10554,10 +10554,998 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.520578</v>
+        <v>0.073932</v>
       </c>
       <c r="C780" t="n">
-        <v>0.004016</v>
+        <v>0.270175</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B781" t="n">
+        <v>0.077901</v>
+      </c>
+      <c r="C781" t="n">
+        <v>0.266667</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B782" t="n">
+        <v>0.07801900000000001</v>
+      </c>
+      <c r="C782" t="n">
+        <v>0.263158</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B783" t="n">
+        <v>0.079314</v>
+      </c>
+      <c r="C783" t="n">
+        <v>0.259649</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B784" t="n">
+        <v>0.079777</v>
+      </c>
+      <c r="C784" t="n">
+        <v>0.25614</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B785" t="n">
+        <v>0.081527</v>
+      </c>
+      <c r="C785" t="n">
+        <v>0.252632</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B786" t="n">
+        <v>0.08204400000000001</v>
+      </c>
+      <c r="C786" t="n">
+        <v>0.249123</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B787" t="n">
+        <v>0.082374</v>
+      </c>
+      <c r="C787" t="n">
+        <v>0.245614</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B788" t="n">
+        <v>0.08261499999999999</v>
+      </c>
+      <c r="C788" t="n">
+        <v>0.242105</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B789" t="n">
+        <v>0.083041</v>
+      </c>
+      <c r="C789" t="n">
+        <v>0.238596</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B790" t="n">
+        <v>0.083339</v>
+      </c>
+      <c r="C790" t="n">
+        <v>0.235088</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B791" t="n">
+        <v>0.08491899999999999</v>
+      </c>
+      <c r="C791" t="n">
+        <v>0.231579</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>0.085797</v>
+      </c>
+      <c r="C792" t="n">
+        <v>0.22807</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B793" t="n">
+        <v>0.088114</v>
+      </c>
+      <c r="C793" t="n">
+        <v>0.224561</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B794" t="n">
+        <v>0.08845799999999999</v>
+      </c>
+      <c r="C794" t="n">
+        <v>0.221053</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B795" t="n">
+        <v>0.08862100000000001</v>
+      </c>
+      <c r="C795" t="n">
+        <v>0.217544</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B796" t="n">
+        <v>0.088813</v>
+      </c>
+      <c r="C796" t="n">
+        <v>0.214035</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B797" t="n">
+        <v>0.09148299999999999</v>
+      </c>
+      <c r="C797" t="n">
+        <v>0.210526</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B798" t="n">
+        <v>0.091712</v>
+      </c>
+      <c r="C798" t="n">
+        <v>0.207018</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B799" t="n">
+        <v>0.09267599999999999</v>
+      </c>
+      <c r="C799" t="n">
+        <v>0.203509</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B800" t="n">
+        <v>0.09284199999999999</v>
+      </c>
+      <c r="C800" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B801" t="n">
+        <v>0.09343899999999999</v>
+      </c>
+      <c r="C801" t="n">
+        <v>0.196491</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B802" t="n">
+        <v>0.095429</v>
+      </c>
+      <c r="C802" t="n">
+        <v>0.192982</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B803" t="n">
+        <v>0.096276</v>
+      </c>
+      <c r="C803" t="n">
+        <v>0.189474</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B804" t="n">
+        <v>0.098773</v>
+      </c>
+      <c r="C804" t="n">
+        <v>0.185965</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B805" t="n">
+        <v>0.099407</v>
+      </c>
+      <c r="C805" t="n">
+        <v>0.182456</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B806" t="n">
+        <v>0.099714</v>
+      </c>
+      <c r="C806" t="n">
+        <v>0.178947</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B807" t="n">
+        <v>0.102482</v>
+      </c>
+      <c r="C807" t="n">
+        <v>0.175439</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B808" t="n">
+        <v>0.104156</v>
+      </c>
+      <c r="C808" t="n">
+        <v>0.17193</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B809" t="n">
+        <v>0.105221</v>
+      </c>
+      <c r="C809" t="n">
+        <v>0.168421</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B810" t="n">
+        <v>0.107647</v>
+      </c>
+      <c r="C810" t="n">
+        <v>0.164912</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B811" t="n">
+        <v>0.11135</v>
+      </c>
+      <c r="C811" t="n">
+        <v>0.161404</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B812" t="n">
+        <v>0.114467</v>
+      </c>
+      <c r="C812" t="n">
+        <v>0.157895</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B813" t="n">
+        <v>0.116468</v>
+      </c>
+      <c r="C813" t="n">
+        <v>0.154386</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B814" t="n">
+        <v>0.116954</v>
+      </c>
+      <c r="C814" t="n">
+        <v>0.150877</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B815" t="n">
+        <v>0.119674</v>
+      </c>
+      <c r="C815" t="n">
+        <v>0.147368</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B816" t="n">
+        <v>0.11989</v>
+      </c>
+      <c r="C816" t="n">
+        <v>0.14386</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B817" t="n">
+        <v>0.120121</v>
+      </c>
+      <c r="C817" t="n">
+        <v>0.140351</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B818" t="n">
+        <v>0.120397</v>
+      </c>
+      <c r="C818" t="n">
+        <v>0.136842</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B819" t="n">
+        <v>0.120671</v>
+      </c>
+      <c r="C819" t="n">
+        <v>0.133333</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B820" t="n">
+        <v>0.123725</v>
+      </c>
+      <c r="C820" t="n">
+        <v>0.129825</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B821" t="n">
+        <v>0.129178</v>
+      </c>
+      <c r="C821" t="n">
+        <v>0.126316</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B822" t="n">
+        <v>0.129973</v>
+      </c>
+      <c r="C822" t="n">
+        <v>0.122807</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B823" t="n">
+        <v>0.130881</v>
+      </c>
+      <c r="C823" t="n">
+        <v>0.119298</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B824" t="n">
+        <v>0.13106</v>
+      </c>
+      <c r="C824" t="n">
+        <v>0.115789</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B825" t="n">
+        <v>0.132913</v>
+      </c>
+      <c r="C825" t="n">
+        <v>0.112281</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B826" t="n">
+        <v>0.133947</v>
+      </c>
+      <c r="C826" t="n">
+        <v>0.108772</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B827" t="n">
+        <v>0.135054</v>
+      </c>
+      <c r="C827" t="n">
+        <v>0.105263</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B828" t="n">
+        <v>0.135826</v>
+      </c>
+      <c r="C828" t="n">
+        <v>0.101754</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B829" t="n">
+        <v>0.138934</v>
+      </c>
+      <c r="C829" t="n">
+        <v>0.098246</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B830" t="n">
+        <v>0.145226</v>
+      </c>
+      <c r="C830" t="n">
+        <v>0.094737</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B831" t="n">
+        <v>0.148376</v>
+      </c>
+      <c r="C831" t="n">
+        <v>0.091228</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B832" t="n">
+        <v>0.149564</v>
+      </c>
+      <c r="C832" t="n">
+        <v>0.08771900000000001</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B833" t="n">
+        <v>0.15277</v>
+      </c>
+      <c r="C833" t="n">
+        <v>0.08421099999999999</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B834" t="n">
+        <v>0.154739</v>
+      </c>
+      <c r="C834" t="n">
+        <v>0.080702</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B835" t="n">
+        <v>0.157185</v>
+      </c>
+      <c r="C835" t="n">
+        <v>0.077193</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B836" t="n">
+        <v>0.17296</v>
+      </c>
+      <c r="C836" t="n">
+        <v>0.073684</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B837" t="n">
+        <v>0.174888</v>
+      </c>
+      <c r="C837" t="n">
+        <v>0.070175</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>0.177038</v>
+      </c>
+      <c r="C838" t="n">
+        <v>0.066667</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>0.177101</v>
+      </c>
+      <c r="C839" t="n">
+        <v>0.06315800000000001</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>0.177957</v>
+      </c>
+      <c r="C840" t="n">
+        <v>0.059649</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>0.184125</v>
+      </c>
+      <c r="C841" t="n">
+        <v>0.05614</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>0.199754</v>
+      </c>
+      <c r="C842" t="n">
+        <v>0.052632</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>0.213575</v>
+      </c>
+      <c r="C843" t="n">
+        <v>0.049123</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>0.238671</v>
+      </c>
+      <c r="C844" t="n">
+        <v>0.045614</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>0.240463</v>
+      </c>
+      <c r="C845" t="n">
+        <v>0.042105</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>0.259969</v>
+      </c>
+      <c r="C846" t="n">
+        <v>0.038596</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>0.293388</v>
+      </c>
+      <c r="C847" t="n">
+        <v>0.035088</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>0.310629</v>
+      </c>
+      <c r="C848" t="n">
+        <v>0.031579</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>0.329245</v>
+      </c>
+      <c r="C849" t="n">
+        <v>0.02807</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>0.355835</v>
+      </c>
+      <c r="C850" t="n">
+        <v>0.024561</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="C851" t="n">
+        <v>0.021053</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>0.402404</v>
+      </c>
+      <c r="C852" t="n">
+        <v>0.017544</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>0.524787</v>
+      </c>
+      <c r="C853" t="n">
+        <v>0.014035</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>0.668428</v>
+      </c>
+      <c r="C854" t="n">
+        <v>0.010526</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>0.9386060000000001</v>
+      </c>
+      <c r="C855" t="n">
+        <v>0.007018</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Adjusted new profile</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>0.948939</v>
+      </c>
+      <c r="C856" t="n">
+        <v>0.003509</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>9.7e-05</v>
+        <v>9.8e-05</v>
       </c>
       <c r="C456" t="n">
         <v>0.997792</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.0004</v>
+        <v>0.000377</v>
       </c>
       <c r="C457" t="n">
         <v>0.9955850000000001</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.000434</v>
+        <v>0.000432</v>
       </c>
       <c r="C458" t="n">
         <v>0.993377</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.000456</v>
+        <v>0.000455</v>
       </c>
       <c r="C459" t="n">
         <v>0.99117</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.000867</v>
+        <v>0.000852</v>
       </c>
       <c r="C460" t="n">
         <v>0.988962</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.000933</v>
+        <v>0.000938</v>
       </c>
       <c r="C461" t="n">
         <v>0.986755</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.00144</v>
+        <v>0.001422</v>
       </c>
       <c r="C462" t="n">
         <v>0.9845469999999999</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.001674</v>
+        <v>0.001665</v>
       </c>
       <c r="C463" t="n">
         <v>0.98234</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.00176</v>
+        <v>0.001768</v>
       </c>
       <c r="C464" t="n">
         <v>0.980132</v>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.002094</v>
+        <v>0.002068</v>
       </c>
       <c r="C465" t="n">
         <v>0.977925</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.002212</v>
+        <v>0.002153</v>
       </c>
       <c r="C466" t="n">
         <v>0.9757169999999999</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.002385</v>
+        <v>0.002382</v>
       </c>
       <c r="C467" t="n">
         <v>0.97351</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.002478</v>
+        <v>0.002498</v>
       </c>
       <c r="C468" t="n">
         <v>0.971302</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.002694</v>
+        <v>0.002654</v>
       </c>
       <c r="C469" t="n">
         <v>0.969095</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.002846</v>
+        <v>0.002691</v>
       </c>
       <c r="C470" t="n">
         <v>0.9668870000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.003044</v>
+        <v>0.002991</v>
       </c>
       <c r="C471" t="n">
         <v>0.96468</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.003331</v>
+        <v>0.003269</v>
       </c>
       <c r="C472" t="n">
         <v>0.962472</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.003436</v>
+        <v>0.003407</v>
       </c>
       <c r="C473" t="n">
         <v>0.960265</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.003445</v>
+        <v>0.003428</v>
       </c>
       <c r="C474" t="n">
         <v>0.958057</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.003692</v>
+        <v>0.003683</v>
       </c>
       <c r="C475" t="n">
         <v>0.95585</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.003802</v>
+        <v>0.003786</v>
       </c>
       <c r="C476" t="n">
         <v>0.953642</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.003932</v>
+        <v>0.003923</v>
       </c>
       <c r="C477" t="n">
         <v>0.951435</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.003961</v>
+        <v>0.00393</v>
       </c>
       <c r="C478" t="n">
         <v>0.949227</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.004122</v>
+        <v>0.004016</v>
       </c>
       <c r="C479" t="n">
         <v>0.94702</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.004197</v>
+        <v>0.004036</v>
       </c>
       <c r="C480" t="n">
         <v>0.944812</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.004221</v>
+        <v>0.00405</v>
       </c>
       <c r="C481" t="n">
         <v>0.942605</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.004318</v>
+        <v>0.004115</v>
       </c>
       <c r="C482" t="n">
         <v>0.940397</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.004325</v>
+        <v>0.004207</v>
       </c>
       <c r="C483" t="n">
         <v>0.93819</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.004338</v>
+        <v>0.00425</v>
       </c>
       <c r="C484" t="n">
         <v>0.935982</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.004465</v>
+        <v>0.004281</v>
       </c>
       <c r="C485" t="n">
         <v>0.933775</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.004578</v>
+        <v>0.004545</v>
       </c>
       <c r="C486" t="n">
         <v>0.931567</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.004885</v>
+        <v>0.004679</v>
       </c>
       <c r="C487" t="n">
         <v>0.92936</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.00489</v>
+        <v>0.004958</v>
       </c>
       <c r="C488" t="n">
         <v>0.927152</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.004987</v>
+        <v>0.004964</v>
       </c>
       <c r="C489" t="n">
         <v>0.924945</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.005002</v>
+        <v>0.004992</v>
       </c>
       <c r="C490" t="n">
         <v>0.922737</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.0051</v>
+        <v>0.005009</v>
       </c>
       <c r="C491" t="n">
         <v>0.92053</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.005413</v>
+        <v>0.005084</v>
       </c>
       <c r="C492" t="n">
         <v>0.918322</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.006756</v>
+        <v>0.006259</v>
       </c>
       <c r="C493" t="n">
         <v>0.916115</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.00713</v>
+        <v>0.006718</v>
       </c>
       <c r="C494" t="n">
         <v>0.913907</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.007217</v>
+        <v>0.007032</v>
       </c>
       <c r="C495" t="n">
         <v>0.9117</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.007402</v>
+        <v>0.007179</v>
       </c>
       <c r="C496" t="n">
         <v>0.909492</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.007668</v>
+        <v>0.007392</v>
       </c>
       <c r="C497" t="n">
         <v>0.907285</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.007828999999999999</v>
+        <v>0.007845</v>
       </c>
       <c r="C498" t="n">
         <v>0.905077</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.008141000000000001</v>
+        <v>0.008041</v>
       </c>
       <c r="C499" t="n">
         <v>0.90287</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.008168999999999999</v>
+        <v>0.008047</v>
       </c>
       <c r="C500" t="n">
         <v>0.900662</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.008283</v>
+        <v>0.008215999999999999</v>
       </c>
       <c r="C501" t="n">
         <v>0.898455</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.008375</v>
+        <v>0.008236</v>
       </c>
       <c r="C502" t="n">
         <v>0.896247</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.008564</v>
+        <v>0.008312999999999999</v>
       </c>
       <c r="C503" t="n">
         <v>0.8940399999999999</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.008725</v>
+        <v>0.008354</v>
       </c>
       <c r="C504" t="n">
         <v>0.891832</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.008737999999999999</v>
+        <v>0.008599000000000001</v>
       </c>
       <c r="C505" t="n">
         <v>0.889625</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.008782999999999999</v>
+        <v>0.008687</v>
       </c>
       <c r="C506" t="n">
         <v>0.887417</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.008794</v>
+        <v>0.008732999999999999</v>
       </c>
       <c r="C507" t="n">
         <v>0.8852100000000001</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.009133</v>
+        <v>0.008775</v>
       </c>
       <c r="C508" t="n">
         <v>0.883002</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.009414</v>
+        <v>0.009171</v>
       </c>
       <c r="C509" t="n">
         <v>0.880795</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.009545</v>
+        <v>0.009441</v>
       </c>
       <c r="C510" t="n">
         <v>0.878587</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.009586000000000001</v>
+        <v>0.009540999999999999</v>
       </c>
       <c r="C511" t="n">
         <v>0.87638</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.009601999999999999</v>
+        <v>0.009557</v>
       </c>
       <c r="C512" t="n">
         <v>0.8741719999999999</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.009802</v>
+        <v>0.009644</v>
       </c>
       <c r="C513" t="n">
         <v>0.871965</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.009894</v>
+        <v>0.009802</v>
       </c>
       <c r="C514" t="n">
         <v>0.869757</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.009929</v>
+        <v>0.009998</v>
       </c>
       <c r="C515" t="n">
         <v>0.86755</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.010317</v>
+        <v>0.010132</v>
       </c>
       <c r="C516" t="n">
         <v>0.8653419999999999</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.010345</v>
+        <v>0.01036</v>
       </c>
       <c r="C517" t="n">
         <v>0.863135</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.01062</v>
+        <v>0.010374</v>
       </c>
       <c r="C518" t="n">
         <v>0.860927</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.010751</v>
+        <v>0.010538</v>
       </c>
       <c r="C519" t="n">
         <v>0.85872</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.010753</v>
+        <v>0.010655</v>
       </c>
       <c r="C520" t="n">
         <v>0.8565120000000001</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.011225</v>
+        <v>0.011139</v>
       </c>
       <c r="C521" t="n">
         <v>0.854305</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.011272</v>
+        <v>0.011178</v>
       </c>
       <c r="C522" t="n">
         <v>0.852097</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.011391</v>
+        <v>0.011231</v>
       </c>
       <c r="C523" t="n">
         <v>0.84989</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.011412</v>
+        <v>0.011272</v>
       </c>
       <c r="C524" t="n">
         <v>0.847682</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.011442</v>
+        <v>0.011409</v>
       </c>
       <c r="C525" t="n">
         <v>0.845475</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.01165</v>
+        <v>0.011712</v>
       </c>
       <c r="C526" t="n">
         <v>0.843267</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.012012</v>
+        <v>0.011986</v>
       </c>
       <c r="C527" t="n">
         <v>0.84106</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.012017</v>
+        <v>0.012073</v>
       </c>
       <c r="C528" t="n">
         <v>0.838852</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.012332</v>
+        <v>0.012151</v>
       </c>
       <c r="C529" t="n">
         <v>0.836645</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.012949</v>
+        <v>0.012822</v>
       </c>
       <c r="C530" t="n">
         <v>0.834437</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.013392</v>
+        <v>0.013135</v>
       </c>
       <c r="C531" t="n">
         <v>0.83223</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.013591</v>
+        <v>0.013224</v>
       </c>
       <c r="C532" t="n">
         <v>0.830022</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.0137</v>
+        <v>0.013265</v>
       </c>
       <c r="C533" t="n">
         <v>0.827815</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.013782</v>
+        <v>0.013609</v>
       </c>
       <c r="C534" t="n">
         <v>0.825607</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.013783</v>
+        <v>0.013663</v>
       </c>
       <c r="C535" t="n">
         <v>0.8234</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.013788</v>
+        <v>0.013674</v>
       </c>
       <c r="C536" t="n">
         <v>0.821192</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.013885</v>
+        <v>0.013689</v>
       </c>
       <c r="C537" t="n">
         <v>0.818985</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.013938</v>
+        <v>0.013775</v>
       </c>
       <c r="C538" t="n">
         <v>0.816777</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.01403</v>
+        <v>0.013889</v>
       </c>
       <c r="C539" t="n">
         <v>0.81457</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.014067</v>
+        <v>0.013999</v>
       </c>
       <c r="C540" t="n">
         <v>0.812362</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.014092</v>
+        <v>0.014024</v>
       </c>
       <c r="C541" t="n">
         <v>0.810155</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.014186</v>
+        <v>0.014046</v>
       </c>
       <c r="C542" t="n">
         <v>0.807947</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.014683</v>
+        <v>0.014154</v>
       </c>
       <c r="C543" t="n">
         <v>0.80574</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.014698</v>
+        <v>0.014194</v>
       </c>
       <c r="C544" t="n">
         <v>0.803532</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.014781</v>
+        <v>0.014582</v>
       </c>
       <c r="C545" t="n">
         <v>0.801325</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.014867</v>
+        <v>0.014651</v>
       </c>
       <c r="C546" t="n">
         <v>0.799117</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.015215</v>
+        <v>0.014998</v>
       </c>
       <c r="C547" t="n">
         <v>0.796909</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.015336</v>
+        <v>0.015205</v>
       </c>
       <c r="C548" t="n">
         <v>0.794702</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.015512</v>
+        <v>0.015318</v>
       </c>
       <c r="C549" t="n">
         <v>0.792494</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.016149</v>
+        <v>0.01558</v>
       </c>
       <c r="C550" t="n">
         <v>0.790287</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.016204</v>
+        <v>0.016034</v>
       </c>
       <c r="C551" t="n">
         <v>0.788079</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.01623</v>
+        <v>0.016087</v>
       </c>
       <c r="C552" t="n">
         <v>0.785872</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.016325</v>
+        <v>0.01626</v>
       </c>
       <c r="C553" t="n">
         <v>0.783664</v>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>0.016446</v>
+        <v>0.01643</v>
       </c>
       <c r="C554" t="n">
         <v>0.781457</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.016675</v>
+        <v>0.016432</v>
       </c>
       <c r="C555" t="n">
         <v>0.779249</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.016686</v>
+        <v>0.016605</v>
       </c>
       <c r="C556" t="n">
         <v>0.777042</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.016948</v>
+        <v>0.016637</v>
       </c>
       <c r="C557" t="n">
         <v>0.774834</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.017228</v>
+        <v>0.01685</v>
       </c>
       <c r="C558" t="n">
         <v>0.772627</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.017262</v>
+        <v>0.016949</v>
       </c>
       <c r="C559" t="n">
         <v>0.770419</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.017277</v>
+        <v>0.017089</v>
       </c>
       <c r="C560" t="n">
         <v>0.768212</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.017401</v>
+        <v>0.01731</v>
       </c>
       <c r="C561" t="n">
         <v>0.766004</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.017403</v>
+        <v>0.017338</v>
       </c>
       <c r="C562" t="n">
         <v>0.7637969999999999</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.017592</v>
+        <v>0.017343</v>
       </c>
       <c r="C563" t="n">
         <v>0.761589</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.018041</v>
+        <v>0.017518</v>
       </c>
       <c r="C564" t="n">
         <v>0.759382</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.018114</v>
+        <v>0.017561</v>
       </c>
       <c r="C565" t="n">
         <v>0.757174</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.018234</v>
+        <v>0.018114</v>
       </c>
       <c r="C566" t="n">
         <v>0.7549670000000001</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.018277</v>
+        <v>0.018147</v>
       </c>
       <c r="C567" t="n">
         <v>0.752759</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.01883</v>
+        <v>0.018456</v>
       </c>
       <c r="C568" t="n">
         <v>0.750552</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.019057</v>
+        <v>0.018877</v>
       </c>
       <c r="C569" t="n">
         <v>0.748344</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.019103</v>
+        <v>0.019003</v>
       </c>
       <c r="C570" t="n">
         <v>0.7461370000000001</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.019844</v>
+        <v>0.019925</v>
       </c>
       <c r="C571" t="n">
         <v>0.743929</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.020036</v>
+        <v>0.020085</v>
       </c>
       <c r="C572" t="n">
         <v>0.741722</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.020136</v>
+        <v>0.020185</v>
       </c>
       <c r="C573" t="n">
         <v>0.739514</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.021102</v>
+        <v>0.020193</v>
       </c>
       <c r="C574" t="n">
         <v>0.737307</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.021217</v>
+        <v>0.021191</v>
       </c>
       <c r="C575" t="n">
         <v>0.7350989999999999</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.021322</v>
+        <v>0.021524</v>
       </c>
       <c r="C576" t="n">
         <v>0.732892</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.021571</v>
+        <v>0.021546</v>
       </c>
       <c r="C577" t="n">
         <v>0.730684</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.021626</v>
+        <v>0.021587</v>
       </c>
       <c r="C578" t="n">
         <v>0.728477</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.021864</v>
+        <v>0.021924</v>
       </c>
       <c r="C579" t="n">
         <v>0.7262690000000001</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.021969</v>
+        <v>0.021941</v>
       </c>
       <c r="C580" t="n">
         <v>0.724062</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.022115</v>
+        <v>0.022049</v>
       </c>
       <c r="C581" t="n">
         <v>0.721854</v>
@@ -7980,7 +7980,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>0.022394</v>
+        <v>0.022385</v>
       </c>
       <c r="C582" t="n">
         <v>0.719647</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.022668</v>
+        <v>0.022411</v>
       </c>
       <c r="C583" t="n">
         <v>0.717439</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.02275</v>
+        <v>0.022814</v>
       </c>
       <c r="C584" t="n">
         <v>0.715232</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.022932</v>
+        <v>0.022952</v>
       </c>
       <c r="C585" t="n">
         <v>0.713024</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.024115</v>
+        <v>0.023069</v>
       </c>
       <c r="C586" t="n">
         <v>0.710817</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.024377</v>
+        <v>0.023345</v>
       </c>
       <c r="C587" t="n">
         <v>0.708609</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.024559</v>
+        <v>0.023505</v>
       </c>
       <c r="C588" t="n">
         <v>0.706402</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.024598</v>
+        <v>0.023758</v>
       </c>
       <c r="C589" t="n">
         <v>0.704194</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.024655</v>
+        <v>0.024017</v>
       </c>
       <c r="C590" t="n">
         <v>0.701987</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.025027</v>
+        <v>0.024378</v>
       </c>
       <c r="C591" t="n">
         <v>0.699779</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.025498</v>
+        <v>0.024402</v>
       </c>
       <c r="C592" t="n">
         <v>0.697572</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.025611</v>
+        <v>0.024454</v>
       </c>
       <c r="C593" t="n">
         <v>0.695364</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.025759</v>
+        <v>0.024645</v>
       </c>
       <c r="C594" t="n">
         <v>0.693157</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.025774</v>
+        <v>0.024645</v>
       </c>
       <c r="C595" t="n">
         <v>0.690949</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.026205</v>
+        <v>0.024773</v>
       </c>
       <c r="C596" t="n">
         <v>0.688742</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.026306</v>
+        <v>0.024967</v>
       </c>
       <c r="C597" t="n">
         <v>0.686534</v>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>0.026321</v>
+        <v>0.025214</v>
       </c>
       <c r="C598" t="n">
         <v>0.684327</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.02636</v>
+        <v>0.025691</v>
       </c>
       <c r="C599" t="n">
         <v>0.682119</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.026404</v>
+        <v>0.025776</v>
       </c>
       <c r="C600" t="n">
         <v>0.679912</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.026547</v>
+        <v>0.025861</v>
       </c>
       <c r="C601" t="n">
         <v>0.677704</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.026603</v>
+        <v>0.02613</v>
       </c>
       <c r="C602" t="n">
         <v>0.675497</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.026608</v>
+        <v>0.026196</v>
       </c>
       <c r="C603" t="n">
         <v>0.673289</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.026621</v>
+        <v>0.026196</v>
       </c>
       <c r="C604" t="n">
         <v>0.671082</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.027074</v>
+        <v>0.026616</v>
       </c>
       <c r="C605" t="n">
         <v>0.668874</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.027281</v>
+        <v>0.02684</v>
       </c>
       <c r="C606" t="n">
         <v>0.666667</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.027348</v>
+        <v>0.026867</v>
       </c>
       <c r="C607" t="n">
         <v>0.664459</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.027635</v>
+        <v>0.027311</v>
       </c>
       <c r="C608" t="n">
         <v>0.662252</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.027698</v>
+        <v>0.027351</v>
       </c>
       <c r="C609" t="n">
         <v>0.660044</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.027991</v>
+        <v>0.027598</v>
       </c>
       <c r="C610" t="n">
         <v>0.657837</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.028526</v>
+        <v>0.027984</v>
       </c>
       <c r="C611" t="n">
         <v>0.655629</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.028623</v>
+        <v>0.028045</v>
       </c>
       <c r="C612" t="n">
         <v>0.6534219999999999</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.028911</v>
+        <v>0.028051</v>
       </c>
       <c r="C613" t="n">
         <v>0.651214</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.029215</v>
+        <v>0.028465</v>
       </c>
       <c r="C614" t="n">
         <v>0.649007</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.029351</v>
+        <v>0.028524</v>
       </c>
       <c r="C615" t="n">
         <v>0.646799</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.02939</v>
+        <v>0.028577</v>
       </c>
       <c r="C616" t="n">
         <v>0.6445920000000001</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.029804</v>
+        <v>0.029249</v>
       </c>
       <c r="C617" t="n">
         <v>0.642384</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.029874</v>
+        <v>0.029285</v>
       </c>
       <c r="C618" t="n">
         <v>0.640177</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.030491</v>
+        <v>0.02957</v>
       </c>
       <c r="C619" t="n">
         <v>0.637969</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.030548</v>
+        <v>0.029672</v>
       </c>
       <c r="C620" t="n">
         <v>0.635762</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.031077</v>
+        <v>0.030401</v>
       </c>
       <c r="C621" t="n">
         <v>0.633554</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.031375</v>
+        <v>0.030411</v>
       </c>
       <c r="C622" t="n">
         <v>0.631347</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.03153</v>
+        <v>0.030618</v>
       </c>
       <c r="C623" t="n">
         <v>0.629139</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.031533</v>
+        <v>0.030686</v>
       </c>
       <c r="C624" t="n">
         <v>0.626932</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.031728</v>
+        <v>0.030811</v>
       </c>
       <c r="C625" t="n">
         <v>0.6247239999999999</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.031991</v>
+        <v>0.031087</v>
       </c>
       <c r="C626" t="n">
         <v>0.622517</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.032076</v>
+        <v>0.031364</v>
       </c>
       <c r="C627" t="n">
         <v>0.620309</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.032083</v>
+        <v>0.031531</v>
       </c>
       <c r="C628" t="n">
         <v>0.618102</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.03231</v>
+        <v>0.031904</v>
       </c>
       <c r="C629" t="n">
         <v>0.6158940000000001</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.032639</v>
+        <v>0.031914</v>
       </c>
       <c r="C630" t="n">
         <v>0.613687</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.032684</v>
+        <v>0.032094</v>
       </c>
       <c r="C631" t="n">
         <v>0.611479</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.03295</v>
+        <v>0.032298</v>
       </c>
       <c r="C632" t="n">
         <v>0.609272</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.033216</v>
+        <v>0.032347</v>
       </c>
       <c r="C633" t="n">
         <v>0.607064</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.033306</v>
+        <v>0.032717</v>
       </c>
       <c r="C634" t="n">
         <v>0.604857</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.033412</v>
+        <v>0.032759</v>
       </c>
       <c r="C635" t="n">
         <v>0.602649</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.033439</v>
+        <v>0.032862</v>
       </c>
       <c r="C636" t="n">
         <v>0.600442</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.033822</v>
+        <v>0.032898</v>
       </c>
       <c r="C637" t="n">
         <v>0.598234</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.034066</v>
+        <v>0.032944</v>
       </c>
       <c r="C638" t="n">
         <v>0.5960259999999999</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.034265</v>
+        <v>0.033193</v>
       </c>
       <c r="C639" t="n">
         <v>0.593819</v>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="B640" t="n">
-        <v>0.034446</v>
+        <v>0.03323</v>
       </c>
       <c r="C640" t="n">
         <v>0.591611</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.034504</v>
+        <v>0.033355</v>
       </c>
       <c r="C641" t="n">
         <v>0.589404</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.034755</v>
+        <v>0.033428</v>
       </c>
       <c r="C642" t="n">
         <v>0.5871960000000001</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.034792</v>
+        <v>0.033582</v>
       </c>
       <c r="C643" t="n">
         <v>0.584989</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.035148</v>
+        <v>0.034151</v>
       </c>
       <c r="C644" t="n">
         <v>0.582781</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.035554</v>
+        <v>0.034295</v>
       </c>
       <c r="C645" t="n">
         <v>0.580574</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.035614</v>
+        <v>0.034305</v>
       </c>
       <c r="C646" t="n">
         <v>0.578366</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.035819</v>
+        <v>0.034552</v>
       </c>
       <c r="C647" t="n">
         <v>0.576159</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.036003</v>
+        <v>0.034684</v>
       </c>
       <c r="C648" t="n">
         <v>0.573951</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.03604</v>
+        <v>0.034764</v>
       </c>
       <c r="C649" t="n">
         <v>0.571744</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.036049</v>
+        <v>0.035114</v>
       </c>
       <c r="C650" t="n">
         <v>0.569536</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.036117</v>
+        <v>0.035219</v>
       </c>
       <c r="C651" t="n">
         <v>0.567329</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.036947</v>
+        <v>0.03525</v>
       </c>
       <c r="C652" t="n">
         <v>0.565121</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.036949</v>
+        <v>0.035536</v>
       </c>
       <c r="C653" t="n">
         <v>0.562914</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.036959</v>
+        <v>0.035783</v>
       </c>
       <c r="C654" t="n">
         <v>0.560706</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.037135</v>
+        <v>0.035925</v>
       </c>
       <c r="C655" t="n">
         <v>0.558499</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.037572</v>
+        <v>0.036488</v>
       </c>
       <c r="C656" t="n">
         <v>0.556291</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.038247</v>
+        <v>0.036689</v>
       </c>
       <c r="C657" t="n">
         <v>0.554084</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.038501</v>
+        <v>0.036865</v>
       </c>
       <c r="C658" t="n">
         <v>0.551876</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.038519</v>
+        <v>0.036949</v>
       </c>
       <c r="C659" t="n">
         <v>0.549669</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.03876</v>
+        <v>0.03725</v>
       </c>
       <c r="C660" t="n">
         <v>0.547461</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.038802</v>
+        <v>0.037254</v>
       </c>
       <c r="C661" t="n">
         <v>0.545254</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.038886</v>
+        <v>0.037277</v>
       </c>
       <c r="C662" t="n">
         <v>0.543046</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.038888</v>
+        <v>0.03737</v>
       </c>
       <c r="C663" t="n">
         <v>0.540839</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.039561</v>
+        <v>0.037761</v>
       </c>
       <c r="C664" t="n">
         <v>0.538631</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.039578</v>
+        <v>0.038026</v>
       </c>
       <c r="C665" t="n">
         <v>0.536424</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.039639</v>
+        <v>0.038185</v>
       </c>
       <c r="C666" t="n">
         <v>0.534216</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.039679</v>
+        <v>0.038472</v>
       </c>
       <c r="C667" t="n">
         <v>0.532009</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.039844</v>
+        <v>0.038496</v>
       </c>
       <c r="C668" t="n">
         <v>0.529801</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.040059</v>
+        <v>0.039054</v>
       </c>
       <c r="C669" t="n">
         <v>0.527594</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.04012</v>
+        <v>0.039172</v>
       </c>
       <c r="C670" t="n">
         <v>0.525386</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.040302</v>
+        <v>0.039418</v>
       </c>
       <c r="C671" t="n">
         <v>0.5231789999999999</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.040887</v>
+        <v>0.039542</v>
       </c>
       <c r="C672" t="n">
         <v>0.520971</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.041002</v>
+        <v>0.040863</v>
       </c>
       <c r="C673" t="n">
         <v>0.518764</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.04157</v>
+        <v>0.041253</v>
       </c>
       <c r="C674" t="n">
         <v>0.516556</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.041644</v>
+        <v>0.041511</v>
       </c>
       <c r="C675" t="n">
         <v>0.5143489999999999</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.042329</v>
+        <v>0.041905</v>
       </c>
       <c r="C676" t="n">
         <v>0.512141</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.042953</v>
+        <v>0.042418</v>
       </c>
       <c r="C677" t="n">
         <v>0.509934</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.04322</v>
+        <v>0.042621</v>
       </c>
       <c r="C678" t="n">
         <v>0.507726</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.043363</v>
+        <v>0.042645</v>
       </c>
       <c r="C679" t="n">
         <v>0.5055190000000001</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.04339</v>
+        <v>0.042826</v>
       </c>
       <c r="C680" t="n">
         <v>0.503311</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.043602</v>
+        <v>0.042945</v>
       </c>
       <c r="C681" t="n">
         <v>0.501104</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.043613</v>
+        <v>0.043208</v>
       </c>
       <c r="C682" t="n">
         <v>0.498896</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.044139</v>
+        <v>0.043325</v>
       </c>
       <c r="C683" t="n">
         <v>0.496689</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.044301</v>
+        <v>0.043723</v>
       </c>
       <c r="C684" t="n">
         <v>0.494481</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.045217</v>
+        <v>0.044069</v>
       </c>
       <c r="C685" t="n">
         <v>0.492274</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.045402</v>
+        <v>0.044099</v>
       </c>
       <c r="C686" t="n">
         <v>0.490066</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.04635</v>
+        <v>0.044998</v>
       </c>
       <c r="C687" t="n">
         <v>0.487859</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.046384</v>
+        <v>0.04506</v>
       </c>
       <c r="C688" t="n">
         <v>0.485651</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.04639</v>
+        <v>0.045855</v>
       </c>
       <c r="C689" t="n">
         <v>0.483444</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.046436</v>
+        <v>0.046328</v>
       </c>
       <c r="C690" t="n">
         <v>0.481236</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.046762</v>
+        <v>0.046447</v>
       </c>
       <c r="C691" t="n">
         <v>0.479029</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.047134</v>
+        <v>0.046586</v>
       </c>
       <c r="C692" t="n">
         <v>0.476821</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.047719</v>
+        <v>0.046775</v>
       </c>
       <c r="C693" t="n">
         <v>0.474614</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.047866</v>
+        <v>0.046799</v>
       </c>
       <c r="C694" t="n">
         <v>0.472406</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.048041</v>
+        <v>0.047712</v>
       </c>
       <c r="C695" t="n">
         <v>0.470199</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.048274</v>
+        <v>0.047891</v>
       </c>
       <c r="C696" t="n">
         <v>0.467991</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.049258</v>
+        <v>0.048214</v>
       </c>
       <c r="C697" t="n">
         <v>0.465784</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.049305</v>
+        <v>0.048256</v>
       </c>
       <c r="C698" t="n">
         <v>0.463576</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.049883</v>
+        <v>0.048686</v>
       </c>
       <c r="C699" t="n">
         <v>0.461369</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.049972</v>
+        <v>0.04925</v>
       </c>
       <c r="C700" t="n">
         <v>0.459161</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.05015</v>
+        <v>0.049634</v>
       </c>
       <c r="C701" t="n">
         <v>0.456954</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.052143</v>
+        <v>0.049958</v>
       </c>
       <c r="C702" t="n">
         <v>0.454746</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.052368</v>
+        <v>0.050122</v>
       </c>
       <c r="C703" t="n">
         <v>0.452539</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.052689</v>
+        <v>0.050332</v>
       </c>
       <c r="C704" t="n">
         <v>0.450331</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.05273</v>
+        <v>0.05168</v>
       </c>
       <c r="C705" t="n">
         <v>0.448124</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.052986</v>
+        <v>0.051884</v>
       </c>
       <c r="C706" t="n">
         <v>0.445916</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.053311</v>
+        <v>0.052311</v>
       </c>
       <c r="C707" t="n">
         <v>0.443709</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.053467</v>
+        <v>0.052565</v>
       </c>
       <c r="C708" t="n">
         <v>0.441501</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.053731</v>
+        <v>0.052943</v>
       </c>
       <c r="C709" t="n">
         <v>0.439294</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.054537</v>
+        <v>0.05295</v>
       </c>
       <c r="C710" t="n">
         <v>0.437086</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.054627</v>
+        <v>0.053161</v>
       </c>
       <c r="C711" t="n">
         <v>0.434879</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.054776</v>
+        <v>0.05319</v>
       </c>
       <c r="C712" t="n">
         <v>0.432671</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.054966</v>
+        <v>0.053343</v>
       </c>
       <c r="C713" t="n">
         <v>0.430464</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.055444</v>
+        <v>0.053733</v>
       </c>
       <c r="C714" t="n">
         <v>0.428256</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.055476</v>
+        <v>0.054542</v>
       </c>
       <c r="C715" t="n">
         <v>0.426049</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.055683</v>
+        <v>0.054552</v>
       </c>
       <c r="C716" t="n">
         <v>0.423841</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.055836</v>
+        <v>0.055416</v>
       </c>
       <c r="C717" t="n">
         <v>0.421634</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.056085</v>
+        <v>0.055678</v>
       </c>
       <c r="C718" t="n">
         <v>0.419426</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.056229</v>
+        <v>0.055924</v>
       </c>
       <c r="C719" t="n">
         <v>0.417219</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.056425</v>
+        <v>0.055931</v>
       </c>
       <c r="C720" t="n">
         <v>0.415011</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.056939</v>
+        <v>0.056027</v>
       </c>
       <c r="C721" t="n">
         <v>0.412804</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.057068</v>
+        <v>0.056088</v>
       </c>
       <c r="C722" t="n">
         <v>0.410596</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.057178</v>
+        <v>0.056454</v>
       </c>
       <c r="C723" t="n">
         <v>0.408389</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.058065</v>
+        <v>0.056477</v>
       </c>
       <c r="C724" t="n">
         <v>0.406181</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.059149</v>
+        <v>0.056744</v>
       </c>
       <c r="C725" t="n">
         <v>0.403974</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.059337</v>
+        <v>0.056758</v>
       </c>
       <c r="C726" t="n">
         <v>0.401766</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.059414</v>
+        <v>0.057033</v>
       </c>
       <c r="C727" t="n">
         <v>0.399558</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.059615</v>
+        <v>0.057233</v>
       </c>
       <c r="C728" t="n">
         <v>0.397351</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.059756</v>
+        <v>0.057307</v>
       </c>
       <c r="C729" t="n">
         <v>0.395143</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.059956</v>
+        <v>0.058541</v>
       </c>
       <c r="C730" t="n">
         <v>0.392936</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.060018</v>
+        <v>0.058728</v>
       </c>
       <c r="C731" t="n">
         <v>0.390728</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.06078</v>
+        <v>0.058876</v>
       </c>
       <c r="C732" t="n">
         <v>0.388521</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.060957</v>
+        <v>0.058903</v>
       </c>
       <c r="C733" t="n">
         <v>0.386313</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.060967</v>
+        <v>0.059096</v>
       </c>
       <c r="C734" t="n">
         <v>0.384106</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.061112</v>
+        <v>0.059569</v>
       </c>
       <c r="C735" t="n">
         <v>0.381898</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.061135</v>
+        <v>0.059628</v>
       </c>
       <c r="C736" t="n">
         <v>0.379691</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.061275</v>
+        <v>0.059771</v>
       </c>
       <c r="C737" t="n">
         <v>0.377483</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.061436</v>
+        <v>0.060133</v>
       </c>
       <c r="C738" t="n">
         <v>0.375276</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.061663</v>
+        <v>0.060744</v>
       </c>
       <c r="C739" t="n">
         <v>0.373068</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.061685</v>
+        <v>0.060949</v>
       </c>
       <c r="C740" t="n">
         <v>0.370861</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.062281</v>
+        <v>0.061071</v>
       </c>
       <c r="C741" t="n">
         <v>0.368653</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.062424</v>
+        <v>0.061186</v>
       </c>
       <c r="C742" t="n">
         <v>0.366446</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.06266099999999999</v>
+        <v>0.061229</v>
       </c>
       <c r="C743" t="n">
         <v>0.364238</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.062695</v>
+        <v>0.061331</v>
       </c>
       <c r="C744" t="n">
         <v>0.362031</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.06279800000000001</v>
+        <v>0.062151</v>
       </c>
       <c r="C745" t="n">
         <v>0.359823</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.062872</v>
+        <v>0.062387</v>
       </c>
       <c r="C746" t="n">
         <v>0.357616</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.063274</v>
+        <v>0.062779</v>
       </c>
       <c r="C747" t="n">
         <v>0.355408</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.06358999999999999</v>
+        <v>0.063023</v>
       </c>
       <c r="C748" t="n">
         <v>0.353201</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.064011</v>
+        <v>0.06303300000000001</v>
       </c>
       <c r="C749" t="n">
         <v>0.350993</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.064293</v>
+        <v>0.063126</v>
       </c>
       <c r="C750" t="n">
         <v>0.348786</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.06458899999999999</v>
+        <v>0.06313299999999999</v>
       </c>
       <c r="C751" t="n">
         <v>0.346578</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.06564</v>
+        <v>0.063391</v>
       </c>
       <c r="C752" t="n">
         <v>0.344371</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.06565500000000001</v>
+        <v>0.06400400000000001</v>
       </c>
       <c r="C753" t="n">
         <v>0.342163</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.06582300000000001</v>
+        <v>0.06419</v>
       </c>
       <c r="C754" t="n">
         <v>0.339956</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.065872</v>
+        <v>0.064287</v>
       </c>
       <c r="C755" t="n">
         <v>0.337748</v>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="B756" t="n">
-        <v>0.06590500000000001</v>
+        <v>0.064419</v>
       </c>
       <c r="C756" t="n">
         <v>0.335541</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.066914</v>
+        <v>0.064986</v>
       </c>
       <c r="C757" t="n">
         <v>0.333333</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.06769500000000001</v>
+        <v>0.06532</v>
       </c>
       <c r="C758" t="n">
         <v>0.331126</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.06773999999999999</v>
+        <v>0.06544700000000001</v>
       </c>
       <c r="C759" t="n">
         <v>0.328918</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.067907</v>
+        <v>0.065633</v>
       </c>
       <c r="C760" t="n">
         <v>0.326711</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.068643</v>
+        <v>0.06594</v>
       </c>
       <c r="C761" t="n">
         <v>0.324503</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.06873</v>
+        <v>0.066112</v>
       </c>
       <c r="C762" t="n">
         <v>0.322296</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.06905699999999999</v>
+        <v>0.066376</v>
       </c>
       <c r="C763" t="n">
         <v>0.320088</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.06916</v>
+        <v>0.067108</v>
       </c>
       <c r="C764" t="n">
         <v>0.317881</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.069282</v>
+        <v>0.068285</v>
       </c>
       <c r="C765" t="n">
         <v>0.315673</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.069408</v>
+        <v>0.06876</v>
       </c>
       <c r="C766" t="n">
         <v>0.313466</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.069844</v>
+        <v>0.069025</v>
       </c>
       <c r="C767" t="n">
         <v>0.311258</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.070187</v>
+        <v>0.069602</v>
       </c>
       <c r="C768" t="n">
         <v>0.309051</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.071034</v>
+        <v>0.069663</v>
       </c>
       <c r="C769" t="n">
         <v>0.306843</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.071687</v>
+        <v>0.069691</v>
       </c>
       <c r="C770" t="n">
         <v>0.304636</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.071951</v>
+        <v>0.070483</v>
       </c>
       <c r="C771" t="n">
         <v>0.302428</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.071976</v>
+        <v>0.070788</v>
       </c>
       <c r="C772" t="n">
         <v>0.300221</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.072589</v>
+        <v>0.07119300000000001</v>
       </c>
       <c r="C773" t="n">
         <v>0.298013</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.072601</v>
+        <v>0.071226</v>
       </c>
       <c r="C774" t="n">
         <v>0.295806</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.074004</v>
+        <v>0.07173400000000001</v>
       </c>
       <c r="C775" t="n">
         <v>0.293598</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.07412199999999999</v>
+        <v>0.071794</v>
       </c>
       <c r="C776" t="n">
         <v>0.291391</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.074186</v>
+        <v>0.072731</v>
       </c>
       <c r="C777" t="n">
         <v>0.289183</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.074432</v>
+        <v>0.073181</v>
       </c>
       <c r="C778" t="n">
         <v>0.286976</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.074961</v>
+        <v>0.073601</v>
       </c>
       <c r="C779" t="n">
         <v>0.284768</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.075694</v>
+        <v>0.074236</v>
       </c>
       <c r="C780" t="n">
         <v>0.282561</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.075764</v>
+        <v>0.07452300000000001</v>
       </c>
       <c r="C781" t="n">
         <v>0.280353</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.075781</v>
+        <v>0.074751</v>
       </c>
       <c r="C782" t="n">
         <v>0.278146</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.076308</v>
+        <v>0.07502200000000001</v>
       </c>
       <c r="C783" t="n">
         <v>0.275938</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.07807799999999999</v>
+        <v>0.075155</v>
       </c>
       <c r="C784" t="n">
         <v>0.273731</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.07857699999999999</v>
+        <v>0.075197</v>
       </c>
       <c r="C785" t="n">
         <v>0.271523</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.078651</v>
+        <v>0.075707</v>
       </c>
       <c r="C786" t="n">
         <v>0.269316</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.079093</v>
+        <v>0.07578600000000001</v>
       </c>
       <c r="C787" t="n">
         <v>0.267108</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.08007400000000001</v>
+        <v>0.076991</v>
       </c>
       <c r="C788" t="n">
         <v>0.264901</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.080245</v>
+        <v>0.077109</v>
       </c>
       <c r="C789" t="n">
         <v>0.262693</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.08082499999999999</v>
+        <v>0.077483</v>
       </c>
       <c r="C790" t="n">
         <v>0.260486</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.081062</v>
+        <v>0.077527</v>
       </c>
       <c r="C791" t="n">
         <v>0.258278</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.08111500000000001</v>
+        <v>0.07870199999999999</v>
       </c>
       <c r="C792" t="n">
         <v>0.256071</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.081774</v>
+        <v>0.078788</v>
       </c>
       <c r="C793" t="n">
         <v>0.253863</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.081856</v>
+        <v>0.079165</v>
       </c>
       <c r="C794" t="n">
         <v>0.251656</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.081966</v>
+        <v>0.08021</v>
       </c>
       <c r="C795" t="n">
         <v>0.249448</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.082694</v>
+        <v>0.080721</v>
       </c>
       <c r="C796" t="n">
         <v>0.247241</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.082723</v>
+        <v>0.08078200000000001</v>
       </c>
       <c r="C797" t="n">
         <v>0.245033</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>0.08278099999999999</v>
+        <v>0.081694</v>
       </c>
       <c r="C798" t="n">
         <v>0.242826</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.083458</v>
+        <v>0.082273</v>
       </c>
       <c r="C799" t="n">
         <v>0.240618</v>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.083729</v>
+        <v>0.082884</v>
       </c>
       <c r="C800" t="n">
         <v>0.238411</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>0.084462</v>
+        <v>0.08312</v>
       </c>
       <c r="C801" t="n">
         <v>0.236203</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B802" t="n">
-        <v>0.084897</v>
+        <v>0.083952</v>
       </c>
       <c r="C802" t="n">
         <v>0.233996</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>0.085396</v>
+        <v>0.084759</v>
       </c>
       <c r="C803" t="n">
         <v>0.231788</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.08486399999999999</v>
       </c>
       <c r="C804" t="n">
         <v>0.229581</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>0.086523</v>
+        <v>0.085491</v>
       </c>
       <c r="C805" t="n">
         <v>0.227373</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>0.086534</v>
+        <v>0.086685</v>
       </c>
       <c r="C806" t="n">
         <v>0.225166</v>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>0.087783</v>
+        <v>0.086852</v>
       </c>
       <c r="C807" t="n">
         <v>0.222958</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.088681</v>
+        <v>0.087216</v>
       </c>
       <c r="C808" t="n">
         <v>0.220751</v>
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>0.090763</v>
+        <v>0.087302</v>
       </c>
       <c r="C809" t="n">
         <v>0.218543</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>0.092617</v>
+        <v>0.087796</v>
       </c>
       <c r="C810" t="n">
         <v>0.216336</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.092706</v>
+        <v>0.088821</v>
       </c>
       <c r="C811" t="n">
         <v>0.214128</v>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.093239</v>
+        <v>0.088938</v>
       </c>
       <c r="C812" t="n">
         <v>0.211921</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.094079</v>
+        <v>0.089713</v>
       </c>
       <c r="C813" t="n">
         <v>0.209713</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.094265</v>
+        <v>0.092524</v>
       </c>
       <c r="C814" t="n">
         <v>0.207506</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.09528399999999999</v>
+        <v>0.093416</v>
       </c>
       <c r="C815" t="n">
         <v>0.205298</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.095609</v>
+        <v>0.094455</v>
       </c>
       <c r="C816" t="n">
         <v>0.203091</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.097844</v>
+        <v>0.095531</v>
       </c>
       <c r="C817" t="n">
         <v>0.200883</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.097902</v>
+        <v>0.09675</v>
       </c>
       <c r="C818" t="n">
         <v>0.198675</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.09915</v>
+        <v>0.097181</v>
       </c>
       <c r="C819" t="n">
         <v>0.196468</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.100728</v>
+        <v>0.098398</v>
       </c>
       <c r="C820" t="n">
         <v>0.19426</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.100963</v>
+        <v>0.098636</v>
       </c>
       <c r="C821" t="n">
         <v>0.192053</v>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.101669</v>
+        <v>0.098857</v>
       </c>
       <c r="C822" t="n">
         <v>0.189845</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.103464</v>
+        <v>0.100983</v>
       </c>
       <c r="C823" t="n">
         <v>0.187638</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.103567</v>
+        <v>0.101788</v>
       </c>
       <c r="C824" t="n">
         <v>0.18543</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>0.104082</v>
+        <v>0.102117</v>
       </c>
       <c r="C825" t="n">
         <v>0.183223</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.105471</v>
+        <v>0.10237</v>
       </c>
       <c r="C826" t="n">
         <v>0.181015</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.106675</v>
+        <v>0.104679</v>
       </c>
       <c r="C827" t="n">
         <v>0.178808</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.106688</v>
+        <v>0.105168</v>
       </c>
       <c r="C828" t="n">
         <v>0.1766</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.107779</v>
+        <v>0.106611</v>
       </c>
       <c r="C829" t="n">
         <v>0.174393</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.108527</v>
+        <v>0.106804</v>
       </c>
       <c r="C830" t="n">
         <v>0.172185</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.108691</v>
+        <v>0.106874</v>
       </c>
       <c r="C831" t="n">
         <v>0.169978</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.10982</v>
+        <v>0.108115</v>
       </c>
       <c r="C832" t="n">
         <v>0.16777</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.110376</v>
+        <v>0.108765</v>
       </c>
       <c r="C833" t="n">
         <v>0.165563</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.110976</v>
+        <v>0.108881</v>
       </c>
       <c r="C834" t="n">
         <v>0.163355</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>0.111861</v>
+        <v>0.109719</v>
       </c>
       <c r="C835" t="n">
         <v>0.161148</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.112168</v>
+        <v>0.110352</v>
       </c>
       <c r="C836" t="n">
         <v>0.15894</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.112491</v>
+        <v>0.11138</v>
       </c>
       <c r="C837" t="n">
         <v>0.156733</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0.116448</v>
+        <v>0.111501</v>
       </c>
       <c r="C838" t="n">
         <v>0.154525</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.116616</v>
+        <v>0.112242</v>
       </c>
       <c r="C839" t="n">
         <v>0.152318</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.11679</v>
+        <v>0.112376</v>
       </c>
       <c r="C840" t="n">
         <v>0.15011</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.117238</v>
+        <v>0.112805</v>
       </c>
       <c r="C841" t="n">
         <v>0.147903</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.117803</v>
+        <v>0.115834</v>
       </c>
       <c r="C842" t="n">
         <v>0.145695</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>0.119808</v>
+        <v>0.116362</v>
       </c>
       <c r="C843" t="n">
         <v>0.143488</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>0.120284</v>
+        <v>0.11637</v>
       </c>
       <c r="C844" t="n">
         <v>0.14128</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.121494</v>
+        <v>0.117588</v>
       </c>
       <c r="C845" t="n">
         <v>0.139073</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>0.12385</v>
+        <v>0.117638</v>
       </c>
       <c r="C846" t="n">
         <v>0.136865</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.126675</v>
+        <v>0.118286</v>
       </c>
       <c r="C847" t="n">
         <v>0.134658</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.127128</v>
+        <v>0.118999</v>
       </c>
       <c r="C848" t="n">
         <v>0.13245</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.127409</v>
+        <v>0.121007</v>
       </c>
       <c r="C849" t="n">
         <v>0.130243</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.129525</v>
+        <v>0.1215</v>
       </c>
       <c r="C850" t="n">
         <v>0.128035</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>0.130044</v>
+        <v>0.125073</v>
       </c>
       <c r="C851" t="n">
         <v>0.125828</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.131218</v>
+        <v>0.125368</v>
       </c>
       <c r="C852" t="n">
         <v>0.12362</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.13236</v>
+        <v>0.126501</v>
       </c>
       <c r="C853" t="n">
         <v>0.121413</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.132424</v>
+        <v>0.129189</v>
       </c>
       <c r="C854" t="n">
         <v>0.119205</v>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>0.134087</v>
+        <v>0.130737</v>
       </c>
       <c r="C855" t="n">
         <v>0.116998</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.13486</v>
+        <v>0.13171</v>
       </c>
       <c r="C856" t="n">
         <v>0.11479</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.135204</v>
+        <v>0.133723</v>
       </c>
       <c r="C857" t="n">
         <v>0.112583</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.137394</v>
+        <v>0.135325</v>
       </c>
       <c r="C858" t="n">
         <v>0.110375</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.137916</v>
+        <v>0.137488</v>
       </c>
       <c r="C859" t="n">
         <v>0.108168</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>0.142701</v>
+        <v>0.138345</v>
       </c>
       <c r="C860" t="n">
         <v>0.10596</v>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>0.143054</v>
+        <v>0.142401</v>
       </c>
       <c r="C861" t="n">
         <v>0.103753</v>
@@ -11620,7 +11620,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>0.147857</v>
+        <v>0.142808</v>
       </c>
       <c r="C862" t="n">
         <v>0.101545</v>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>0.149068</v>
+        <v>0.14371</v>
       </c>
       <c r="C863" t="n">
         <v>0.099338</v>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="B864" t="n">
-        <v>0.150558</v>
+        <v>0.14636</v>
       </c>
       <c r="C864" t="n">
         <v>0.09712999999999999</v>
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>0.150558</v>
+        <v>0.147046</v>
       </c>
       <c r="C865" t="n">
         <v>0.09492299999999999</v>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>0.150558</v>
+        <v>0.147829</v>
       </c>
       <c r="C866" t="n">
         <v>0.09271500000000001</v>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>0.151527</v>
+        <v>0.147829</v>
       </c>
       <c r="C867" t="n">
         <v>0.09050800000000001</v>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>0.155849</v>
+        <v>0.147829</v>
       </c>
       <c r="C868" t="n">
         <v>0.0883</v>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>0.159175</v>
+        <v>0.148303</v>
       </c>
       <c r="C869" t="n">
         <v>0.086093</v>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>0.159504</v>
+        <v>0.149409</v>
       </c>
       <c r="C870" t="n">
         <v>0.083885</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>0.161195</v>
+        <v>0.152283</v>
       </c>
       <c r="C871" t="n">
         <v>0.081678</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>0.161403</v>
+        <v>0.154399</v>
       </c>
       <c r="C872" t="n">
         <v>0.07947</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.162386</v>
+        <v>0.157774</v>
       </c>
       <c r="C873" t="n">
         <v>0.077263</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>0.162483</v>
+        <v>0.159977</v>
       </c>
       <c r="C874" t="n">
         <v>0.075055</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.166104</v>
+        <v>0.161417</v>
       </c>
       <c r="C875" t="n">
         <v>0.072848</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>0.170336</v>
+        <v>0.165255</v>
       </c>
       <c r="C876" t="n">
         <v>0.07063999999999999</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>0.170369</v>
+        <v>0.17124</v>
       </c>
       <c r="C877" t="n">
         <v>0.06843299999999999</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.172763</v>
+        <v>0.173218</v>
       </c>
       <c r="C878" t="n">
         <v>0.06622500000000001</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>0.178901</v>
+        <v>0.174278</v>
       </c>
       <c r="C879" t="n">
         <v>0.06401800000000001</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>0.185299</v>
+        <v>0.184731</v>
       </c>
       <c r="C880" t="n">
         <v>0.06181</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.191712</v>
+        <v>0.18548</v>
       </c>
       <c r="C881" t="n">
         <v>0.059603</v>
@@ -11880,7 +11880,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>0.193578</v>
+        <v>0.190349</v>
       </c>
       <c r="C882" t="n">
         <v>0.057395</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>0.193724</v>
+        <v>0.190665</v>
       </c>
       <c r="C883" t="n">
         <v>0.055188</v>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>0.194661</v>
+        <v>0.192211</v>
       </c>
       <c r="C884" t="n">
         <v>0.05298</v>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.196588</v>
+        <v>0.192241</v>
       </c>
       <c r="C885" t="n">
         <v>0.050773</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.199123</v>
+        <v>0.193947</v>
       </c>
       <c r="C886" t="n">
         <v>0.048565</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>0.215262</v>
+        <v>0.195903</v>
       </c>
       <c r="C887" t="n">
         <v>0.046358</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>0.2292</v>
+        <v>0.224552</v>
       </c>
       <c r="C888" t="n">
         <v>0.04415</v>
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>0.236819</v>
+        <v>0.22876</v>
       </c>
       <c r="C889" t="n">
         <v>0.041943</v>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.238891</v>
+        <v>0.23871</v>
       </c>
       <c r="C890" t="n">
         <v>0.039735</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.245518</v>
+        <v>0.242003</v>
       </c>
       <c r="C891" t="n">
         <v>0.037528</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>0.271131</v>
+        <v>0.268877</v>
       </c>
       <c r="C892" t="n">
         <v>0.03532</v>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>0.271293</v>
+        <v>0.269148</v>
       </c>
       <c r="C893" t="n">
         <v>0.033113</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>0.292699</v>
+        <v>0.274093</v>
       </c>
       <c r="C894" t="n">
         <v>0.030905</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>0.30124</v>
+        <v>0.297576</v>
       </c>
       <c r="C895" t="n">
         <v>0.028698</v>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>0.328577</v>
+        <v>0.316305</v>
       </c>
       <c r="C896" t="n">
         <v>0.02649</v>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>0.341114</v>
+        <v>0.318487</v>
       </c>
       <c r="C897" t="n">
         <v>0.024283</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>0.346968</v>
+        <v>0.324197</v>
       </c>
       <c r="C898" t="n">
         <v>0.022075</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.369012</v>
+        <v>0.33584</v>
       </c>
       <c r="C899" t="n">
         <v>0.019868</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>0.377541</v>
+        <v>0.348781</v>
       </c>
       <c r="C900" t="n">
         <v>0.01766</v>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>0.469569</v>
+        <v>0.463041</v>
       </c>
       <c r="C901" t="n">
         <v>0.015453</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>0.481541</v>
+        <v>0.481082</v>
       </c>
       <c r="C902" t="n">
         <v>0.013245</v>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.5914740000000001</v>
+        <v>0.592096</v>
       </c>
       <c r="C903" t="n">
         <v>0.011038</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.612096</v>
+        <v>0.611522</v>
       </c>
       <c r="C904" t="n">
         <v>0.008829999999999999</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>0.925445</v>
+        <v>0.87456</v>
       </c>
       <c r="C905" t="n">
         <v>0.006623</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>0.97348</v>
+        <v>0.923489</v>
       </c>
       <c r="C906" t="n">
         <v>0.004415</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>1.16703</v>
+        <v>1.179393</v>
       </c>
       <c r="C907" t="n">
         <v>0.002208</v>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="B910" t="n">
-        <v>0.000435</v>
+        <v>0.00041</v>
       </c>
       <c r="C910" t="n">
         <v>0.9955850000000001</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>0.000472</v>
+        <v>0.00047</v>
       </c>
       <c r="C911" t="n">
         <v>0.993377</v>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="B913" t="n">
-        <v>0.000943</v>
+        <v>0.000926</v>
       </c>
       <c r="C913" t="n">
         <v>0.988962</v>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.001014</v>
+        <v>0.00102</v>
       </c>
       <c r="C914" t="n">
         <v>0.986755</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>0.001565</v>
+        <v>0.001547</v>
       </c>
       <c r="C915" t="n">
         <v>0.9845469999999999</v>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>0.00182</v>
+        <v>0.00181</v>
       </c>
       <c r="C916" t="n">
         <v>0.98234</v>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>0.001912</v>
+        <v>0.001923</v>
       </c>
       <c r="C917" t="n">
         <v>0.980132</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>0.002276</v>
+        <v>0.002249</v>
       </c>
       <c r="C918" t="n">
         <v>0.977925</v>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>0.002403</v>
+        <v>0.002342</v>
       </c>
       <c r="C919" t="n">
         <v>0.9757169999999999</v>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="B920" t="n">
-        <v>0.002592</v>
+        <v>0.002591</v>
       </c>
       <c r="C920" t="n">
         <v>0.97351</v>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>0.002693</v>
+        <v>0.002717</v>
       </c>
       <c r="C921" t="n">
         <v>0.971302</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>0.002928</v>
+        <v>0.002887</v>
       </c>
       <c r="C922" t="n">
         <v>0.969095</v>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>0.003093</v>
+        <v>0.002926</v>
       </c>
       <c r="C923" t="n">
         <v>0.9668870000000001</v>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>0.003308</v>
+        <v>0.003253</v>
       </c>
       <c r="C924" t="n">
         <v>0.96468</v>
@@ -12439,7 +12439,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>0.00362</v>
+        <v>0.003556</v>
       </c>
       <c r="C925" t="n">
         <v>0.962472</v>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>0.003734</v>
+        <v>0.003706</v>
       </c>
       <c r="C926" t="n">
         <v>0.960265</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>0.003744</v>
+        <v>0.003729</v>
       </c>
       <c r="C927" t="n">
         <v>0.958057</v>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>0.004013</v>
+        <v>0.004006</v>
       </c>
       <c r="C928" t="n">
         <v>0.95585</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>0.004132</v>
+        <v>0.004118</v>
       </c>
       <c r="C929" t="n">
         <v>0.953642</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>0.004274</v>
+        <v>0.004267</v>
       </c>
       <c r="C930" t="n">
         <v>0.951435</v>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="B931" t="n">
-        <v>0.004305</v>
+        <v>0.004274</v>
       </c>
       <c r="C931" t="n">
         <v>0.949227</v>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="B932" t="n">
-        <v>0.00448</v>
+        <v>0.004368</v>
       </c>
       <c r="C932" t="n">
         <v>0.94702</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>0.004561</v>
+        <v>0.00439</v>
       </c>
       <c r="C933" t="n">
         <v>0.944812</v>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>0.004587</v>
+        <v>0.004405</v>
       </c>
       <c r="C934" t="n">
         <v>0.942605</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="B935" t="n">
-        <v>0.004693</v>
+        <v>0.004475</v>
       </c>
       <c r="C935" t="n">
         <v>0.940397</v>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>0.0047</v>
+        <v>0.004575</v>
       </c>
       <c r="C936" t="n">
         <v>0.93819</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="B937" t="n">
-        <v>0.004715</v>
+        <v>0.004622</v>
       </c>
       <c r="C937" t="n">
         <v>0.935982</v>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>0.004853</v>
+        <v>0.004656</v>
       </c>
       <c r="C938" t="n">
         <v>0.933775</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>0.004976</v>
+        <v>0.004943</v>
       </c>
       <c r="C939" t="n">
         <v>0.931567</v>
@@ -12634,7 +12634,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>0.005309</v>
+        <v>0.005089</v>
       </c>
       <c r="C940" t="n">
         <v>0.92936</v>
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="B941" t="n">
-        <v>0.005314</v>
+        <v>0.005392</v>
       </c>
       <c r="C941" t="n">
         <v>0.927152</v>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>0.00542</v>
+        <v>0.005399</v>
       </c>
       <c r="C942" t="n">
         <v>0.924945</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>0.005436</v>
+        <v>0.00543</v>
       </c>
       <c r="C943" t="n">
         <v>0.922737</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>0.005543</v>
+        <v>0.005448</v>
       </c>
       <c r="C944" t="n">
         <v>0.92053</v>
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>0.005883</v>
+        <v>0.00553</v>
       </c>
       <c r="C945" t="n">
         <v>0.918322</v>
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.007343</v>
+        <v>0.006808</v>
       </c>
       <c r="C946" t="n">
         <v>0.916115</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>0.007749</v>
+        <v>0.007307</v>
       </c>
       <c r="C947" t="n">
         <v>0.913907</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.007842999999999999</v>
+        <v>0.007648</v>
       </c>
       <c r="C948" t="n">
         <v>0.9117</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>0.008045</v>
+        <v>0.007808</v>
       </c>
       <c r="C949" t="n">
         <v>0.909492</v>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>0.008333999999999999</v>
+        <v>0.00804</v>
       </c>
       <c r="C950" t="n">
         <v>0.907285</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>0.008508999999999999</v>
+        <v>0.008533000000000001</v>
       </c>
       <c r="C951" t="n">
         <v>0.905077</v>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>0.008847000000000001</v>
+        <v>0.008746</v>
       </c>
       <c r="C952" t="n">
         <v>0.90287</v>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>0.008878</v>
+        <v>0.008753</v>
       </c>
       <c r="C953" t="n">
         <v>0.900662</v>
@@ -12816,7 +12816,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>0.009002</v>
+        <v>0.008935999999999999</v>
       </c>
       <c r="C954" t="n">
         <v>0.898455</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>0.009102000000000001</v>
+        <v>0.008958000000000001</v>
       </c>
       <c r="C955" t="n">
         <v>0.896247</v>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>0.009306999999999999</v>
+        <v>0.009042</v>
       </c>
       <c r="C956" t="n">
         <v>0.8940399999999999</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>0.009482000000000001</v>
+        <v>0.009086</v>
       </c>
       <c r="C957" t="n">
         <v>0.891832</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>0.009497</v>
+        <v>0.009353</v>
       </c>
       <c r="C958" t="n">
         <v>0.889625</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="B959" t="n">
-        <v>0.009545</v>
+        <v>0.009449000000000001</v>
       </c>
       <c r="C959" t="n">
         <v>0.887417</v>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.009557</v>
+        <v>0.009499</v>
       </c>
       <c r="C960" t="n">
         <v>0.8852100000000001</v>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>0.009926000000000001</v>
+        <v>0.009544</v>
       </c>
       <c r="C961" t="n">
         <v>0.883002</v>
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>0.010231</v>
+        <v>0.009974999999999999</v>
       </c>
       <c r="C962" t="n">
         <v>0.880795</v>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>0.010374</v>
+        <v>0.010269</v>
       </c>
       <c r="C963" t="n">
         <v>0.878587</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>0.010418</v>
+        <v>0.010378</v>
       </c>
       <c r="C964" t="n">
         <v>0.87638</v>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>0.010435</v>
+        <v>0.010394</v>
       </c>
       <c r="C965" t="n">
         <v>0.8741719999999999</v>
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>0.010653</v>
+        <v>0.01049</v>
       </c>
       <c r="C966" t="n">
         <v>0.871965</v>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>0.010752</v>
+        <v>0.010661</v>
       </c>
       <c r="C967" t="n">
         <v>0.869757</v>
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B968" t="n">
-        <v>0.01079</v>
+        <v>0.010875</v>
       </c>
       <c r="C968" t="n">
         <v>0.86755</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0.011212</v>
+        <v>0.01102</v>
       </c>
       <c r="C969" t="n">
         <v>0.8653419999999999</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="B970" t="n">
-        <v>0.011243</v>
+        <v>0.011269</v>
       </c>
       <c r="C970" t="n">
         <v>0.863135</v>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>0.011542</v>
+        <v>0.011284</v>
       </c>
       <c r="C971" t="n">
         <v>0.860927</v>
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>0.011685</v>
+        <v>0.011462</v>
       </c>
       <c r="C972" t="n">
         <v>0.85872</v>
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>0.011687</v>
+        <v>0.011589</v>
       </c>
       <c r="C973" t="n">
         <v>0.8565120000000001</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>0.0122</v>
+        <v>0.012116</v>
       </c>
       <c r="C974" t="n">
         <v>0.854305</v>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>0.012251</v>
+        <v>0.012157</v>
       </c>
       <c r="C975" t="n">
         <v>0.852097</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>0.01238</v>
+        <v>0.012216</v>
       </c>
       <c r="C976" t="n">
         <v>0.84989</v>
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>0.012402</v>
+        <v>0.01226</v>
       </c>
       <c r="C977" t="n">
         <v>0.847682</v>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>0.012436</v>
+        <v>0.012409</v>
       </c>
       <c r="C978" t="n">
         <v>0.845475</v>
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>0.012661</v>
+        <v>0.012739</v>
       </c>
       <c r="C979" t="n">
         <v>0.843267</v>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>0.013054</v>
+        <v>0.013036</v>
       </c>
       <c r="C980" t="n">
         <v>0.84106</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>0.01306</v>
+        <v>0.013131</v>
       </c>
       <c r="C981" t="n">
         <v>0.838852</v>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="B982" t="n">
-        <v>0.013403</v>
+        <v>0.013217</v>
       </c>
       <c r="C982" t="n">
         <v>0.836645</v>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>0.014073</v>
+        <v>0.013946</v>
       </c>
       <c r="C983" t="n">
         <v>0.834437</v>
@@ -13206,7 +13206,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>0.014555</v>
+        <v>0.014287</v>
       </c>
       <c r="C984" t="n">
         <v>0.83223</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>0.01477</v>
+        <v>0.014383</v>
       </c>
       <c r="C985" t="n">
         <v>0.830022</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>0.014889</v>
+        <v>0.014428</v>
       </c>
       <c r="C986" t="n">
         <v>0.827815</v>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>0.014979</v>
+        <v>0.014802</v>
       </c>
       <c r="C987" t="n">
         <v>0.825607</v>
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>0.01498</v>
+        <v>0.014861</v>
       </c>
       <c r="C988" t="n">
         <v>0.8234</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="B989" t="n">
-        <v>0.014985</v>
+        <v>0.014873</v>
       </c>
       <c r="C989" t="n">
         <v>0.821192</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>0.01509</v>
+        <v>0.014889</v>
       </c>
       <c r="C990" t="n">
         <v>0.818985</v>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.015148</v>
+        <v>0.014983</v>
       </c>
       <c r="C991" t="n">
         <v>0.816777</v>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>0.015248</v>
+        <v>0.015106</v>
       </c>
       <c r="C992" t="n">
         <v>0.81457</v>
@@ -13323,7 +13323,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>0.015288</v>
+        <v>0.015226</v>
       </c>
       <c r="C993" t="n">
         <v>0.812362</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>0.015316</v>
+        <v>0.015253</v>
       </c>
       <c r="C994" t="n">
         <v>0.810155</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="B995" t="n">
-        <v>0.015418</v>
+        <v>0.015277</v>
       </c>
       <c r="C995" t="n">
         <v>0.807947</v>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>0.015958</v>
+        <v>0.015394</v>
       </c>
       <c r="C996" t="n">
         <v>0.80574</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="B997" t="n">
-        <v>0.015974</v>
+        <v>0.015438</v>
       </c>
       <c r="C997" t="n">
         <v>0.803532</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>0.016064</v>
+        <v>0.01586</v>
       </c>
       <c r="C998" t="n">
         <v>0.801325</v>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="B999" t="n">
-        <v>0.016158</v>
+        <v>0.015935</v>
       </c>
       <c r="C999" t="n">
         <v>0.799117</v>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.016536</v>
+        <v>0.016313</v>
       </c>
       <c r="C1000" t="n">
         <v>0.796909</v>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.016667</v>
+        <v>0.016538</v>
       </c>
       <c r="C1001" t="n">
         <v>0.794702</v>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>0.016859</v>
+        <v>0.016661</v>
       </c>
       <c r="C1002" t="n">
         <v>0.792494</v>
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>0.017551</v>
+        <v>0.016946</v>
       </c>
       <c r="C1003" t="n">
         <v>0.790287</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>0.017611</v>
+        <v>0.017439</v>
       </c>
       <c r="C1004" t="n">
         <v>0.788079</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>0.017639</v>
+        <v>0.017497</v>
       </c>
       <c r="C1005" t="n">
         <v>0.785872</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>0.017742</v>
+        <v>0.017685</v>
       </c>
       <c r="C1006" t="n">
         <v>0.783664</v>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>0.017873</v>
+        <v>0.01787</v>
       </c>
       <c r="C1007" t="n">
         <v>0.781457</v>
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>0.018123</v>
+        <v>0.017872</v>
       </c>
       <c r="C1008" t="n">
         <v>0.779249</v>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>0.018134</v>
+        <v>0.01806</v>
       </c>
       <c r="C1009" t="n">
         <v>0.777042</v>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.018419</v>
+        <v>0.018095</v>
       </c>
       <c r="C1010" t="n">
         <v>0.774834</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.018724</v>
+        <v>0.018327</v>
       </c>
       <c r="C1011" t="n">
         <v>0.772627</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>0.018761</v>
+        <v>0.018434</v>
       </c>
       <c r="C1012" t="n">
         <v>0.770419</v>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>0.018777</v>
+        <v>0.018587</v>
       </c>
       <c r="C1013" t="n">
         <v>0.768212</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.018911</v>
+        <v>0.018828</v>
       </c>
       <c r="C1014" t="n">
         <v>0.766004</v>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.018914</v>
+        <v>0.018858</v>
       </c>
       <c r="C1015" t="n">
         <v>0.7637969999999999</v>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>0.019119</v>
+        <v>0.018863</v>
       </c>
       <c r="C1016" t="n">
         <v>0.761589</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>0.019607</v>
+        <v>0.019054</v>
       </c>
       <c r="C1017" t="n">
         <v>0.759382</v>
@@ -13648,7 +13648,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.019686</v>
+        <v>0.0191</v>
       </c>
       <c r="C1018" t="n">
         <v>0.757174</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>0.019817</v>
+        <v>0.019702</v>
       </c>
       <c r="C1019" t="n">
         <v>0.7549670000000001</v>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.019863</v>
+        <v>0.019737</v>
       </c>
       <c r="C1020" t="n">
         <v>0.752759</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>0.020465</v>
+        <v>0.020073</v>
       </c>
       <c r="C1021" t="n">
         <v>0.750552</v>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>0.020712</v>
+        <v>0.020532</v>
       </c>
       <c r="C1022" t="n">
         <v>0.748344</v>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>0.020761</v>
+        <v>0.020669</v>
       </c>
       <c r="C1023" t="n">
         <v>0.7461370000000001</v>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>0.021567</v>
+        <v>0.021672</v>
       </c>
       <c r="C1024" t="n">
         <v>0.743929</v>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>0.021775</v>
+        <v>0.021845</v>
       </c>
       <c r="C1025" t="n">
         <v>0.741722</v>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>0.021884</v>
+        <v>0.021954</v>
       </c>
       <c r="C1026" t="n">
         <v>0.739514</v>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>0.022933</v>
+        <v>0.021964</v>
       </c>
       <c r="C1027" t="n">
         <v>0.737307</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>0.023059</v>
+        <v>0.023049</v>
       </c>
       <c r="C1028" t="n">
         <v>0.7350989999999999</v>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>0.023173</v>
+        <v>0.023411</v>
       </c>
       <c r="C1029" t="n">
         <v>0.732892</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>0.023444</v>
+        <v>0.023435</v>
       </c>
       <c r="C1030" t="n">
         <v>0.730684</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.023503</v>
+        <v>0.023479</v>
       </c>
       <c r="C1031" t="n">
         <v>0.728477</v>
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>0.023762</v>
+        <v>0.023845</v>
       </c>
       <c r="C1032" t="n">
         <v>0.7262690000000001</v>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>0.023876</v>
+        <v>0.023865</v>
       </c>
       <c r="C1033" t="n">
         <v>0.724062</v>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>0.024034</v>
+        <v>0.023982</v>
       </c>
       <c r="C1034" t="n">
         <v>0.721854</v>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>0.024338</v>
+        <v>0.024348</v>
       </c>
       <c r="C1035" t="n">
         <v>0.719647</v>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>0.024636</v>
+        <v>0.024375</v>
       </c>
       <c r="C1036" t="n">
         <v>0.717439</v>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>0.024725</v>
+        <v>0.024814</v>
       </c>
       <c r="C1037" t="n">
         <v>0.715232</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>0.024923</v>
+        <v>0.024963</v>
       </c>
       <c r="C1038" t="n">
         <v>0.713024</v>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>0.026208</v>
+        <v>0.025091</v>
       </c>
       <c r="C1039" t="n">
         <v>0.710817</v>
@@ -13934,7 +13934,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0.026493</v>
+        <v>0.025392</v>
       </c>
       <c r="C1040" t="n">
         <v>0.708609</v>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>0.026691</v>
+        <v>0.025566</v>
       </c>
       <c r="C1041" t="n">
         <v>0.706402</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>0.026733</v>
+        <v>0.02584</v>
       </c>
       <c r="C1042" t="n">
         <v>0.704194</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.026796</v>
+        <v>0.026122</v>
       </c>
       <c r="C1043" t="n">
         <v>0.701987</v>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>0.0272</v>
+        <v>0.026515</v>
       </c>
       <c r="C1044" t="n">
         <v>0.699779</v>
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0.027711</v>
+        <v>0.026541</v>
       </c>
       <c r="C1045" t="n">
         <v>0.697572</v>
@@ -14012,7 +14012,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>0.027834</v>
+        <v>0.026597</v>
       </c>
       <c r="C1046" t="n">
         <v>0.695364</v>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>0.027995</v>
+        <v>0.026805</v>
       </c>
       <c r="C1047" t="n">
         <v>0.693157</v>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>0.028012</v>
+        <v>0.026805</v>
       </c>
       <c r="C1048" t="n">
         <v>0.690949</v>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>0.028479</v>
+        <v>0.026945</v>
       </c>
       <c r="C1049" t="n">
         <v>0.688742</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>0.028589</v>
+        <v>0.027156</v>
       </c>
       <c r="C1050" t="n">
         <v>0.686534</v>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.028606</v>
+        <v>0.027424</v>
       </c>
       <c r="C1051" t="n">
         <v>0.684327</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>0.028649</v>
+        <v>0.027943</v>
       </c>
       <c r="C1052" t="n">
         <v>0.682119</v>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>0.028696</v>
+        <v>0.028036</v>
       </c>
       <c r="C1053" t="n">
         <v>0.679912</v>
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>0.028851</v>
+        <v>0.028128</v>
       </c>
       <c r="C1054" t="n">
         <v>0.677704</v>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>0.028912</v>
+        <v>0.028421</v>
       </c>
       <c r="C1055" t="n">
         <v>0.675497</v>
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>0.028917</v>
+        <v>0.028492</v>
       </c>
       <c r="C1056" t="n">
         <v>0.673289</v>
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>0.028932</v>
+        <v>0.028493</v>
       </c>
       <c r="C1057" t="n">
         <v>0.671082</v>
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0.029425</v>
+        <v>0.028949</v>
       </c>
       <c r="C1058" t="n">
         <v>0.668874</v>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>0.029649</v>
+        <v>0.029192</v>
       </c>
       <c r="C1059" t="n">
         <v>0.666667</v>
@@ -14194,7 +14194,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>0.029722</v>
+        <v>0.029222</v>
       </c>
       <c r="C1060" t="n">
         <v>0.664459</v>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>0.030034</v>
+        <v>0.029705</v>
       </c>
       <c r="C1061" t="n">
         <v>0.662252</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>0.030102</v>
+        <v>0.029749</v>
       </c>
       <c r="C1062" t="n">
         <v>0.660044</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>0.030421</v>
+        <v>0.030018</v>
       </c>
       <c r="C1063" t="n">
         <v>0.657837</v>
@@ -14246,7 +14246,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>0.031002</v>
+        <v>0.030437</v>
       </c>
       <c r="C1064" t="n">
         <v>0.655629</v>
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>0.031107</v>
+        <v>0.030504</v>
       </c>
       <c r="C1065" t="n">
         <v>0.6534219999999999</v>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>0.031421</v>
+        <v>0.03051</v>
       </c>
       <c r="C1066" t="n">
         <v>0.651214</v>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>0.031751</v>
+        <v>0.03096</v>
       </c>
       <c r="C1067" t="n">
         <v>0.649007</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>0.031899</v>
+        <v>0.031024</v>
       </c>
       <c r="C1068" t="n">
         <v>0.646799</v>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>0.031941</v>
+        <v>0.031082</v>
       </c>
       <c r="C1069" t="n">
         <v>0.6445920000000001</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>0.032391</v>
+        <v>0.031813</v>
       </c>
       <c r="C1070" t="n">
         <v>0.642384</v>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>0.032467</v>
+        <v>0.031852</v>
       </c>
       <c r="C1071" t="n">
         <v>0.640177</v>
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>0.033138</v>
+        <v>0.032162</v>
       </c>
       <c r="C1072" t="n">
         <v>0.637969</v>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>0.033199</v>
+        <v>0.032273</v>
       </c>
       <c r="C1073" t="n">
         <v>0.635762</v>
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>0.033774</v>
+        <v>0.033066</v>
       </c>
       <c r="C1074" t="n">
         <v>0.633554</v>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.034099</v>
+        <v>0.033077</v>
       </c>
       <c r="C1075" t="n">
         <v>0.631347</v>
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.034267</v>
+        <v>0.033302</v>
       </c>
       <c r="C1076" t="n">
         <v>0.629139</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>0.03427</v>
+        <v>0.033376</v>
       </c>
       <c r="C1077" t="n">
         <v>0.626932</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.034483</v>
+        <v>0.033511</v>
       </c>
       <c r="C1078" t="n">
         <v>0.6247239999999999</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>0.034768</v>
+        <v>0.033812</v>
       </c>
       <c r="C1079" t="n">
         <v>0.622517</v>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>0.034861</v>
+        <v>0.034113</v>
       </c>
       <c r="C1080" t="n">
         <v>0.620309</v>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>0.034868</v>
+        <v>0.034295</v>
       </c>
       <c r="C1081" t="n">
         <v>0.618102</v>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>0.035114</v>
+        <v>0.0347</v>
       </c>
       <c r="C1082" t="n">
         <v>0.6158940000000001</v>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>0.035473</v>
+        <v>0.034711</v>
       </c>
       <c r="C1083" t="n">
         <v>0.613687</v>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.035521</v>
+        <v>0.034907</v>
       </c>
       <c r="C1084" t="n">
         <v>0.611479</v>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>0.03581</v>
+        <v>0.035129</v>
       </c>
       <c r="C1085" t="n">
         <v>0.609272</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.0361</v>
+        <v>0.035183</v>
       </c>
       <c r="C1086" t="n">
         <v>0.607064</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>0.036197</v>
+        <v>0.035585</v>
       </c>
       <c r="C1087" t="n">
         <v>0.604857</v>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>0.036312</v>
+        <v>0.03563</v>
       </c>
       <c r="C1088" t="n">
         <v>0.602649</v>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>0.036342</v>
+        <v>0.035743</v>
       </c>
       <c r="C1089" t="n">
         <v>0.600442</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>0.036758</v>
+        <v>0.035782</v>
       </c>
       <c r="C1090" t="n">
         <v>0.598234</v>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>0.037023</v>
+        <v>0.035832</v>
       </c>
       <c r="C1091" t="n">
         <v>0.5960259999999999</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>0.037239</v>
+        <v>0.036103</v>
       </c>
       <c r="C1092" t="n">
         <v>0.593819</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>0.037437</v>
+        <v>0.036142</v>
       </c>
       <c r="C1093" t="n">
         <v>0.591611</v>
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>0.037499</v>
+        <v>0.036279</v>
       </c>
       <c r="C1094" t="n">
         <v>0.589404</v>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>0.037772</v>
+        <v>0.036358</v>
       </c>
       <c r="C1095" t="n">
         <v>0.5871960000000001</v>
@@ -14662,7 +14662,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>0.037812</v>
+        <v>0.036526</v>
       </c>
       <c r="C1096" t="n">
         <v>0.584989</v>
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>0.0382</v>
+        <v>0.037145</v>
       </c>
       <c r="C1097" t="n">
         <v>0.582781</v>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>0.038641</v>
+        <v>0.037302</v>
       </c>
       <c r="C1098" t="n">
         <v>0.580574</v>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>0.038706</v>
+        <v>0.037313</v>
       </c>
       <c r="C1099" t="n">
         <v>0.578366</v>
@@ -14714,7 +14714,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>0.038929</v>
+        <v>0.03758</v>
       </c>
       <c r="C1100" t="n">
         <v>0.576159</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>0.039129</v>
+        <v>0.037724</v>
       </c>
       <c r="C1101" t="n">
         <v>0.573951</v>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>0.039169</v>
+        <v>0.037811</v>
       </c>
       <c r="C1102" t="n">
         <v>0.571744</v>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>0.039178</v>
+        <v>0.038193</v>
       </c>
       <c r="C1103" t="n">
         <v>0.569536</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.039252</v>
+        <v>0.038306</v>
       </c>
       <c r="C1104" t="n">
         <v>0.567329</v>
@@ -14779,7 +14779,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>0.040154</v>
+        <v>0.03834</v>
       </c>
       <c r="C1105" t="n">
         <v>0.565121</v>
@@ -14792,7 +14792,7 @@
         </is>
       </c>
       <c r="B1106" t="n">
-        <v>0.040157</v>
+        <v>0.038651</v>
       </c>
       <c r="C1106" t="n">
         <v>0.562914</v>
@@ -14805,7 +14805,7 @@
         </is>
       </c>
       <c r="B1107" t="n">
-        <v>0.040168</v>
+        <v>0.03892</v>
       </c>
       <c r="C1107" t="n">
         <v>0.560706</v>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>0.040359</v>
+        <v>0.039074</v>
       </c>
       <c r="C1108" t="n">
         <v>0.558499</v>
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>0.040834</v>
+        <v>0.039687</v>
       </c>
       <c r="C1109" t="n">
         <v>0.556291</v>
@@ -14844,7 +14844,7 @@
         </is>
       </c>
       <c r="B1110" t="n">
-        <v>0.041567</v>
+        <v>0.039905</v>
       </c>
       <c r="C1110" t="n">
         <v>0.554084</v>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B1111" t="n">
-        <v>0.041843</v>
+        <v>0.040097</v>
       </c>
       <c r="C1111" t="n">
         <v>0.551876</v>
@@ -14870,7 +14870,7 @@
         </is>
       </c>
       <c r="B1112" t="n">
-        <v>0.041862</v>
+        <v>0.040188</v>
       </c>
       <c r="C1112" t="n">
         <v>0.549669</v>
@@ -14883,7 +14883,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>0.042125</v>
+        <v>0.040515</v>
       </c>
       <c r="C1113" t="n">
         <v>0.547461</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>0.04217</v>
+        <v>0.04052</v>
       </c>
       <c r="C1114" t="n">
         <v>0.545254</v>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>0.042262</v>
+        <v>0.040545</v>
       </c>
       <c r="C1115" t="n">
         <v>0.543046</v>
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>0.042264</v>
+        <v>0.040645</v>
       </c>
       <c r="C1116" t="n">
         <v>0.540839</v>
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>0.042995</v>
+        <v>0.041071</v>
       </c>
       <c r="C1117" t="n">
         <v>0.538631</v>
@@ -14948,7 +14948,7 @@
         </is>
       </c>
       <c r="B1118" t="n">
-        <v>0.043014</v>
+        <v>0.041359</v>
       </c>
       <c r="C1118" t="n">
         <v>0.536424</v>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="B1119" t="n">
-        <v>0.043079</v>
+        <v>0.041533</v>
       </c>
       <c r="C1119" t="n">
         <v>0.534216</v>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="B1120" t="n">
-        <v>0.043124</v>
+        <v>0.041844</v>
       </c>
       <c r="C1120" t="n">
         <v>0.532009</v>
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>0.043303</v>
+        <v>0.04187</v>
       </c>
       <c r="C1121" t="n">
         <v>0.529801</v>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="B1122" t="n">
-        <v>0.043536</v>
+        <v>0.042478</v>
       </c>
       <c r="C1122" t="n">
         <v>0.527594</v>
@@ -15013,7 +15013,7 @@
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>0.043603</v>
+        <v>0.042606</v>
       </c>
       <c r="C1123" t="n">
         <v>0.525386</v>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>0.0438</v>
+        <v>0.042874</v>
       </c>
       <c r="C1124" t="n">
         <v>0.5231789999999999</v>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>0.044437</v>
+        <v>0.043008</v>
       </c>
       <c r="C1125" t="n">
         <v>0.520971</v>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="B1126" t="n">
-        <v>0.044561</v>
+        <v>0.044445</v>
       </c>
       <c r="C1126" t="n">
         <v>0.518764</v>
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="B1127" t="n">
-        <v>0.045178</v>
+        <v>0.044869</v>
       </c>
       <c r="C1127" t="n">
         <v>0.516556</v>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="B1128" t="n">
-        <v>0.045259</v>
+        <v>0.04515</v>
       </c>
       <c r="C1128" t="n">
         <v>0.5143489999999999</v>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="B1129" t="n">
-        <v>0.046004</v>
+        <v>0.045579</v>
       </c>
       <c r="C1129" t="n">
         <v>0.512141</v>
@@ -15104,7 +15104,7 @@
         </is>
       </c>
       <c r="B1130" t="n">
-        <v>0.046681</v>
+        <v>0.046136</v>
       </c>
       <c r="C1130" t="n">
         <v>0.509934</v>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="B1131" t="n">
-        <v>0.046971</v>
+        <v>0.046357</v>
       </c>
       <c r="C1131" t="n">
         <v>0.507726</v>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="B1132" t="n">
-        <v>0.047127</v>
+        <v>0.046383</v>
       </c>
       <c r="C1132" t="n">
         <v>0.5055190000000001</v>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="B1133" t="n">
-        <v>0.047157</v>
+        <v>0.04658</v>
       </c>
       <c r="C1133" t="n">
         <v>0.503311</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="B1134" t="n">
-        <v>0.047387</v>
+        <v>0.04671</v>
       </c>
       <c r="C1134" t="n">
         <v>0.501104</v>
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="B1135" t="n">
-        <v>0.047399</v>
+        <v>0.046995</v>
       </c>
       <c r="C1135" t="n">
         <v>0.498896</v>
@@ -15182,7 +15182,7 @@
         </is>
       </c>
       <c r="B1136" t="n">
-        <v>0.047971</v>
+        <v>0.047123</v>
       </c>
       <c r="C1136" t="n">
         <v>0.496689</v>
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="B1137" t="n">
-        <v>0.048147</v>
+        <v>0.047556</v>
       </c>
       <c r="C1137" t="n">
         <v>0.494481</v>
@@ -15208,7 +15208,7 @@
         </is>
       </c>
       <c r="B1138" t="n">
-        <v>0.049142</v>
+        <v>0.047932</v>
       </c>
       <c r="C1138" t="n">
         <v>0.492274</v>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>0.049343</v>
+        <v>0.047964</v>
       </c>
       <c r="C1139" t="n">
         <v>0.490066</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="B1140" t="n">
-        <v>0.050374</v>
+        <v>0.048943</v>
       </c>
       <c r="C1140" t="n">
         <v>0.487859</v>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="B1141" t="n">
-        <v>0.050411</v>
+        <v>0.04901</v>
       </c>
       <c r="C1141" t="n">
         <v>0.485651</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="B1142" t="n">
-        <v>0.050417</v>
+        <v>0.049875</v>
       </c>
       <c r="C1142" t="n">
         <v>0.483444</v>
@@ -15273,7 +15273,7 @@
         </is>
       </c>
       <c r="B1143" t="n">
-        <v>0.050467</v>
+        <v>0.050389</v>
       </c>
       <c r="C1143" t="n">
         <v>0.481236</v>
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="B1144" t="n">
-        <v>0.050821</v>
+        <v>0.050519</v>
       </c>
       <c r="C1144" t="n">
         <v>0.479029</v>
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>0.051225</v>
+        <v>0.050669</v>
       </c>
       <c r="C1145" t="n">
         <v>0.476821</v>
@@ -15312,7 +15312,7 @@
         </is>
       </c>
       <c r="B1146" t="n">
-        <v>0.051862</v>
+        <v>0.050876</v>
       </c>
       <c r="C1146" t="n">
         <v>0.474614</v>
@@ -15325,7 +15325,7 @@
         </is>
       </c>
       <c r="B1147" t="n">
-        <v>0.052021</v>
+        <v>0.050902</v>
       </c>
       <c r="C1147" t="n">
         <v>0.472406</v>
@@ -15338,7 +15338,7 @@
         </is>
       </c>
       <c r="B1148" t="n">
-        <v>0.052212</v>
+        <v>0.051894</v>
       </c>
       <c r="C1148" t="n">
         <v>0.470199</v>
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>0.052464</v>
+        <v>0.052089</v>
       </c>
       <c r="C1149" t="n">
         <v>0.467991</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="B1150" t="n">
-        <v>0.053534</v>
+        <v>0.05244</v>
       </c>
       <c r="C1150" t="n">
         <v>0.465784</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>0.053585</v>
+        <v>0.052486</v>
       </c>
       <c r="C1151" t="n">
         <v>0.463576</v>
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>0.054214</v>
+        <v>0.052954</v>
       </c>
       <c r="C1152" t="n">
         <v>0.461369</v>
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="B1153" t="n">
-        <v>0.05431</v>
+        <v>0.053567</v>
       </c>
       <c r="C1153" t="n">
         <v>0.459161</v>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>0.054503</v>
+        <v>0.053985</v>
       </c>
       <c r="C1154" t="n">
         <v>0.456954</v>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>0.056669</v>
+        <v>0.054337</v>
       </c>
       <c r="C1155" t="n">
         <v>0.454746</v>
@@ -15442,7 +15442,7 @@
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>0.056914</v>
+        <v>0.054515</v>
       </c>
       <c r="C1156" t="n">
         <v>0.452539</v>
@@ -15455,7 +15455,7 @@
         </is>
       </c>
       <c r="B1157" t="n">
-        <v>0.057262</v>
+        <v>0.054744</v>
       </c>
       <c r="C1157" t="n">
         <v>0.450331</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>0.057308</v>
+        <v>0.056211</v>
       </c>
       <c r="C1158" t="n">
         <v>0.448124</v>
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="B1159" t="n">
-        <v>0.057586</v>
+        <v>0.056432</v>
       </c>
       <c r="C1159" t="n">
         <v>0.445916</v>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="B1160" t="n">
-        <v>0.057938</v>
+        <v>0.056897</v>
       </c>
       <c r="C1160" t="n">
         <v>0.443709</v>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="B1161" t="n">
-        <v>0.058109</v>
+        <v>0.057173</v>
       </c>
       <c r="C1161" t="n">
         <v>0.441501</v>
@@ -15520,7 +15520,7 @@
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>0.058396</v>
+        <v>0.057584</v>
       </c>
       <c r="C1162" t="n">
         <v>0.439294</v>
@@ -15533,7 +15533,7 @@
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>0.059271</v>
+        <v>0.057592</v>
       </c>
       <c r="C1163" t="n">
         <v>0.437086</v>
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="B1164" t="n">
-        <v>0.059369</v>
+        <v>0.057821</v>
       </c>
       <c r="C1164" t="n">
         <v>0.434879</v>
@@ -15559,7 +15559,7 @@
         </is>
       </c>
       <c r="B1165" t="n">
-        <v>0.059531</v>
+        <v>0.057853</v>
       </c>
       <c r="C1165" t="n">
         <v>0.432671</v>
@@ -15572,7 +15572,7 @@
         </is>
       </c>
       <c r="B1166" t="n">
-        <v>0.059737</v>
+        <v>0.058019</v>
       </c>
       <c r="C1166" t="n">
         <v>0.430464</v>
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>0.060257</v>
+        <v>0.058443</v>
       </c>
       <c r="C1167" t="n">
         <v>0.428256</v>
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>0.060292</v>
+        <v>0.059323</v>
       </c>
       <c r="C1168" t="n">
         <v>0.426049</v>
@@ -15611,7 +15611,7 @@
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>0.060517</v>
+        <v>0.059334</v>
       </c>
       <c r="C1169" t="n">
         <v>0.423841</v>
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="B1170" t="n">
-        <v>0.060683</v>
+        <v>0.060273</v>
       </c>
       <c r="C1170" t="n">
         <v>0.421634</v>
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>0.060954</v>
+        <v>0.060559</v>
       </c>
       <c r="C1171" t="n">
         <v>0.419426</v>
@@ -15650,7 +15650,7 @@
         </is>
       </c>
       <c r="B1172" t="n">
-        <v>0.06111</v>
+        <v>0.060826</v>
       </c>
       <c r="C1172" t="n">
         <v>0.417219</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>0.061323</v>
+        <v>0.060834</v>
       </c>
       <c r="C1173" t="n">
         <v>0.415011</v>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="B1174" t="n">
-        <v>0.061882</v>
+        <v>0.060938</v>
       </c>
       <c r="C1174" t="n">
         <v>0.412804</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="B1175" t="n">
-        <v>0.062022</v>
+        <v>0.061005</v>
       </c>
       <c r="C1175" t="n">
         <v>0.410596</v>
@@ -15702,7 +15702,7 @@
         </is>
       </c>
       <c r="B1176" t="n">
-        <v>0.062142</v>
+        <v>0.061403</v>
       </c>
       <c r="C1176" t="n">
         <v>0.408389</v>
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="B1177" t="n">
-        <v>0.063106</v>
+        <v>0.061427</v>
       </c>
       <c r="C1177" t="n">
         <v>0.406181</v>
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="B1178" t="n">
-        <v>0.06428399999999999</v>
+        <v>0.061718</v>
       </c>
       <c r="C1178" t="n">
         <v>0.403974</v>
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="B1179" t="n">
-        <v>0.064488</v>
+        <v>0.061734</v>
       </c>
       <c r="C1179" t="n">
         <v>0.401766</v>
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>0.064572</v>
+        <v>0.062033</v>
       </c>
       <c r="C1180" t="n">
         <v>0.399558</v>
@@ -15767,7 +15767,7 @@
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>0.06479</v>
+        <v>0.06225</v>
       </c>
       <c r="C1181" t="n">
         <v>0.397351</v>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="B1182" t="n">
-        <v>0.064944</v>
+        <v>0.062331</v>
       </c>
       <c r="C1182" t="n">
         <v>0.395143</v>
@@ -15793,7 +15793,7 @@
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>0.065161</v>
+        <v>0.06367299999999999</v>
       </c>
       <c r="C1183" t="n">
         <v>0.392936</v>
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>0.06522799999999999</v>
+        <v>0.063876</v>
       </c>
       <c r="C1184" t="n">
         <v>0.390728</v>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="B1185" t="n">
-        <v>0.066057</v>
+        <v>0.064037</v>
       </c>
       <c r="C1185" t="n">
         <v>0.388521</v>
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="B1186" t="n">
-        <v>0.066249</v>
+        <v>0.064067</v>
       </c>
       <c r="C1186" t="n">
         <v>0.386313</v>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="B1187" t="n">
-        <v>0.066259</v>
+        <v>0.064277</v>
       </c>
       <c r="C1187" t="n">
         <v>0.384106</v>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="B1188" t="n">
-        <v>0.066417</v>
+        <v>0.064791</v>
       </c>
       <c r="C1188" t="n">
         <v>0.381898</v>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="B1189" t="n">
-        <v>0.066442</v>
+        <v>0.064855</v>
       </c>
       <c r="C1189" t="n">
         <v>0.379691</v>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="B1190" t="n">
-        <v>0.066595</v>
+        <v>0.06501</v>
       </c>
       <c r="C1190" t="n">
         <v>0.377483</v>
@@ -15897,7 +15897,7 @@
         </is>
       </c>
       <c r="B1191" t="n">
-        <v>0.066769</v>
+        <v>0.065404</v>
       </c>
       <c r="C1191" t="n">
         <v>0.375276</v>
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="B1192" t="n">
-        <v>0.06701600000000001</v>
+        <v>0.066068</v>
       </c>
       <c r="C1192" t="n">
         <v>0.373068</v>
@@ -15923,7 +15923,7 @@
         </is>
       </c>
       <c r="B1193" t="n">
-        <v>0.06704</v>
+        <v>0.066291</v>
       </c>
       <c r="C1193" t="n">
         <v>0.370861</v>
@@ -15936,7 +15936,7 @@
         </is>
       </c>
       <c r="B1194" t="n">
-        <v>0.067687</v>
+        <v>0.066425</v>
       </c>
       <c r="C1194" t="n">
         <v>0.368653</v>
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>0.067843</v>
+        <v>0.06655</v>
       </c>
       <c r="C1195" t="n">
         <v>0.366446</v>
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="B1196" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.066596</v>
       </c>
       <c r="C1196" t="n">
         <v>0.364238</v>
@@ -15975,7 +15975,7 @@
         </is>
       </c>
       <c r="B1197" t="n">
-        <v>0.068137</v>
+        <v>0.066708</v>
       </c>
       <c r="C1197" t="n">
         <v>0.362031</v>
@@ -15988,7 +15988,7 @@
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>0.068249</v>
+        <v>0.06759900000000001</v>
       </c>
       <c r="C1198" t="n">
         <v>0.359823</v>
@@ -16001,7 +16001,7 @@
         </is>
       </c>
       <c r="B1199" t="n">
-        <v>0.06833</v>
+        <v>0.067856</v>
       </c>
       <c r="C1199" t="n">
         <v>0.357616</v>
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="B1200" t="n">
-        <v>0.06876699999999999</v>
+        <v>0.068283</v>
       </c>
       <c r="C1200" t="n">
         <v>0.355408</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="B1201" t="n">
-        <v>0.06911</v>
+        <v>0.068548</v>
       </c>
       <c r="C1201" t="n">
         <v>0.353201</v>
@@ -16040,7 +16040,7 @@
         </is>
       </c>
       <c r="B1202" t="n">
-        <v>0.069568</v>
+        <v>0.06855899999999999</v>
       </c>
       <c r="C1202" t="n">
         <v>0.350993</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>0.06987400000000001</v>
+        <v>0.068659</v>
       </c>
       <c r="C1203" t="n">
         <v>0.348786</v>
@@ -16066,7 +16066,7 @@
         </is>
       </c>
       <c r="B1204" t="n">
-        <v>0.07019599999999999</v>
+        <v>0.06866700000000001</v>
       </c>
       <c r="C1204" t="n">
         <v>0.346578</v>
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="B1205" t="n">
-        <v>0.071338</v>
+        <v>0.06894699999999999</v>
       </c>
       <c r="C1205" t="n">
         <v>0.344371</v>
@@ -16092,7 +16092,7 @@
         </is>
       </c>
       <c r="B1206" t="n">
-        <v>0.071354</v>
+        <v>0.069615</v>
       </c>
       <c r="C1206" t="n">
         <v>0.342163</v>
@@ -16105,7 +16105,7 @@
         </is>
       </c>
       <c r="B1207" t="n">
-        <v>0.071537</v>
+        <v>0.069817</v>
       </c>
       <c r="C1207" t="n">
         <v>0.339956</v>
@@ -16118,7 +16118,7 @@
         </is>
       </c>
       <c r="B1208" t="n">
-        <v>0.07159</v>
+        <v>0.069923</v>
       </c>
       <c r="C1208" t="n">
         <v>0.337748</v>
@@ -16131,7 +16131,7 @@
         </is>
       </c>
       <c r="B1209" t="n">
-        <v>0.071626</v>
+        <v>0.070066</v>
       </c>
       <c r="C1209" t="n">
         <v>0.335541</v>
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="B1210" t="n">
-        <v>0.07272199999999999</v>
+        <v>0.070683</v>
       </c>
       <c r="C1210" t="n">
         <v>0.333333</v>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="B1211" t="n">
-        <v>0.073572</v>
+        <v>0.071046</v>
       </c>
       <c r="C1211" t="n">
         <v>0.331126</v>
@@ -16170,7 +16170,7 @@
         </is>
       </c>
       <c r="B1212" t="n">
-        <v>0.07362100000000001</v>
+        <v>0.071184</v>
       </c>
       <c r="C1212" t="n">
         <v>0.328918</v>
@@ -16183,7 +16183,7 @@
         </is>
       </c>
       <c r="B1213" t="n">
-        <v>0.07380200000000001</v>
+        <v>0.07138700000000001</v>
       </c>
       <c r="C1213" t="n">
         <v>0.326711</v>
@@ -16196,7 +16196,7 @@
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>0.074601</v>
+        <v>0.07172099999999999</v>
       </c>
       <c r="C1214" t="n">
         <v>0.324503</v>
@@ -16209,7 +16209,7 @@
         </is>
       </c>
       <c r="B1215" t="n">
-        <v>0.074696</v>
+        <v>0.071908</v>
       </c>
       <c r="C1215" t="n">
         <v>0.322296</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="B1216" t="n">
-        <v>0.07505199999999999</v>
+        <v>0.072195</v>
       </c>
       <c r="C1216" t="n">
         <v>0.320088</v>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="B1217" t="n">
-        <v>0.07516399999999999</v>
+        <v>0.072991</v>
       </c>
       <c r="C1217" t="n">
         <v>0.317881</v>
@@ -16248,7 +16248,7 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>0.075297</v>
+        <v>0.07427</v>
       </c>
       <c r="C1218" t="n">
         <v>0.315673</v>
@@ -16261,7 +16261,7 @@
         </is>
       </c>
       <c r="B1219" t="n">
-        <v>0.075433</v>
+        <v>0.07478700000000001</v>
       </c>
       <c r="C1219" t="n">
         <v>0.313466</v>
@@ -16274,7 +16274,7 @@
         </is>
       </c>
       <c r="B1220" t="n">
-        <v>0.075907</v>
+        <v>0.075076</v>
       </c>
       <c r="C1220" t="n">
         <v>0.311258</v>
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="B1221" t="n">
-        <v>0.07628</v>
+        <v>0.07570300000000001</v>
       </c>
       <c r="C1221" t="n">
         <v>0.309051</v>
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>0.07720100000000001</v>
+        <v>0.07577</v>
       </c>
       <c r="C1222" t="n">
         <v>0.306843</v>
@@ -16313,7 +16313,7 @@
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>0.07790999999999999</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="C1223" t="n">
         <v>0.304636</v>
@@ -16326,7 +16326,7 @@
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>0.078197</v>
+        <v>0.07666199999999999</v>
       </c>
       <c r="C1224" t="n">
         <v>0.302428</v>
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="B1225" t="n">
-        <v>0.078225</v>
+        <v>0.07699300000000001</v>
       </c>
       <c r="C1225" t="n">
         <v>0.300221</v>
@@ -16352,7 +16352,7 @@
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>0.07889</v>
+        <v>0.077433</v>
       </c>
       <c r="C1226" t="n">
         <v>0.298013</v>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="B1227" t="n">
-        <v>0.078903</v>
+        <v>0.077469</v>
       </c>
       <c r="C1227" t="n">
         <v>0.295806</v>
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="B1228" t="n">
-        <v>0.080428</v>
+        <v>0.078023</v>
       </c>
       <c r="C1228" t="n">
         <v>0.293598</v>
@@ -16391,7 +16391,7 @@
         </is>
       </c>
       <c r="B1229" t="n">
-        <v>0.080557</v>
+        <v>0.078087</v>
       </c>
       <c r="C1229" t="n">
         <v>0.291391</v>
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="B1230" t="n">
-        <v>0.080626</v>
+        <v>0.079107</v>
       </c>
       <c r="C1230" t="n">
         <v>0.289183</v>
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="B1231" t="n">
-        <v>0.08089300000000001</v>
+        <v>0.079596</v>
       </c>
       <c r="C1231" t="n">
         <v>0.286976</v>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="B1232" t="n">
-        <v>0.081468</v>
+        <v>0.080053</v>
       </c>
       <c r="C1232" t="n">
         <v>0.284768</v>
@@ -16443,7 +16443,7 @@
         </is>
       </c>
       <c r="B1233" t="n">
-        <v>0.082265</v>
+        <v>0.080743</v>
       </c>
       <c r="C1233" t="n">
         <v>0.282561</v>
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="B1234" t="n">
-        <v>0.082341</v>
+        <v>0.081055</v>
       </c>
       <c r="C1234" t="n">
         <v>0.280353</v>
@@ -16469,7 +16469,7 @@
         </is>
       </c>
       <c r="B1235" t="n">
-        <v>0.08236</v>
+        <v>0.081304</v>
       </c>
       <c r="C1235" t="n">
         <v>0.278146</v>
@@ -16482,7 +16482,7 @@
         </is>
       </c>
       <c r="B1236" t="n">
-        <v>0.08293200000000001</v>
+        <v>0.081598</v>
       </c>
       <c r="C1236" t="n">
         <v>0.275938</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="B1237" t="n">
-        <v>0.084856</v>
+        <v>0.081744</v>
       </c>
       <c r="C1237" t="n">
         <v>0.273731</v>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>0.085398</v>
+        <v>0.081789</v>
       </c>
       <c r="C1238" t="n">
         <v>0.271523</v>
@@ -16521,7 +16521,7 @@
         </is>
       </c>
       <c r="B1239" t="n">
-        <v>0.085479</v>
+        <v>0.082344</v>
       </c>
       <c r="C1239" t="n">
         <v>0.269316</v>
@@ -16534,7 +16534,7 @@
         </is>
       </c>
       <c r="B1240" t="n">
-        <v>0.08595899999999999</v>
+        <v>0.082429</v>
       </c>
       <c r="C1240" t="n">
         <v>0.267108</v>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>0.08702500000000001</v>
+        <v>0.08373999999999999</v>
       </c>
       <c r="C1241" t="n">
         <v>0.264901</v>
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="B1242" t="n">
-        <v>0.087211</v>
+        <v>0.083868</v>
       </c>
       <c r="C1242" t="n">
         <v>0.262693</v>
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="B1243" t="n">
-        <v>0.087841</v>
+        <v>0.084275</v>
       </c>
       <c r="C1243" t="n">
         <v>0.260486</v>
@@ -16586,7 +16586,7 @@
         </is>
       </c>
       <c r="B1244" t="n">
-        <v>0.088099</v>
+        <v>0.084323</v>
       </c>
       <c r="C1244" t="n">
         <v>0.258278</v>
@@ -16599,7 +16599,7 @@
         </is>
       </c>
       <c r="B1245" t="n">
-        <v>0.088157</v>
+        <v>0.085601</v>
       </c>
       <c r="C1245" t="n">
         <v>0.256071</v>
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>0.08887299999999999</v>
+        <v>0.08569400000000001</v>
       </c>
       <c r="C1246" t="n">
         <v>0.253863</v>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="B1247" t="n">
-        <v>0.088962</v>
+        <v>0.086104</v>
       </c>
       <c r="C1247" t="n">
         <v>0.251656</v>
@@ -16638,7 +16638,7 @@
         </is>
       </c>
       <c r="B1248" t="n">
-        <v>0.08908099999999999</v>
+        <v>0.087241</v>
       </c>
       <c r="C1248" t="n">
         <v>0.249448</v>
@@ -16651,7 +16651,7 @@
         </is>
       </c>
       <c r="B1249" t="n">
-        <v>0.08987299999999999</v>
+        <v>0.087797</v>
       </c>
       <c r="C1249" t="n">
         <v>0.247241</v>
@@ -16664,7 +16664,7 @@
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>0.089904</v>
+        <v>0.087863</v>
       </c>
       <c r="C1250" t="n">
         <v>0.245033</v>
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="B1251" t="n">
-        <v>0.08996700000000001</v>
+        <v>0.088856</v>
       </c>
       <c r="C1251" t="n">
         <v>0.242826</v>
@@ -16690,7 +16690,7 @@
         </is>
       </c>
       <c r="B1252" t="n">
-        <v>0.09070300000000001</v>
+        <v>0.089485</v>
       </c>
       <c r="C1252" t="n">
         <v>0.240618</v>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>0.09099699999999999</v>
+        <v>0.09014999999999999</v>
       </c>
       <c r="C1253" t="n">
         <v>0.238411</v>
@@ -16716,7 +16716,7 @@
         </is>
       </c>
       <c r="B1254" t="n">
-        <v>0.091794</v>
+        <v>0.090406</v>
       </c>
       <c r="C1254" t="n">
         <v>0.236203</v>
@@ -16729,7 +16729,7 @@
         </is>
       </c>
       <c r="B1255" t="n">
-        <v>0.092267</v>
+        <v>0.091311</v>
       </c>
       <c r="C1255" t="n">
         <v>0.233996</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="B1256" t="n">
-        <v>0.092809</v>
+        <v>0.09218899999999999</v>
       </c>
       <c r="C1256" t="n">
         <v>0.231788</v>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="B1257" t="n">
-        <v>0.09400799999999999</v>
+        <v>0.092303</v>
       </c>
       <c r="C1257" t="n">
         <v>0.229581</v>
@@ -16768,7 +16768,7 @@
         </is>
       </c>
       <c r="B1258" t="n">
-        <v>0.09403400000000001</v>
+        <v>0.092985</v>
       </c>
       <c r="C1258" t="n">
         <v>0.227373</v>
@@ -16781,7 +16781,7 @@
         </is>
       </c>
       <c r="B1259" t="n">
-        <v>0.094046</v>
+        <v>0.09428400000000001</v>
       </c>
       <c r="C1259" t="n">
         <v>0.225166</v>
@@ -16794,7 +16794,7 @@
         </is>
       </c>
       <c r="B1260" t="n">
-        <v>0.095403</v>
+        <v>0.09446599999999999</v>
       </c>
       <c r="C1260" t="n">
         <v>0.222958</v>
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>0.09637999999999999</v>
+        <v>0.094861</v>
       </c>
       <c r="C1261" t="n">
         <v>0.220751</v>
@@ -16820,7 +16820,7 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>0.09864199999999999</v>
+        <v>0.094955</v>
       </c>
       <c r="C1262" t="n">
         <v>0.218543</v>
@@ -16833,7 +16833,7 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>0.100657</v>
+        <v>0.09549299999999999</v>
       </c>
       <c r="C1263" t="n">
         <v>0.216336</v>
@@ -16846,7 +16846,7 @@
         </is>
       </c>
       <c r="B1264" t="n">
-        <v>0.100754</v>
+        <v>0.096607</v>
       </c>
       <c r="C1264" t="n">
         <v>0.214128</v>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="B1265" t="n">
-        <v>0.101333</v>
+        <v>0.096734</v>
       </c>
       <c r="C1265" t="n">
         <v>0.211921</v>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>0.102246</v>
+        <v>0.097577</v>
       </c>
       <c r="C1266" t="n">
         <v>0.209713</v>
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>0.102448</v>
+        <v>0.100634</v>
       </c>
       <c r="C1267" t="n">
         <v>0.207506</v>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="B1268" t="n">
-        <v>0.103555</v>
+        <v>0.101604</v>
       </c>
       <c r="C1268" t="n">
         <v>0.205298</v>
@@ -16911,7 +16911,7 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>0.103909</v>
+        <v>0.102735</v>
       </c>
       <c r="C1269" t="n">
         <v>0.203091</v>
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="B1270" t="n">
-        <v>0.106338</v>
+        <v>0.103905</v>
       </c>
       <c r="C1270" t="n">
         <v>0.200883</v>
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="B1271" t="n">
-        <v>0.106401</v>
+        <v>0.105231</v>
       </c>
       <c r="C1271" t="n">
         <v>0.198675</v>
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>0.107757</v>
+        <v>0.1057</v>
       </c>
       <c r="C1272" t="n">
         <v>0.196468</v>
@@ -16963,7 +16963,7 @@
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>0.109472</v>
+        <v>0.107023</v>
       </c>
       <c r="C1273" t="n">
         <v>0.19426</v>
@@ -16976,7 +16976,7 @@
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>0.109728</v>
+        <v>0.107282</v>
       </c>
       <c r="C1274" t="n">
         <v>0.192053</v>
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>0.110495</v>
+        <v>0.107522</v>
       </c>
       <c r="C1275" t="n">
         <v>0.189845</v>
@@ -17002,7 +17002,7 @@
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>0.112446</v>
+        <v>0.109835</v>
       </c>
       <c r="C1276" t="n">
         <v>0.187638</v>
@@ -17015,7 +17015,7 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>0.112557</v>
+        <v>0.110711</v>
       </c>
       <c r="C1277" t="n">
         <v>0.18543</v>
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="B1278" t="n">
-        <v>0.113117</v>
+        <v>0.111069</v>
       </c>
       <c r="C1278" t="n">
         <v>0.183223</v>
@@ -17041,7 +17041,7 @@
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>0.114626</v>
+        <v>0.111343</v>
       </c>
       <c r="C1279" t="n">
         <v>0.181015</v>
@@ -17054,7 +17054,7 @@
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>0.115936</v>
+        <v>0.113855</v>
       </c>
       <c r="C1280" t="n">
         <v>0.178808</v>
@@ -17067,7 +17067,7 @@
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>0.115949</v>
+        <v>0.114387</v>
       </c>
       <c r="C1281" t="n">
         <v>0.1766</v>
@@ -17080,7 +17080,7 @@
         </is>
       </c>
       <c r="B1282" t="n">
-        <v>0.117135</v>
+        <v>0.115956</v>
       </c>
       <c r="C1282" t="n">
         <v>0.174393</v>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>0.117949</v>
+        <v>0.116167</v>
       </c>
       <c r="C1283" t="n">
         <v>0.172185</v>
@@ -17106,7 +17106,7 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>0.118126</v>
+        <v>0.116242</v>
       </c>
       <c r="C1284" t="n">
         <v>0.169978</v>
@@ -17119,7 +17119,7 @@
         </is>
       </c>
       <c r="B1285" t="n">
-        <v>0.119354</v>
+        <v>0.117592</v>
       </c>
       <c r="C1285" t="n">
         <v>0.16777</v>
@@ -17132,7 +17132,7 @@
         </is>
       </c>
       <c r="B1286" t="n">
-        <v>0.119958</v>
+        <v>0.1183</v>
       </c>
       <c r="C1286" t="n">
         <v>0.165563</v>
@@ -17145,7 +17145,7 @@
         </is>
       </c>
       <c r="B1287" t="n">
-        <v>0.12061</v>
+        <v>0.118426</v>
       </c>
       <c r="C1287" t="n">
         <v>0.163355</v>
@@ -17158,7 +17158,7 @@
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>0.121571</v>
+        <v>0.119338</v>
       </c>
       <c r="C1288" t="n">
         <v>0.161148</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>0.121905</v>
+        <v>0.120026</v>
       </c>
       <c r="C1289" t="n">
         <v>0.15894</v>
@@ -17184,7 +17184,7 @@
         </is>
       </c>
       <c r="B1290" t="n">
-        <v>0.122256</v>
+        <v>0.121143</v>
       </c>
       <c r="C1290" t="n">
         <v>0.156733</v>
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>0.126557</v>
+        <v>0.121275</v>
       </c>
       <c r="C1291" t="n">
         <v>0.154525</v>
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="B1292" t="n">
-        <v>0.12674</v>
+        <v>0.122081</v>
       </c>
       <c r="C1292" t="n">
         <v>0.152318</v>
@@ -17223,7 +17223,7 @@
         </is>
       </c>
       <c r="B1293" t="n">
-        <v>0.126928</v>
+        <v>0.122227</v>
       </c>
       <c r="C1293" t="n">
         <v>0.15011</v>
@@ -17236,7 +17236,7 @@
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>0.127415</v>
+        <v>0.122693</v>
       </c>
       <c r="C1294" t="n">
         <v>0.147903</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="B1295" t="n">
-        <v>0.128029</v>
+        <v>0.125988</v>
       </c>
       <c r="C1295" t="n">
         <v>0.145695</v>
@@ -17262,7 +17262,7 @@
         </is>
       </c>
       <c r="B1296" t="n">
-        <v>0.130209</v>
+        <v>0.126562</v>
       </c>
       <c r="C1296" t="n">
         <v>0.143488</v>
@@ -17275,7 +17275,7 @@
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>0.130726</v>
+        <v>0.126571</v>
       </c>
       <c r="C1297" t="n">
         <v>0.14128</v>
@@ -17288,7 +17288,7 @@
         </is>
       </c>
       <c r="B1298" t="n">
-        <v>0.132041</v>
+        <v>0.127896</v>
       </c>
       <c r="C1298" t="n">
         <v>0.139073</v>
@@ -17301,7 +17301,7 @@
         </is>
       </c>
       <c r="B1299" t="n">
-        <v>0.134601</v>
+        <v>0.12795</v>
       </c>
       <c r="C1299" t="n">
         <v>0.136865</v>
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>0.137672</v>
+        <v>0.128655</v>
       </c>
       <c r="C1300" t="n">
         <v>0.134658</v>
@@ -17327,7 +17327,7 @@
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>0.138164</v>
+        <v>0.12943</v>
       </c>
       <c r="C1301" t="n">
         <v>0.13245</v>
@@ -17340,7 +17340,7 @@
         </is>
       </c>
       <c r="B1302" t="n">
-        <v>0.13847</v>
+        <v>0.131615</v>
       </c>
       <c r="C1302" t="n">
         <v>0.130243</v>
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="B1303" t="n">
-        <v>0.140769</v>
+        <v>0.132151</v>
       </c>
       <c r="C1303" t="n">
         <v>0.128035</v>
@@ -17366,7 +17366,7 @@
         </is>
       </c>
       <c r="B1304" t="n">
-        <v>0.141333</v>
+        <v>0.136036</v>
       </c>
       <c r="C1304" t="n">
         <v>0.125828</v>
@@ -17379,7 +17379,7 @@
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>0.142609</v>
+        <v>0.136358</v>
       </c>
       <c r="C1305" t="n">
         <v>0.12362</v>
@@ -17392,7 +17392,7 @@
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>0.14385</v>
+        <v>0.13759</v>
       </c>
       <c r="C1306" t="n">
         <v>0.121413</v>
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>0.14392</v>
+        <v>0.140513</v>
       </c>
       <c r="C1307" t="n">
         <v>0.119205</v>
@@ -17418,7 +17418,7 @@
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>0.145727</v>
+        <v>0.142197</v>
       </c>
       <c r="C1308" t="n">
         <v>0.116998</v>
@@ -17431,7 +17431,7 @@
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>0.146567</v>
+        <v>0.143255</v>
       </c>
       <c r="C1309" t="n">
         <v>0.11479</v>
@@ -17444,7 +17444,7 @@
         </is>
       </c>
       <c r="B1310" t="n">
-        <v>0.146941</v>
+        <v>0.145445</v>
       </c>
       <c r="C1310" t="n">
         <v>0.112583</v>
@@ -17457,7 +17457,7 @@
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>0.149321</v>
+        <v>0.147188</v>
       </c>
       <c r="C1311" t="n">
         <v>0.110375</v>
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="B1312" t="n">
-        <v>0.149888</v>
+        <v>0.14954</v>
       </c>
       <c r="C1312" t="n">
         <v>0.108168</v>
@@ -17483,7 +17483,7 @@
         </is>
       </c>
       <c r="B1313" t="n">
-        <v>0.155088</v>
+        <v>0.150473</v>
       </c>
       <c r="C1313" t="n">
         <v>0.10596</v>
@@ -17496,7 +17496,7 @@
         </is>
       </c>
       <c r="B1314" t="n">
-        <v>0.155472</v>
+        <v>0.154884</v>
       </c>
       <c r="C1314" t="n">
         <v>0.103753</v>
@@ -17509,7 +17509,7 @@
         </is>
       </c>
       <c r="B1315" t="n">
-        <v>0.160693</v>
+        <v>0.155326</v>
       </c>
       <c r="C1315" t="n">
         <v>0.101545</v>
@@ -17522,7 +17522,7 @@
         </is>
       </c>
       <c r="B1316" t="n">
-        <v>0.162009</v>
+        <v>0.156308</v>
       </c>
       <c r="C1316" t="n">
         <v>0.099338</v>
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>0.163628</v>
+        <v>0.159189</v>
       </c>
       <c r="C1317" t="n">
         <v>0.09712999999999999</v>
@@ -17548,7 +17548,7 @@
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>0.163628</v>
+        <v>0.159937</v>
       </c>
       <c r="C1318" t="n">
         <v>0.09492299999999999</v>
@@ -17561,7 +17561,7 @@
         </is>
       </c>
       <c r="B1319" t="n">
-        <v>0.163628</v>
+        <v>0.160787</v>
       </c>
       <c r="C1319" t="n">
         <v>0.09271500000000001</v>
@@ -17574,7 +17574,7 @@
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>0.164681</v>
+        <v>0.160787</v>
       </c>
       <c r="C1320" t="n">
         <v>0.09050800000000001</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>0.169377</v>
+        <v>0.160787</v>
       </c>
       <c r="C1321" t="n">
         <v>0.0883</v>
@@ -17600,7 +17600,7 @@
         </is>
       </c>
       <c r="B1322" t="n">
-        <v>0.172993</v>
+        <v>0.161304</v>
       </c>
       <c r="C1322" t="n">
         <v>0.086093</v>
@@ -17613,7 +17613,7 @@
         </is>
       </c>
       <c r="B1323" t="n">
-        <v>0.173351</v>
+        <v>0.162506</v>
       </c>
       <c r="C1323" t="n">
         <v>0.083885</v>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="B1324" t="n">
-        <v>0.175188</v>
+        <v>0.165632</v>
       </c>
       <c r="C1324" t="n">
         <v>0.081678</v>
@@ -17639,7 +17639,7 @@
         </is>
       </c>
       <c r="B1325" t="n">
-        <v>0.175414</v>
+        <v>0.167934</v>
       </c>
       <c r="C1325" t="n">
         <v>0.07947</v>
@@ -17652,7 +17652,7 @@
         </is>
       </c>
       <c r="B1326" t="n">
-        <v>0.176482</v>
+        <v>0.171605</v>
       </c>
       <c r="C1326" t="n">
         <v>0.077263</v>
@@ -17665,7 +17665,7 @@
         </is>
       </c>
       <c r="B1327" t="n">
-        <v>0.176588</v>
+        <v>0.174</v>
       </c>
       <c r="C1327" t="n">
         <v>0.075055</v>
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="B1328" t="n">
-        <v>0.180524</v>
+        <v>0.175567</v>
       </c>
       <c r="C1328" t="n">
         <v>0.072848</v>
@@ -17691,7 +17691,7 @@
         </is>
       </c>
       <c r="B1329" t="n">
-        <v>0.185123</v>
+        <v>0.179741</v>
       </c>
       <c r="C1329" t="n">
         <v>0.07063999999999999</v>
@@ -17704,7 +17704,7 @@
         </is>
       </c>
       <c r="B1330" t="n">
-        <v>0.185158</v>
+        <v>0.186251</v>
       </c>
       <c r="C1330" t="n">
         <v>0.06843299999999999</v>
@@ -17717,7 +17717,7 @@
         </is>
       </c>
       <c r="B1331" t="n">
-        <v>0.18776</v>
+        <v>0.188403</v>
       </c>
       <c r="C1331" t="n">
         <v>0.06622500000000001</v>
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="B1332" t="n">
-        <v>0.194431</v>
+        <v>0.189555</v>
       </c>
       <c r="C1332" t="n">
         <v>0.06401800000000001</v>
@@ -17743,7 +17743,7 @@
         </is>
       </c>
       <c r="B1333" t="n">
-        <v>0.201385</v>
+        <v>0.200924</v>
       </c>
       <c r="C1333" t="n">
         <v>0.06181</v>
@@ -17756,7 +17756,7 @@
         </is>
       </c>
       <c r="B1334" t="n">
-        <v>0.208355</v>
+        <v>0.201739</v>
       </c>
       <c r="C1334" t="n">
         <v>0.059603</v>
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="B1335" t="n">
-        <v>0.210382</v>
+        <v>0.207035</v>
       </c>
       <c r="C1335" t="n">
         <v>0.057395</v>
@@ -17782,7 +17782,7 @@
         </is>
       </c>
       <c r="B1336" t="n">
-        <v>0.210541</v>
+        <v>0.207379</v>
       </c>
       <c r="C1336" t="n">
         <v>0.055188</v>
@@ -17795,7 +17795,7 @@
         </is>
       </c>
       <c r="B1337" t="n">
-        <v>0.211559</v>
+        <v>0.20906</v>
       </c>
       <c r="C1337" t="n">
         <v>0.05298</v>
@@ -17808,7 +17808,7 @@
         </is>
       </c>
       <c r="B1338" t="n">
-        <v>0.213653</v>
+        <v>0.209093</v>
       </c>
       <c r="C1338" t="n">
         <v>0.050773</v>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="B1339" t="n">
-        <v>0.216408</v>
+        <v>0.210949</v>
       </c>
       <c r="C1339" t="n">
         <v>0.048565</v>
@@ -17834,7 +17834,7 @@
         </is>
       </c>
       <c r="B1340" t="n">
-        <v>0.233949</v>
+        <v>0.213076</v>
       </c>
       <c r="C1340" t="n">
         <v>0.046358</v>
@@ -17847,7 +17847,7 @@
         </is>
       </c>
       <c r="B1341" t="n">
-        <v>0.249096</v>
+        <v>0.244236</v>
       </c>
       <c r="C1341" t="n">
         <v>0.04415</v>
@@ -17860,7 +17860,7 @@
         </is>
       </c>
       <c r="B1342" t="n">
-        <v>0.257377</v>
+        <v>0.248813</v>
       </c>
       <c r="C1342" t="n">
         <v>0.041943</v>
@@ -17873,7 +17873,7 @@
         </is>
       </c>
       <c r="B1343" t="n">
-        <v>0.259629</v>
+        <v>0.259635</v>
       </c>
       <c r="C1343" t="n">
         <v>0.039735</v>
@@ -17886,7 +17886,7 @@
         </is>
       </c>
       <c r="B1344" t="n">
-        <v>0.266831</v>
+        <v>0.263217</v>
       </c>
       <c r="C1344" t="n">
         <v>0.037528</v>
@@ -17899,7 +17899,7 @@
         </is>
       </c>
       <c r="B1345" t="n">
-        <v>0.294668</v>
+        <v>0.292447</v>
       </c>
       <c r="C1345" t="n">
         <v>0.03532</v>
@@ -17912,7 +17912,7 @@
         </is>
       </c>
       <c r="B1346" t="n">
-        <v>0.294844</v>
+        <v>0.292741</v>
       </c>
       <c r="C1346" t="n">
         <v>0.033113</v>
@@ -17925,7 +17925,7 @@
         </is>
       </c>
       <c r="B1347" t="n">
-        <v>0.318108</v>
+        <v>0.29812</v>
       </c>
       <c r="C1347" t="n">
         <v>0.030905</v>
@@ -17938,7 +17938,7 @@
         </is>
       </c>
       <c r="B1348" t="n">
-        <v>0.32739</v>
+        <v>0.323661</v>
       </c>
       <c r="C1348" t="n">
         <v>0.028698</v>
@@ -17951,7 +17951,7 @@
         </is>
       </c>
       <c r="B1349" t="n">
-        <v>0.3571</v>
+        <v>0.344032</v>
       </c>
       <c r="C1349" t="n">
         <v>0.02649</v>
@@ -17964,7 +17964,7 @@
         </is>
       </c>
       <c r="B1350" t="n">
-        <v>0.370725</v>
+        <v>0.346406</v>
       </c>
       <c r="C1350" t="n">
         <v>0.024283</v>
@@ -17977,7 +17977,7 @@
         </is>
       </c>
       <c r="B1351" t="n">
-        <v>0.377088</v>
+        <v>0.352617</v>
       </c>
       <c r="C1351" t="n">
         <v>0.022075</v>
@@ -17990,7 +17990,7 @@
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>0.401045</v>
+        <v>0.36528</v>
       </c>
       <c r="C1352" t="n">
         <v>0.019868</v>
@@ -18003,7 +18003,7 @@
         </is>
       </c>
       <c r="B1353" t="n">
-        <v>0.410314</v>
+        <v>0.379355</v>
       </c>
       <c r="C1353" t="n">
         <v>0.01766</v>
@@ -18016,7 +18016,7 @@
         </is>
       </c>
       <c r="B1354" t="n">
-        <v>0.510332</v>
+        <v>0.503632</v>
       </c>
       <c r="C1354" t="n">
         <v>0.015453</v>
@@ -18029,7 +18029,7 @@
         </is>
       </c>
       <c r="B1355" t="n">
-        <v>0.523343</v>
+        <v>0.523254</v>
       </c>
       <c r="C1355" t="n">
         <v>0.013245</v>
@@ -18042,7 +18042,7 @@
         </is>
       </c>
       <c r="B1356" t="n">
-        <v>0.642819</v>
+        <v>0.644</v>
       </c>
       <c r="C1356" t="n">
         <v>0.011038</v>
@@ -18055,7 +18055,7 @@
         </is>
       </c>
       <c r="B1357" t="n">
-        <v>0.665232</v>
+        <v>0.6651280000000001</v>
       </c>
       <c r="C1357" t="n">
         <v>0.008829999999999999</v>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="B1358" t="n">
-        <v>1.005781</v>
+        <v>0.951224</v>
       </c>
       <c r="C1358" t="n">
         <v>0.006623</v>
@@ -18081,7 +18081,7 @@
         </is>
       </c>
       <c r="B1359" t="n">
-        <v>1.057987</v>
+        <v>1.004442</v>
       </c>
       <c r="C1359" t="n">
         <v>0.004415</v>
@@ -18094,7 +18094,7 @@
         </is>
       </c>
       <c r="B1360" t="n">
-        <v>1.268338</v>
+        <v>1.282779</v>
       </c>
       <c r="C1360" t="n">
         <v>0.002208</v>

--- a/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
+++ b/vignettes/vignette-2/tail_exceedance_plot_data.xlsx
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.000876</v>
+        <v>0.000874</v>
       </c>
       <c r="C437" t="n">
         <v>0.988372</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.001448</v>
+        <v>0.001445</v>
       </c>
       <c r="C439" t="n">
         <v>0.983721</v>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>0.001766</v>
+        <v>0.001767</v>
       </c>
       <c r="C441" t="n">
         <v>0.97907</v>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.002107</v>
+        <v>0.002104</v>
       </c>
       <c r="C442" t="n">
         <v>0.9767439999999999</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.002246</v>
+        <v>0.002236</v>
       </c>
       <c r="C443" t="n">
         <v>0.974419</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.002408</v>
+        <v>0.002409</v>
       </c>
       <c r="C444" t="n">
         <v>0.972093</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.002489</v>
+        <v>0.002492</v>
       </c>
       <c r="C445" t="n">
         <v>0.969767</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.002642</v>
+        <v>0.002646</v>
       </c>
       <c r="C446" t="n">
         <v>0.967442</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.002712</v>
+        <v>0.002713</v>
       </c>
       <c r="C447" t="n">
         <v>0.965116</v>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.003063</v>
+        <v>0.003056</v>
       </c>
       <c r="C448" t="n">
         <v>0.962791</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>0.003404</v>
+        <v>0.003395</v>
       </c>
       <c r="C449" t="n">
         <v>0.960465</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.003468</v>
+        <v>0.003464</v>
       </c>
       <c r="C450" t="n">
         <v>0.95814</v>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>0.003708</v>
+        <v>0.003709</v>
       </c>
       <c r="C451" t="n">
         <v>0.9558140000000001</v>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.003806</v>
+        <v>0.003804</v>
       </c>
       <c r="C452" t="n">
         <v>0.953488</v>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.003967</v>
+        <v>0.00397</v>
       </c>
       <c r="C453" t="n">
         <v>0.951163</v>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>0.003996</v>
+        <v>0.003993</v>
       </c>
       <c r="C454" t="n">
         <v>0.948837</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.004029</v>
+        <v>0.00403</v>
       </c>
       <c r="C455" t="n">
         <v>0.946512</v>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.004077</v>
+        <v>0.004078</v>
       </c>
       <c r="C456" t="n">
         <v>0.944186</v>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.004188</v>
+        <v>0.004175</v>
       </c>
       <c r="C457" t="n">
         <v>0.94186</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.004227</v>
+        <v>0.004214</v>
       </c>
       <c r="C458" t="n">
         <v>0.939535</v>
@@ -6381,7 +6381,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.004277</v>
+        <v>0.004279</v>
       </c>
       <c r="C459" t="n">
         <v>0.937209</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.004363</v>
+        <v>0.004353</v>
       </c>
       <c r="C460" t="n">
         <v>0.934884</v>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.004368</v>
+        <v>0.004361</v>
       </c>
       <c r="C461" t="n">
         <v>0.932558</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.004598</v>
+        <v>0.004595</v>
       </c>
       <c r="C462" t="n">
         <v>0.930233</v>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.004662</v>
+        <v>0.004666</v>
       </c>
       <c r="C463" t="n">
         <v>0.927907</v>
@@ -6446,7 +6446,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.004924</v>
+        <v>0.004929</v>
       </c>
       <c r="C464" t="n">
         <v>0.925581</v>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>0.005037</v>
+        <v>0.005034</v>
       </c>
       <c r="C466" t="n">
         <v>0.92093</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>0.005147</v>
+        <v>0.005148</v>
       </c>
       <c r="C467" t="n">
         <v>0.918605</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>0.006478</v>
+        <v>0.006467</v>
       </c>
       <c r="C468" t="n">
         <v>0.916279</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.006774</v>
+        <v>0.006771</v>
       </c>
       <c r="C469" t="n">
         <v>0.913953</v>
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>0.007147</v>
+        <v>0.007141</v>
       </c>
       <c r="C470" t="n">
         <v>0.911628</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.00725</v>
+        <v>0.007249</v>
       </c>
       <c r="C471" t="n">
         <v>0.9093020000000001</v>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.007447</v>
+        <v>0.007451</v>
       </c>
       <c r="C472" t="n">
         <v>0.906977</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.007849</v>
+        <v>0.007853000000000001</v>
       </c>
       <c r="C473" t="n">
         <v>0.904651</v>
@@ -6576,7 +6576,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.008194</v>
+        <v>0.008199</v>
       </c>
       <c r="C474" t="n">
         <v>0.902326</v>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.008215</v>
+        <v>0.008203999999999999</v>
       </c>
       <c r="C475" t="n">
         <v>0.9</v>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.008342</v>
+        <v>0.008337000000000001</v>
       </c>
       <c r="C476" t="n">
         <v>0.897674</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.008451</v>
+        <v>0.008455000000000001</v>
       </c>
       <c r="C477" t="n">
         <v>0.895349</v>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>0.008717000000000001</v>
+        <v>0.008671999999999999</v>
       </c>
       <c r="C478" t="n">
         <v>0.893023</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.00877</v>
+        <v>0.008777</v>
       </c>
       <c r="C479" t="n">
         <v>0.890698</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.008796</v>
+        <v>0.008803999999999999</v>
       </c>
       <c r="C480" t="n">
         <v>0.8883720000000001</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.008848</v>
+        <v>0.008836</v>
       </c>
       <c r="C481" t="n">
         <v>0.886047</v>
@@ -6680,7 +6680,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>0.008867999999999999</v>
+        <v>0.008840000000000001</v>
       </c>
       <c r="C482" t="n">
         <v>0.883721</v>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>0.009214999999999999</v>
+        <v>0.009216999999999999</v>
       </c>
       <c r="C483" t="n">
         <v>0.881395</v>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.009447000000000001</v>
+        <v>0.009454000000000001</v>
       </c>
       <c r="C484" t="n">
         <v>0.87907</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.009613999999999999</v>
+        <v>0.009611</v>
       </c>
       <c r="C485" t="n">
         <v>0.876744</v>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>0.009634999999999999</v>
+        <v>0.009655</v>
       </c>
       <c r="C486" t="n">
         <v>0.8744189999999999</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>0.009714</v>
+        <v>0.009716000000000001</v>
       </c>
       <c r="C487" t="n">
         <v>0.872093</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>0.009842999999999999</v>
+        <v>0.009847</v>
       </c>
       <c r="C488" t="n">
         <v>0.869767</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>0.00996</v>
+        <v>0.009967999999999999</v>
       </c>
       <c r="C489" t="n">
         <v>0.867442</v>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>0.010309</v>
+        <v>0.010321</v>
       </c>
       <c r="C490" t="n">
         <v>0.865116</v>
@@ -6797,7 +6797,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>0.010382</v>
+        <v>0.010388</v>
       </c>
       <c r="C491" t="n">
         <v>0.862791</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>0.010558</v>
+        <v>0.01053</v>
       </c>
       <c r="C492" t="n">
         <v>0.860465</v>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>0.01068</v>
+        <v>0.010674</v>
       </c>
       <c r="C493" t="n">
         <v>0.85814</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>0.01086</v>
+        <v>0.010852</v>
       </c>
       <c r="C494" t="n">
         <v>0.855814</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>0.011248</v>
+        <v>0.011251</v>
       </c>
       <c r="C495" t="n">
         <v>0.853488</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>0.011321</v>
+        <v>0.011312</v>
       </c>
       <c r="C496" t="n">
         <v>0.851163</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>0.011435</v>
+        <v>0.011422</v>
       </c>
       <c r="C497" t="n">
         <v>0.848837</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>0.011483</v>
+        <v>0.011484</v>
       </c>
       <c r="C498" t="n">
         <v>0.846512</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>0.011569</v>
+        <v>0.011524</v>
       </c>
       <c r="C499" t="n">
         <v>0.844186</v>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>0.011759</v>
+        <v>0.011778</v>
       </c>
       <c r="C500" t="n">
         <v>0.8418600000000001</v>
@@ -6927,7 +6927,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>0.012054</v>
+        <v>0.012055</v>
       </c>
       <c r="C501" t="n">
         <v>0.839535</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>0.01209</v>
+        <v>0.012106</v>
       </c>
       <c r="C502" t="n">
         <v>0.837209</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>0.012511</v>
+        <v>0.012487</v>
       </c>
       <c r="C503" t="n">
         <v>0.834884</v>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>0.013017</v>
+        <v>0.013004</v>
       </c>
       <c r="C504" t="n">
         <v>0.832558</v>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>0.013042</v>
+        <v>0.013056</v>
       </c>
       <c r="C505" t="n">
         <v>0.830233</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>0.013385</v>
+        <v>0.013387</v>
       </c>
       <c r="C506" t="n">
         <v>0.8279069999999999</v>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>0.013516</v>
+        <v>0.013505</v>
       </c>
       <c r="C507" t="n">
         <v>0.825581</v>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>0.013615</v>
+        <v>0.013621</v>
       </c>
       <c r="C508" t="n">
         <v>0.823256</v>
@@ -7031,7 +7031,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>0.013616</v>
+        <v>0.013628</v>
       </c>
       <c r="C509" t="n">
         <v>0.82093</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>0.013755</v>
+        <v>0.013757</v>
       </c>
       <c r="C510" t="n">
         <v>0.818605</v>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>0.013837</v>
+        <v>0.01385</v>
       </c>
       <c r="C511" t="n">
         <v>0.816279</v>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>0.013866</v>
+        <v>0.013857</v>
       </c>
       <c r="C512" t="n">
         <v>0.813953</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>0.014011</v>
+        <v>0.014026</v>
       </c>
       <c r="C513" t="n">
         <v>0.811628</v>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>0.014076</v>
+        <v>0.014081</v>
       </c>
       <c r="C514" t="n">
         <v>0.809302</v>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>0.014095</v>
+        <v>0.014091</v>
       </c>
       <c r="C515" t="n">
         <v>0.8069770000000001</v>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>0.014246</v>
+        <v>0.014248</v>
       </c>
       <c r="C516" t="n">
         <v>0.804651</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>0.014781</v>
+        <v>0.014772</v>
       </c>
       <c r="C517" t="n">
         <v>0.802326</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>0.015132</v>
+        <v>0.015136</v>
       </c>
       <c r="C518" t="n">
         <v>0.8</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>0.015283</v>
+        <v>0.0153</v>
       </c>
       <c r="C519" t="n">
         <v>0.797674</v>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>0.015449</v>
+        <v>0.015438</v>
       </c>
       <c r="C520" t="n">
         <v>0.795349</v>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>0.015654</v>
+        <v>0.015677</v>
       </c>
       <c r="C521" t="n">
         <v>0.793023</v>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>0.016222</v>
+        <v>0.016211</v>
       </c>
       <c r="C522" t="n">
         <v>0.790698</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>0.016362</v>
+        <v>0.016339</v>
       </c>
       <c r="C523" t="n">
         <v>0.788372</v>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>0.016396</v>
+        <v>0.016413</v>
       </c>
       <c r="C524" t="n">
         <v>0.7860470000000001</v>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>0.016511</v>
+        <v>0.016506</v>
       </c>
       <c r="C525" t="n">
         <v>0.783721</v>
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>0.016533</v>
+        <v>0.016553</v>
       </c>
       <c r="C526" t="n">
         <v>0.781395</v>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>0.016754</v>
+        <v>0.016758</v>
       </c>
       <c r="C527" t="n">
         <v>0.77907</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>0.017021</v>
+        <v>0.017015</v>
       </c>
       <c r="C528" t="n">
         <v>0.776744</v>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>0.017309</v>
+        <v>0.017297</v>
       </c>
       <c r="C529" t="n">
         <v>0.774419</v>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>0.017343</v>
+        <v>0.017328</v>
       </c>
       <c r="C530" t="n">
         <v>0.772093</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>0.017418</v>
+        <v>0.017399</v>
       </c>
       <c r="C531" t="n">
         <v>0.769767</v>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>0.017449</v>
+        <v>0.017443</v>
       </c>
       <c r="C532" t="n">
         <v>0.767442</v>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>0.017758</v>
+        <v>0.017768</v>
       </c>
       <c r="C533" t="n">
         <v>0.765116</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>0.018159</v>
+        <v>0.018168</v>
       </c>
       <c r="C534" t="n">
         <v>0.762791</v>
@@ -7369,7 +7369,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>0.01829</v>
+        <v>0.01828</v>
       </c>
       <c r="C535" t="n">
         <v>0.7604649999999999</v>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>0.018724</v>
+        <v>0.018581</v>
       </c>
       <c r="C536" t="n">
         <v>0.75814</v>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>0.019036</v>
+        <v>0.01898</v>
       </c>
       <c r="C537" t="n">
         <v>0.755814</v>
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>0.019146</v>
+        <v>0.019128</v>
       </c>
       <c r="C538" t="n">
         <v>0.753488</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>0.01928</v>
+        <v>0.019279</v>
       </c>
       <c r="C539" t="n">
         <v>0.751163</v>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>0.019922</v>
+        <v>0.019939</v>
       </c>
       <c r="C540" t="n">
         <v>0.748837</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>0.019995</v>
+        <v>0.020016</v>
       </c>
       <c r="C541" t="n">
         <v>0.746512</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>0.020216</v>
+        <v>0.020232</v>
       </c>
       <c r="C542" t="n">
         <v>0.744186</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>0.021327</v>
+        <v>0.021336</v>
       </c>
       <c r="C543" t="n">
         <v>0.74186</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>0.021426</v>
+        <v>0.021447</v>
       </c>
       <c r="C544" t="n">
         <v>0.7395350000000001</v>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>0.021628</v>
+        <v>0.021626</v>
       </c>
       <c r="C545" t="n">
         <v>0.737209</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>0.021643</v>
+        <v>0.021647</v>
       </c>
       <c r="C546" t="n">
         <v>0.734884</v>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>0.021972</v>
+        <v>0.021998</v>
       </c>
       <c r="C547" t="n">
         <v>0.732558</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>0.022071</v>
+        <v>0.022079</v>
       </c>
       <c r="C548" t="n">
         <v>0.730233</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>0.022437</v>
+        <v>0.022436</v>
       </c>
       <c r="C549" t="n">
         <v>0.727907</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>0.02245</v>
+        <v>0.022442</v>
       </c>
       <c r="C550" t="n">
         <v>0.725581</v>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>0.02285</v>
+        <v>0.022832</v>
       </c>
       <c r="C551" t="n">
         <v>0.723256</v>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>0.02286</v>
+        <v>0.022869</v>
       </c>
       <c r="C552" t="n">
         <v>0.72093</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="B553" t="n">
-        <v>0.023037</v>
+        <v>0.023062</v>
       </c>
       <c r="C553" t="n">
         <v>0.718605</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>0.023358</v>
+        <v>0.023381</v>
       </c>
       <c r="C555" t="n">
         <v>0.7139529999999999</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B556" t="n">
-        <v>0.023903</v>
+        <v>0.023901</v>
       </c>
       <c r="C556" t="n">
         <v>0.711628</v>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>0.024215</v>
+        <v>0.02413</v>
       </c>
       <c r="C557" t="n">
         <v>0.709302</v>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>0.024319</v>
+        <v>0.024322</v>
       </c>
       <c r="C558" t="n">
         <v>0.706977</v>
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>0.024603</v>
+        <v>0.024629</v>
       </c>
       <c r="C559" t="n">
         <v>0.704651</v>
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>0.024668</v>
+        <v>0.024657</v>
       </c>
       <c r="C560" t="n">
         <v>0.702326</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>0.024713</v>
+        <v>0.024685</v>
       </c>
       <c r="C561" t="n">
         <v>0.7</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>0.024716</v>
+        <v>0.024728</v>
       </c>
       <c r="C562" t="n">
         <v>0.697674</v>
@@ -7733,7 +7733,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>0.024741</v>
+        <v>0.024769</v>
       </c>
       <c r="C563" t="n">
         <v>0.695349</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>0.024814</v>
+        <v>0.024804</v>
       </c>
       <c r="C564" t="n">
         <v>0.6930229999999999</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>0.02515</v>
+        <v>0.025156</v>
       </c>
       <c r="C565" t="n">
         <v>0.690698</v>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>0.025212</v>
+        <v>0.025231</v>
       </c>
       <c r="C566" t="n">
         <v>0.688372</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>0.02567</v>
+        <v>0.025683</v>
       </c>
       <c r="C567" t="n">
         <v>0.686047</v>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>0.025915</v>
+        <v>0.025931</v>
       </c>
       <c r="C568" t="n">
         <v>0.683721</v>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>0.026163</v>
+        <v>0.026183</v>
       </c>
       <c r="C569" t="n">
         <v>0.681395</v>
@@ -7824,7 +7824,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>0.026368</v>
+        <v>0.02636</v>
       </c>
       <c r="C570" t="n">
         <v>0.67907</v>
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>0.026467</v>
+        <v>0.026473</v>
       </c>
       <c r="C571" t="n">
         <v>0.676744</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>0.026492</v>
+        <v>0.0265</v>
       </c>
       <c r="C572" t="n">
         <v>0.674419</v>
@@ -7863,7 +7863,7 @@
         </is>
       </c>
       <c r="B573" t="n">
-        <v>0.027092</v>
+        <v>0.027034</v>
       </c>
       <c r="C573" t="n">
         <v>0.6720930000000001</v>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>0.027214</v>
+        <v>0.027193</v>
       </c>
       <c r="C574" t="n">
         <v>0.669767</v>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>0.02748</v>
+        <v>0.027491</v>
       </c>
       <c r="C575" t="n">
         <v>0.667442</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>0.027545</v>
+        <v>0.027495</v>
       </c>
       <c r="C576" t="n">
         <v>0.665116</v>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>0.027673</v>
+        <v>0.027675</v>
       </c>
       <c r="C577" t="n">
         <v>0.662791</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>0.027856</v>
+        <v>0.027807</v>
       </c>
       <c r="C578" t="n">
         <v>0.660465</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>0.027913</v>
+        <v>0.027949</v>
       </c>
       <c r="C579" t="n">
         <v>0.6581399999999999</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>0.028089</v>
+        <v>0.028107</v>
       </c>
       <c r="C580" t="n">
         <v>0.655814</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>0.028231</v>
+        <v>0.028236</v>
       </c>
       <c r="C581" t="n">
         <v>0.653488</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>0.029038</v>
+        <v>0.028999</v>
       </c>
       <c r="C583" t="n">
         <v>0.648837</v>
@@ -8006,7 +8006,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>0.029106</v>
+        <v>0.029048</v>
       </c>
       <c r="C584" t="n">
         <v>0.646512</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>0.0293</v>
+        <v>0.029317</v>
       </c>
       <c r="C585" t="n">
         <v>0.644186</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>0.029517</v>
+        <v>0.029547</v>
       </c>
       <c r="C586" t="n">
         <v>0.64186</v>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>0.029567</v>
+        <v>0.029573</v>
       </c>
       <c r="C587" t="n">
         <v>0.639535</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>0.029853</v>
+        <v>0.029829</v>
       </c>
       <c r="C588" t="n">
         <v>0.637209</v>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>0.030265</v>
+        <v>0.030298</v>
       </c>
       <c r="C589" t="n">
         <v>0.634884</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>0.030596</v>
+        <v>0.03062</v>
       </c>
       <c r="C590" t="n">
         <v>0.632558</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>0.030606</v>
+        <v>0.030646</v>
       </c>
       <c r="C591" t="n">
         <v>0.630233</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>0.030864</v>
+        <v>0.030856</v>
       </c>
       <c r="C592" t="n">
         <v>0.627907</v>
@@ -8123,7 +8123,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>0.031233</v>
+        <v>0.031186</v>
       </c>
       <c r="C593" t="n">
         <v>0.6255810000000001</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B594" t="n">
-        <v>0.031523</v>
+        <v>0.031495</v>
       </c>
       <c r="C594" t="n">
         <v>0.623256</v>
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>0.031722</v>
+        <v>0.031742</v>
       </c>
       <c r="C595" t="n">
         <v>0.62093</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>0.031892</v>
+        <v>0.031929</v>
       </c>
       <c r="C596" t="n">
         <v>0.618605</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>0.031984</v>
+        <v>0.031985</v>
       </c>
       <c r="C597" t="n">
         <v>0.616279</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>0.032475</v>
+        <v>0.032499</v>
       </c>
       <c r="C599" t="n">
         <v>0.6116279999999999</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>0.032703</v>
+        <v>0.032675</v>
       </c>
       <c r="C600" t="n">
         <v>0.609302</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>0.032738</v>
+        <v>0.032757</v>
       </c>
       <c r="C601" t="n">
         <v>0.606977</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>0.032768</v>
+        <v>0.032786</v>
       </c>
       <c r="C602" t="n">
         <v>0.604651</v>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>0.033026</v>
+        <v>0.032984</v>
       </c>
       <c r="C603" t="n">
         <v>0.602326</v>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>0.033105</v>
+        <v>0.033123</v>
       </c>
       <c r="C604" t="n">
         <v>0.6</v>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>0.033309</v>
+        <v>0.033323</v>
       </c>
       <c r="C605" t="n">
         <v>0.597674</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>0.033475</v>
+        <v>0.033427</v>
       </c>
       <c r="C606" t="n">
         <v>0.595349</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>0.033501</v>
+        <v>0.033506</v>
       </c>
       <c r="C607" t="n">
         <v>0.593023</v>
@@ -8318,7 +8318,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>0.033562</v>
+        <v>0.033559</v>
       </c>
       <c r="C608" t="n">
         <v>0.5906979999999999</v>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="B609" t="n">
-        <v>0.033939</v>
+        <v>0.033847</v>
       </c>
       <c r="C609" t="n">
         <v>0.588372</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>0.034207</v>
+        <v>0.034233</v>
       </c>
       <c r="C610" t="n">
         <v>0.586047</v>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>0.034712</v>
+        <v>0.034703</v>
       </c>
       <c r="C611" t="n">
         <v>0.583721</v>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>0.034925</v>
+        <v>0.03481</v>
       </c>
       <c r="C612" t="n">
         <v>0.581395</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>0.034955</v>
+        <v>0.034936</v>
       </c>
       <c r="C613" t="n">
         <v>0.57907</v>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>0.035036</v>
+        <v>0.034975</v>
       </c>
       <c r="C614" t="n">
         <v>0.576744</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>0.035039</v>
+        <v>0.035029</v>
       </c>
       <c r="C615" t="n">
         <v>0.574419</v>
@@ -8422,7 +8422,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>0.035443</v>
+        <v>0.035448</v>
       </c>
       <c r="C616" t="n">
         <v>0.572093</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>0.035697</v>
+        <v>0.035712</v>
       </c>
       <c r="C617" t="n">
         <v>0.569767</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>0.035798</v>
+        <v>0.035738</v>
       </c>
       <c r="C618" t="n">
         <v>0.567442</v>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>0.036127</v>
+        <v>0.03605</v>
       </c>
       <c r="C619" t="n">
         <v>0.565116</v>
@@ -8474,7 +8474,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>0.036297</v>
+        <v>0.036264</v>
       </c>
       <c r="C620" t="n">
         <v>0.562791</v>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>0.036581</v>
+        <v>0.036584</v>
       </c>
       <c r="C621" t="n">
         <v>0.560465</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>0.036594</v>
+        <v>0.036626</v>
       </c>
       <c r="C622" t="n">
         <v>0.55814</v>
@@ -8513,7 +8513,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>0.036883</v>
+        <v>0.036924</v>
       </c>
       <c r="C623" t="n">
         <v>0.555814</v>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="B624" t="n">
-        <v>0.037189</v>
+        <v>0.037245</v>
       </c>
       <c r="C624" t="n">
         <v>0.553488</v>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="B625" t="n">
-        <v>0.037258</v>
+        <v>0.037249</v>
       </c>
       <c r="C625" t="n">
         <v>0.551163</v>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>0.037312</v>
+        <v>0.037392</v>
       </c>
       <c r="C626" t="n">
         <v>0.548837</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>0.037536</v>
+        <v>0.037578</v>
       </c>
       <c r="C627" t="n">
         <v>0.546512</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>0.037693</v>
+        <v>0.037663</v>
       </c>
       <c r="C628" t="n">
         <v>0.5441859999999999</v>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>0.037694</v>
+        <v>0.037675</v>
       </c>
       <c r="C629" t="n">
         <v>0.54186</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B630" t="n">
-        <v>0.038463</v>
+        <v>0.038478</v>
       </c>
       <c r="C630" t="n">
         <v>0.539535</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>0.038759</v>
+        <v>0.038782</v>
       </c>
       <c r="C631" t="n">
         <v>0.537209</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>0.039032</v>
+        <v>0.039012</v>
       </c>
       <c r="C632" t="n">
         <v>0.534884</v>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>0.039772</v>
+        <v>0.039729</v>
       </c>
       <c r="C633" t="n">
         <v>0.532558</v>
@@ -8656,7 +8656,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>0.039972</v>
+        <v>0.039888</v>
       </c>
       <c r="C634" t="n">
         <v>0.530233</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>0.039989</v>
+        <v>0.040001</v>
       </c>
       <c r="C635" t="n">
         <v>0.527907</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>0.040255</v>
+        <v>0.040179</v>
       </c>
       <c r="C636" t="n">
         <v>0.525581</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>0.040999</v>
+        <v>0.040986</v>
       </c>
       <c r="C637" t="n">
         <v>0.5232560000000001</v>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>0.041656</v>
+        <v>0.04161</v>
       </c>
       <c r="C638" t="n">
         <v>0.52093</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>0.041713</v>
+        <v>0.041724</v>
       </c>
       <c r="C639" t="n">
         <v>0.518605</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>0.042387</v>
+        <v>0.042429</v>
       </c>
       <c r="C641" t="n">
         <v>0.513953</v>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>0.042463</v>
+        <v>0.042489</v>
       </c>
       <c r="C642" t="n">
         <v>0.511628</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>0.043175</v>
+        <v>0.043148</v>
       </c>
       <c r="C643" t="n">
         <v>0.509302</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>0.043444</v>
+        <v>0.043482</v>
       </c>
       <c r="C644" t="n">
         <v>0.506977</v>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>0.043856</v>
+        <v>0.043813</v>
       </c>
       <c r="C645" t="n">
         <v>0.504651</v>
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>0.043883</v>
+        <v>0.043849</v>
       </c>
       <c r="C646" t="n">
         <v>0.5023260000000001</v>
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>0.043887</v>
+        <v>0.043928</v>
       </c>
       <c r="C647" t="n">
         <v>0.5</v>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>0.044194</v>
+        <v>0.044131</v>
       </c>
       <c r="C648" t="n">
         <v>0.497674</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>0.044377</v>
+        <v>0.044359</v>
       </c>
       <c r="C649" t="n">
         <v>0.495349</v>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>0.045507</v>
+        <v>0.045525</v>
       </c>
       <c r="C650" t="n">
         <v>0.493023</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>0.045564</v>
+        <v>0.045567</v>
       </c>
       <c r="C651" t="n">
         <v>0.490698</v>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>0.046314</v>
+        <v>0.046194</v>
       </c>
       <c r="C652" t="n">
         <v>0.488372</v>
@@ -8903,7 +8903,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>0.046508</v>
+        <v>0.04653</v>
       </c>
       <c r="C653" t="n">
         <v>0.486047</v>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>0.046526</v>
+        <v>0.046559</v>
       </c>
       <c r="C654" t="n">
         <v>0.483721</v>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="B655" t="n">
-        <v>0.046767</v>
+        <v>0.046801</v>
       </c>
       <c r="C655" t="n">
         <v>0.481395</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>0.046854</v>
+        <v>0.04687</v>
       </c>
       <c r="C656" t="n">
         <v>0.47907</v>
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B657" t="n">
-        <v>0.047828</v>
+        <v>0.047842</v>
       </c>
       <c r="C657" t="n">
         <v>0.476744</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>0.047854</v>
+        <v>0.047905</v>
       </c>
       <c r="C658" t="n">
         <v>0.474419</v>
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>0.04812</v>
+        <v>0.048152</v>
       </c>
       <c r="C659" t="n">
         <v>0.472093</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>0.048459</v>
+        <v>0.048529</v>
       </c>
       <c r="C660" t="n">
         <v>0.469767</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>0.048576</v>
+        <v>0.048647</v>
       </c>
       <c r="C661" t="n">
         <v>0.467442</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>0.049439</v>
+        <v>0.049461</v>
       </c>
       <c r="C662" t="n">
         <v>0.465116</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>0.049619</v>
+        <v>0.049672</v>
       </c>
       <c r="C663" t="n">
         <v>0.462791</v>
@@ -9046,7 +9046,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>0.04981</v>
+        <v>0.049869</v>
       </c>
       <c r="C664" t="n">
         <v>0.460465</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="B665" t="n">
-        <v>0.050527</v>
+        <v>0.050522</v>
       </c>
       <c r="C665" t="n">
         <v>0.45814</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>0.05193</v>
+        <v>0.051985</v>
       </c>
       <c r="C666" t="n">
         <v>0.455814</v>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>0.052161</v>
+        <v>0.052204</v>
       </c>
       <c r="C667" t="n">
         <v>0.453488</v>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>0.052677</v>
+        <v>0.052592</v>
       </c>
       <c r="C668" t="n">
         <v>0.451163</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="B669" t="n">
-        <v>0.052758</v>
+        <v>0.052806</v>
       </c>
       <c r="C669" t="n">
         <v>0.448837</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>0.05314</v>
+        <v>0.053118</v>
       </c>
       <c r="C670" t="n">
         <v>0.446512</v>
@@ -9137,7 +9137,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>0.053367</v>
+        <v>0.053432</v>
       </c>
       <c r="C671" t="n">
         <v>0.444186</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>0.053659</v>
+        <v>0.053636</v>
       </c>
       <c r="C672" t="n">
         <v>0.44186</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>0.053746</v>
+        <v>0.053732</v>
       </c>
       <c r="C673" t="n">
         <v>0.439535</v>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>0.054008</v>
+        <v>0.053979</v>
       </c>
       <c r="C674" t="n">
         <v>0.437209</v>
@@ -9189,7 +9189,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>0.054366</v>
+        <v>0.054254</v>
       </c>
       <c r="C675" t="n">
         <v>0.434884</v>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="B676" t="n">
-        <v>0.054997</v>
+        <v>0.054991</v>
       </c>
       <c r="C676" t="n">
         <v>0.432558</v>
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>0.055209</v>
+        <v>0.055176</v>
       </c>
       <c r="C677" t="n">
         <v>0.430233</v>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>0.05568</v>
+        <v>0.055705</v>
       </c>
       <c r="C678" t="n">
         <v>0.427907</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="B679" t="n">
-        <v>0.055767</v>
+        <v>0.055837</v>
       </c>
       <c r="C679" t="n">
         <v>0.425581</v>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>0.056157</v>
+        <v>0.056162</v>
       </c>
       <c r="C680" t="n">
         <v>0.423256</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>0.056228</v>
+        <v>0.056214</v>
       </c>
       <c r="C681" t="n">
         <v>0.42093</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>0.056542</v>
+        <v>0.056514</v>
       </c>
       <c r="C682" t="n">
         <v>0.418605</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>0.056551</v>
+        <v>0.05658</v>
       </c>
       <c r="C683" t="n">
         <v>0.416279</v>
@@ -9306,7 +9306,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0.056571</v>
+        <v>0.056604</v>
       </c>
       <c r="C684" t="n">
         <v>0.413953</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>0.056646</v>
+        <v>0.056699</v>
       </c>
       <c r="C685" t="n">
         <v>0.411628</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>0.057088</v>
+        <v>0.057086</v>
       </c>
       <c r="C686" t="n">
         <v>0.409302</v>
@@ -9345,7 +9345,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0.057615</v>
+        <v>0.057674</v>
       </c>
       <c r="C687" t="n">
         <v>0.406977</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0.057876</v>
+        <v>0.057737</v>
       </c>
       <c r="C688" t="n">
         <v>0.404651</v>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>0.058578</v>
+        <v>0.058604</v>
       </c>
       <c r="C689" t="n">
         <v>0.402326</v>
@@ -9384,7 +9384,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>0.058753</v>
+        <v>0.058661</v>
       </c>
       <c r="C690" t="n">
         <v>0.4</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>0.059495</v>
+        <v>0.059485</v>
       </c>
       <c r="C691" t="n">
         <v>0.397674</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>0.059601</v>
+        <v>0.059602</v>
       </c>
       <c r="C692" t="n">
         <v>0.395349</v>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="B693" t="n">
-        <v>0.059645</v>
+        <v>0.059701</v>
       </c>
       <c r="C693" t="n">
         <v>0.393023</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>0.059726</v>
+        <v>0.059742</v>
       </c>
       <c r="C694" t="n">
         <v>0.390698</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>0.060099</v>
+        <v>0.059954</v>
       </c>
       <c r="C695" t="n">
         <v>0.388372</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>0.060498</v>
+        <v>0.060576</v>
       </c>
       <c r="C696" t="n">
         <v>0.386047</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>0.060988</v>
+        <v>0.061009</v>
       </c>
       <c r="C697" t="n">
         <v>0.383721</v>
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>0.061218</v>
+        <v>0.06121</v>
       </c>
       <c r="C698" t="n">
         <v>0.381395</v>
@@ -9501,7 +9501,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>0.061353</v>
+        <v>0.061356</v>
       </c>
       <c r="C699" t="n">
         <v>0.37907</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>0.061536</v>
+        <v>0.061505</v>
       </c>
       <c r="C700" t="n">
         <v>0.376744</v>
@@ -9527,7 +9527,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>0.061592</v>
+        <v>0.061624</v>
       </c>
       <c r="C701" t="n">
         <v>0.374419</v>
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>0.061758</v>
+        <v>0.06175</v>
       </c>
       <c r="C702" t="n">
         <v>0.372093</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>0.062379</v>
+        <v>0.062114</v>
       </c>
       <c r="C703" t="n">
         <v>0.369767</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>0.062706</v>
+        <v>0.062778</v>
       </c>
       <c r="C704" t="n">
         <v>0.367442</v>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>0.062745</v>
+        <v>0.062805</v>
       </c>
       <c r="C705" t="n">
         <v>0.365116</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0.062863</v>
+        <v>0.062929</v>
       </c>
       <c r="C706" t="n">
         <v>0.362791</v>
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>0.062995</v>
+        <v>0.06304</v>
       </c>
       <c r="C707" t="n">
         <v>0.360465</v>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>0.063109</v>
+        <v>0.06306200000000001</v>
       </c>
       <c r="C708" t="n">
         <v>0.35814</v>
@@ -9631,7 +9631,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0.063177</v>
+        <v>0.063137</v>
       </c>
       <c r="C709" t="n">
         <v>0.355814</v>
@@ -9644,7 +9644,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>0.063501</v>
+        <v>0.063496</v>
       </c>
       <c r="C710" t="n">
         <v>0.353488</v>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0.06392200000000001</v>
+        <v>0.063989</v>
       </c>
       <c r="C711" t="n">
         <v>0.351163</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>0.06438199999999999</v>
+        <v>0.064362</v>
       </c>
       <c r="C712" t="n">
         <v>0.348837</v>
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>0.06474000000000001</v>
+        <v>0.06482</v>
       </c>
       <c r="C713" t="n">
         <v>0.346512</v>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>0.065053</v>
+        <v>0.065012</v>
       </c>
       <c r="C714" t="n">
         <v>0.344186</v>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>0.065066</v>
+        <v>0.06507400000000001</v>
       </c>
       <c r="C715" t="n">
         <v>0.34186</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>0.065138</v>
+        <v>0.065208</v>
       </c>
       <c r="C716" t="n">
         <v>0.339535</v>
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>0.065722</v>
+        <v>0.065694</v>
       </c>
       <c r="C717" t="n">
         <v>0.337209</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>0.06576600000000001</v>
+        <v>0.06576799999999999</v>
       </c>
       <c r="C718" t="n">
         <v>0.334884</v>
@@ -9761,7 +9761,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>0.06597600000000001</v>
+        <v>0.065995</v>
       </c>
       <c r="C719" t="n">
         <v>0.332558</v>
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>0.06598</v>
+        <v>0.066012</v>
       </c>
       <c r="C720" t="n">
         <v>0.330233</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>0.06600499999999999</v>
+        <v>0.066056</v>
       </c>
       <c r="C721" t="n">
         <v>0.327907</v>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>0.066108</v>
+        <v>0.06615600000000001</v>
       </c>
       <c r="C722" t="n">
         <v>0.325581</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>0.068102</v>
+        <v>0.06805</v>
       </c>
       <c r="C723" t="n">
         <v>0.323256</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>0.06940200000000001</v>
+        <v>0.06943199999999999</v>
       </c>
       <c r="C724" t="n">
         <v>0.32093</v>
@@ -9839,7 +9839,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>0.06951400000000001</v>
+        <v>0.069618</v>
       </c>
       <c r="C725" t="n">
         <v>0.318605</v>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>0.06974900000000001</v>
+        <v>0.069783</v>
       </c>
       <c r="C726" t="n">
         <v>0.316279</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B727" t="n">
-        <v>0.069885</v>
+        <v>0.069816</v>
       </c>
       <c r="C727" t="n">
         <v>0.313953</v>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>0.070397</v>
+        <v>0.070436</v>
       </c>
       <c r="C728" t="n">
         <v>0.311628</v>
@@ -9891,7 +9891,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>0.07069599999999999</v>
+        <v>0.070814</v>
       </c>
       <c r="C729" t="n">
         <v>0.309302</v>
@@ -9904,7 +9904,7 @@
         </is>
       </c>
       <c r="B730" t="n">
-        <v>0.07101499999999999</v>
+        <v>0.070868</v>
       </c>
       <c r="C730" t="n">
         <v>0.306977</v>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>0.071968</v>
+        <v>0.071945</v>
       </c>
       <c r="C731" t="n">
         <v>0.304651</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>0.072087</v>
+        <v>0.07205400000000001</v>
       </c>
       <c r="C732" t="n">
         <v>0.302326</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>0.07281700000000001</v>
+        <v>0.072392</v>
       </c>
       <c r="C733" t="n">
         <v>0.3</v>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>0.072835</v>
+        <v>0.072741</v>
       </c>
       <c r="C734" t="n">
         <v>0.297674</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>0.07374600000000001</v>
+        <v>0.073542</v>
       </c>
       <c r="C735" t="n">
         <v>0.295349</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>0.07384400000000001</v>
+        <v>0.07378899999999999</v>
       </c>
       <c r="C736" t="n">
         <v>0.293023</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>0.073958</v>
+        <v>0.07391399999999999</v>
       </c>
       <c r="C737" t="n">
         <v>0.290698</v>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="B738" t="n">
-        <v>0.074549</v>
+        <v>0.074544</v>
       </c>
       <c r="C738" t="n">
         <v>0.288372</v>
@@ -10021,7 +10021,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>0.074605</v>
+        <v>0.07468900000000001</v>
       </c>
       <c r="C739" t="n">
         <v>0.286047</v>
@@ -10034,7 +10034,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>0.075027</v>
+        <v>0.074918</v>
       </c>
       <c r="C740" t="n">
         <v>0.283721</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="B741" t="n">
-        <v>0.075166</v>
+        <v>0.075213</v>
       </c>
       <c r="C741" t="n">
         <v>0.281395</v>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>0.075879</v>
+        <v>0.07589</v>
       </c>
       <c r="C742" t="n">
         <v>0.27907</v>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>0.076054</v>
+        <v>0.076014</v>
       </c>
       <c r="C743" t="n">
         <v>0.276744</v>
@@ -10086,7 +10086,7 @@
         </is>
       </c>
       <c r="B744" t="n">
-        <v>0.076201</v>
+        <v>0.07614899999999999</v>
       </c>
       <c r="C744" t="n">
         <v>0.274419</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>0.076728</v>
+        <v>0.076651</v>
       </c>
       <c r="C745" t="n">
         <v>0.272093</v>
@@ -10112,7 +10112,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>0.077043</v>
+        <v>0.076864</v>
       </c>
       <c r="C746" t="n">
         <v>0.269767</v>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>0.077657</v>
+        <v>0.07779</v>
       </c>
       <c r="C747" t="n">
         <v>0.267442</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>0.07818899999999999</v>
+        <v>0.078177</v>
       </c>
       <c r="C748" t="n">
         <v>0.265116</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>0.07822800000000001</v>
+        <v>0.078291</v>
       </c>
       <c r="C749" t="n">
         <v>0.262791</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>0.078468</v>
+        <v>0.07832799999999999</v>
       </c>
       <c r="C750" t="n">
         <v>0.260465</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>0.07945000000000001</v>
+        <v>0.07932400000000001</v>
       </c>
       <c r="C751" t="n">
         <v>0.25814</v>
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>0.079497</v>
+        <v>0.07944900000000001</v>
       </c>
       <c r="C752" t="n">
         <v>0.255814</v>
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>0.080399</v>
+        <v>0.080454</v>
       </c>
       <c r="C753" t="n">
         <v>0.253488</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B754" t="n">
-        <v>0.080704</v>
+        <v>0.080569</v>
       </c>
       <c r="C754" t="n">
         <v>0.251163</v>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>0.081177</v>
+        <v>0.081206</v>
       </c>
       <c r="C755" t="n">
         <v>0.248837</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B757" t="n">
-        <v>0.081585</v>
+        <v>0.081705</v>
       </c>
       <c r="C757" t="n">
         <v>0.244186</v>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>0.082514</v>
+        <v>0.08261400000000001</v>
       </c>
       <c r="C758" t="n">
         <v>0.24186</v>
@@ -10281,7 +10281,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>0.082939</v>
+        <v>0.082915</v>
       </c>
       <c r="C759" t="n">
         <v>0.239535</v>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="B760" t="n">
-        <v>0.083208</v>
+        <v>0.083269</v>
       </c>
       <c r="C760" t="n">
         <v>0.237209</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>0.08419699999999999</v>
+        <v>0.084272</v>
       </c>
       <c r="C761" t="n">
         <v>0.234884</v>
@@ -10320,7 +10320,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>0.085228</v>
+        <v>0.085357</v>
       </c>
       <c r="C762" t="n">
         <v>0.232558</v>
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>0.08561100000000001</v>
+        <v>0.085648</v>
       </c>
       <c r="C763" t="n">
         <v>0.230233</v>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>0.086447</v>
+        <v>0.086349</v>
       </c>
       <c r="C764" t="n">
         <v>0.227907</v>
@@ -10359,7 +10359,7 @@
         </is>
       </c>
       <c r="B765" t="n">
-        <v>0.086877</v>
+        <v>0.086935</v>
       </c>
       <c r="C765" t="n">
         <v>0.225581</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>0.087023</v>
+        <v>0.087117</v>
       </c>
       <c r="C766" t="n">
         <v>0.223256</v>
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>0.087062</v>
+        <v>0.08719300000000001</v>
       </c>
       <c r="C767" t="n">
         <v>0.22093</v>
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="B768" t="n">
-        <v>0.088237</v>
+        <v>0.08828999999999999</v>
       </c>
       <c r="C768" t="n">
         <v>0.218605</v>
@@ -10411,7 +10411,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>0.089021</v>
+        <v>0.089035</v>
       </c>
       <c r="C769" t="n">
         <v>0.216279</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>0.089184</v>
+        <v>0.089283</v>
       </c>
       <c r="C770" t="n">
         <v>0.213953</v>
@@ -10437,7 +10437,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>0.08944299999999999</v>
+        <v>0.089467</v>
       </c>
       <c r="C771" t="n">
         <v>0.211628</v>
@@ -10450,7 +10450,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>0.09277100000000001</v>
+        <v>0.092783</v>
       </c>
       <c r="C772" t="n">
         <v>0.209302</v>
@@ -10463,7 +10463,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>0.09339500000000001</v>
+        <v>0.09343</v>
       </c>
       <c r="C773" t="n">
         <v>0.206977</v>
@@ -10476,7 +10476,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>0.094517</v>
+        <v>0.09457500000000001</v>
       </c>
       <c r="C774" t="n">
         <v>0.204651</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B775" t="n">
-        <v>0.094835</v>
+        <v>0.09495000000000001</v>
       </c>
       <c r="C775" t="n">
         <v>0.202326</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>0.098387</v>
+        <v>0.098493</v>
       </c>
       <c r="C776" t="n">
         <v>0.2</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B777" t="n">
-        <v>0.098816</v>
+        <v>0.09879599999999999</v>
       </c>
       <c r="C777" t="n">
         <v>0.197674</v>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="B778" t="n">
-        <v>0.099379</v>
+        <v>0.099345</v>
       </c>
       <c r="C778" t="n">
         <v>0.195349</v>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>0.101245</v>
+        <v>0.101355</v>
       </c>
       <c r="C779" t="n">
         <v>0.193023</v>
@@ -10554,7 +10554,7 @@
         </is>
       </c>
       <c r="B780" t="n">
-        <v>0.102386</v>
+        <v>0.102384</v>
       </c>
       <c r="C780" t="n">
         <v>0.190698</v>
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>0.102479</v>
+        <v>0.102442</v>
       </c>
       <c r="C781" t="n">
         <v>0.188372</v>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>0.104511</v>
+        <v>0.104431</v>
       </c>
       <c r="C782" t="n">
         <v>0.186047</v>
@@ -10593,7 +10593,7 @@
         </is>
       </c>
       <c r="B783" t="n">
-        <v>0.104541</v>
+        <v>0.104613</v>
       </c>
       <c r="C783" t="n">
         <v>0.183721</v>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>0.105851</v>
+        <v>0.105859</v>
       </c>
       <c r="C784" t="n">
         <v>0.181395</v>
@@ -10619,7 +10619,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>0.106881</v>
+        <v>0.106917</v>
       </c>
       <c r="C785" t="n">
         <v>0.17907</v>
@@ -10632,7 +10632,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>0.108741</v>
+        <v>0.108709</v>
       </c>
       <c r="C786" t="n">
         <v>0.176744</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>0.108778</v>
+        <v>0.108722</v>
       </c>
       <c r="C787" t="n">
         <v>0.174419</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>0.108876</v>
+        <v>0.108907</v>
       </c>
       <c r="C788" t="n">
         <v>0.172093</v>
@@ -10671,7 +10671,7 @@
         </is>
       </c>
       <c r="B789" t="n">
-        <v>0.109798</v>
+        <v>0.109586</v>
       </c>
       <c r="C789" t="n">
         <v>0.169767</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>0.110303</v>
+        <v>0.110347</v>
       </c>
       <c r="C790" t="n">
         <v>0.167442</v>
@@ -10697,7 +10697,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>0.111081</v>
+        <v>0.111069</v>
       </c>
       <c r="C791" t="n">
         <v>0.165116</v>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>0.111254</v>
+        <v>0.111114</v>
       </c>
       <c r="C792" t="n">
         <v>0.162791</v>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>0.111968</v>
+        <v>0.111769</v>
       </c>
       <c r="C793" t="n">
         <v>0.160465</v>
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="B794" t="n">
-        <v>0.11239</v>
+        <v>0.112428</v>
       </c>
       <c r="C794" t="n">
         <v>0.15814</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>0.112688</v>
+        <v>0.112773</v>
       </c>
       <c r="C795" t="n">
         <v>0.155814</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>0.113191</v>
+        <v>0.11318</v>
       </c>
       <c r="C796" t="n">
         <v>0.153488</v>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>0.114329</v>
+        <v>0.114091</v>
       </c>
       <c r="C797" t="n">
         <v>0.151163</v>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B798" t="n">
-        <v>0.116757</v>
+        <v>0.116718</v>
       </c>
       <c r="C798" t="n">
         <v>0.148837</v>
@@ -10801,7 +10801,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>0.116823</v>
+        <v>0.116826</v>
       </c>
       <c r="C799" t="n">
         <v>0.146512</v>
@@ -10814,7 +10814,7 @@
         </is>
       </c>
       <c r="B800" t="n">
-        <v>0.118038</v>
+        <v>0.118066</v>
       </c>
       <c r="C800" t="n">
         <v>0.144186</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="B801" t="n">
-        <v>0.118055</v>
+        <v>0.118071</v>
       </c>
       <c r="C801" t="n">
         <v>0.14186</v>
@@ -10840,7 +10840,7 @@
         </is>
       </c>
       <c r="B802" t="n">
-        <v>0.118113</v>
+        <v>0.118212</v>
       </c>
       <c r="C802" t="n">
         <v>0.139535</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>0.118492</v>
+        <v>0.118593</v>
       </c>
       <c r="C803" t="n">
         <v>0.137209</v>
@@ -10866,7 +10866,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>0.119506</v>
+        <v>0.119686</v>
       </c>
       <c r="C804" t="n">
         <v>0.134884</v>
@@ -10879,7 +10879,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>0.120963</v>
+        <v>0.121226</v>
       </c>
       <c r="C805" t="n">
         <v>0.132558</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B806" t="n">
-        <v>0.121524</v>
+        <v>0.121482</v>
       </c>
       <c r="C806" t="n">
         <v>0.130233</v>
@@ -10905,7 +10905,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>0.124529</v>
+        <v>0.124668</v>
       </c>
       <c r="C807" t="n">
         <v>0.127907</v>
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>0.127292</v>
+        <v>0.127098</v>
       </c>
       <c r="C808" t="n">
         <v>0.125581</v>
@@ -10931,7 +10931,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>0.12821</v>
+        <v>0.128356</v>
       </c>
       <c r="C809" t="n">
         <v>0.123256</v>
@@ -10944,7 +10944,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>0.128913</v>
+        <v>0.128718</v>
       </c>
       <c r="C810" t="n">
         <v>0.12093</v>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>0.134071</v>
+        <v>0.134083</v>
       </c>
       <c r="C811" t="n">
         <v>0.118605</v>
@@ -10970,7 +10970,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>0.135423</v>
+        <v>0.135463</v>
       </c>
       <c r="C812" t="n">
         <v>0.116279</v>
@@ -10983,7 +10983,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>0.136359</v>
+        <v>0.136116</v>
       </c>
       <c r="C813" t="n">
         <v>0.113953</v>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>0.136686</v>
+        <v>0.136275</v>
       </c>
       <c r="C814" t="n">
         <v>0.111628</v>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>0.1384</v>
+        <v>0.138405</v>
       </c>
       <c r="C815" t="n">
         <v>0.109302</v>
@@ -11022,7 +11022,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>0.140026</v>
+        <v>0.139917</v>
       </c>
       <c r="C816" t="n">
         <v>0.106977</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>0.1434</v>
+        <v>0.143488</v>
       </c>
       <c r="C817" t="n">
         <v>0.104651</v>
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>0.14359</v>
+        <v>0.143641</v>
       </c>
       <c r="C818" t="n">
         <v>0.102326</v>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>0.146016</v>
+        <v>0.145673</v>
       </c>
       <c r="C819" t="n">
         <v>0.1</v>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>0.147634</v>
+        <v>0.147562</v>
       </c>
       <c r="C820" t="n">
         <v>0.097674</v>
@@ -11087,7 +11087,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>0.149214</v>
+        <v>0.149481</v>
       </c>
       <c r="C821" t="n">
         <v>0.095349</v>
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>0.149569</v>
+        <v>0.149521</v>
       </c>
       <c r="C822" t="n">
         <v>0.09302299999999999</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>0.15207</v>
+        <v>0.151675</v>
       </c>
       <c r="C823" t="n">
         <v>0.090698</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>0.15207</v>
+        <v>0.151675</v>
       </c>
       <c r="C824" t="n">
         <v>0.08837200000000001</v>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>0.15207</v>
+        <v>0.151675</v>
       </c>
       <c r="C825" t="n">
         <v>0.086047</v>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>0.152315</v>
+        <v>0.152483</v>
       </c>
       <c r="C826" t="n">
         <v>0.083721</v>
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>0.157831</v>
+        <v>0.157764</v>
       </c>
       <c r="C827" t="n">
         <v>0.081395</v>
@@ -11178,7 +11178,7 @@
         </is>
       </c>
       <c r="B828" t="n">
-        <v>0.1605</v>
+        <v>0.160314</v>
       </c>
       <c r="C828" t="n">
         <v>0.07907</v>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>0.161943</v>
+        <v>0.161844</v>
       </c>
       <c r="C829" t="n">
         <v>0.07674400000000001</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>0.16202</v>
+        <v>0.162097</v>
       </c>
       <c r="C830" t="n">
         <v>0.074419</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="B831" t="n">
-        <v>0.16724</v>
+        <v>0.167223</v>
       </c>
       <c r="C831" t="n">
         <v>0.072093</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="B832" t="n">
-        <v>0.170767</v>
+        <v>0.170878</v>
       </c>
       <c r="C832" t="n">
         <v>0.069767</v>
@@ -11243,7 +11243,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>0.172034</v>
+        <v>0.17222</v>
       </c>
       <c r="C833" t="n">
         <v>0.067442</v>
@@ -11256,7 +11256,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>0.173561</v>
+        <v>0.173748</v>
       </c>
       <c r="C834" t="n">
         <v>0.06511599999999999</v>
@@ -11269,7 +11269,7 @@
         </is>
       </c>
       <c r="B835" t="n">
-        <v>0.185724</v>
+        <v>0.185837</v>
       </c>
       <c r="C835" t="n">
         <v>0.062791</v>
@@ -11282,7 +11282,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>0.186256</v>
+        <v>0.186388</v>
       </c>
       <c r="C836" t="n">
         <v>0.060465</v>
@@ -11295,7 +11295,7 @@
         </is>
       </c>
       <c r="B837" t="n">
-        <v>0.193252</v>
+        <v>0.193171</v>
       </c>
       <c r="C837" t="n">
         <v>0.05814</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B838" t="n">
-        <v>0.194424</v>
+        <v>0.194347</v>
       </c>
       <c r="C838" t="n">
         <v>0.055814</v>
@@ -11321,7 +11321,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>0.194713</v>
+        <v>0.194931</v>
       </c>
       <c r="C839" t="n">
         <v>0.053488</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>0.196191</v>
+        <v>0.195843</v>
       </c>
       <c r="C840" t="n">
         <v>0.051163</v>
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>0.196257</v>
+        <v>0.196227</v>
       </c>
       <c r="C841" t="n">
         <v>0.048837</v>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="B842" t="n">
-        <v>0.200038</v>
+        <v>0.199328</v>
       </c>
       <c r="C842" t="n">
         <v>0.046512</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>0.223785</v>
+        <v>0.224035</v>
       </c>
       <c r="C843" t="n">
         <v>0.044186</v>
@@ -11386,7 +11386,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>0.23186</v>
+        <v>0.232003</v>
       </c>
       <c r="C844" t="n">
         <v>0.04186</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>0.239412</v>
+        <v>0.239463</v>
       </c>
       <c r="C845" t="n">
         <v>0.039535</v>
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>0.246024</v>
+        <v>0.245557</v>
       </c>
       <c r="C846" t="n">
         <v>0.037209</v>
@@ -11425,7 +11425,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>0.271966</v>
+        <v>0.271939</v>
       </c>
       <c r="C847" t="n">
         <v>0.034884</v>
@@ -11438,7 +11438,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>0.272787</v>
+        <v>0.273122</v>
       </c>
       <c r="C848" t="n">
         <v>0.032558</v>
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>0.274573</v>
+        <v>0.274416</v>
       </c>
       <c r="C849" t="n">
         <v>0.030233</v>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>0.304415</v>
+        <v>0.304001</v>
       </c>
       <c r="C850" t="n">
         <v>0.027907</v>
@@ -11477,7 +11477,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>0.314349</v>
+        <v>0.314727</v>
       </c>
       <c r="C851" t="n">
         <v>0.025581</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>0.318489</v>
+        <v>0.318878</v>
       </c>
       <c r="C852" t="n">
         <v>0.023256</v>
@@ -11503,7 +11503,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>0.33103</v>
+        <v>0.330493</v>
       </c>
       <c r="C853" t="n">
         <v>0.02093</v>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>0.339948</v>
+        <v>0.339718</v>
       </c>
       <c r="C854" t="n">
         <v>0.018605</v>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>0.350217</v>
+        <v>0.35044</v>
       </c>
       <c r="C855" t="n">
         <v>0.016279</v>
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>0.473555</v>
+        <v>0.472737</v>
       </c>
       <c r="C856" t="n">
         <v>0.013953</v>
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>0.482607</v>
+        <v>0.482702</v>
       </c>
       <c r="C857" t="n">
         <v>0.011628</v>
@@ -11568,7 +11568,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>0.597927</v>
+        <v>0.5985819999999999</v>
       </c>
       <c r="C858" t="n">
         <v>0.009302</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>0.614938</v>
+        <v>0.615194</v>
       </c>
       <c r="C859" t="n">
         <v>0.006977</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>0.917299</v>
+        <v>0.918286</v>
       </c>
       <c r="C860" t="n">
         <v>0.004651</v>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>1.177623</v>
+        <v>1.180031</v>
       </c>
       <c r="C861" t="n">
         <v>0.002326</v>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>0.000951</v>
+        <v>0.0009479999999999999</v>
       </c>
       <c r="C867" t="n">
         <v>0.988372</v>
@@ -11711,7 +11711,7 @@
         </is>
       </c>
       <c r="B869" t="n">
-        <v>0.001572</v>
+        <v>0.001569</v>
       </c>
       <c r="C869" t="n">
         <v>0.983721</v>
@@ -11737,7 +11737,7 @@
         </is>
       </c>
       <c r="B871" t="n">
-        <v>0.001917</v>
+        <v>0.001918</v>
       </c>
       <c r="C871" t="n">
         <v>0.97907</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="B872" t="n">
-        <v>0.002288</v>
+        <v>0.002284</v>
       </c>
       <c r="C872" t="n">
         <v>0.9767439999999999</v>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>0.002438</v>
+        <v>0.002427</v>
       </c>
       <c r="C873" t="n">
         <v>0.974419</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>0.002614</v>
+        <v>0.002615</v>
       </c>
       <c r="C874" t="n">
         <v>0.972093</v>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>0.002702</v>
+        <v>0.002705</v>
       </c>
       <c r="C875" t="n">
         <v>0.969767</v>
@@ -11802,7 +11802,7 @@
         </is>
       </c>
       <c r="B876" t="n">
-        <v>0.002868</v>
+        <v>0.002872</v>
       </c>
       <c r="C876" t="n">
         <v>0.967442</v>
@@ -11815,7 +11815,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>0.002944</v>
+        <v>0.002945</v>
       </c>
       <c r="C877" t="n">
         <v>0.965116</v>
@@ -11828,7 +11828,7 @@
         </is>
       </c>
       <c r="B878" t="n">
-        <v>0.003326</v>
+        <v>0.003317</v>
       </c>
       <c r="C878" t="n">
         <v>0.962791</v>
@@ -11841,7 +11841,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>0.003695</v>
+        <v>0.003685</v>
       </c>
       <c r="C879" t="n">
         <v>0.960465</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>0.003765</v>
+        <v>0.00376</v>
       </c>
       <c r="C880" t="n">
         <v>0.95814</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="B881" t="n">
-        <v>0.004025</v>
+        <v>0.004026</v>
       </c>
       <c r="C881" t="n">
         <v>0.9558140000000001</v>
@@ -11880,7 +11880,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>0.004131</v>
+        <v>0.00413</v>
       </c>
       <c r="C882" t="n">
         <v>0.953488</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>0.004306</v>
+        <v>0.004309</v>
       </c>
       <c r="C883" t="n">
         <v>0.951163</v>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>0.004338</v>
+        <v>0.004334</v>
       </c>
       <c r="C884" t="n">
         <v>0.948837</v>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>0.004374</v>
+        <v>0.004375</v>
       </c>
       <c r="C885" t="n">
         <v>0.946512</v>
@@ -11932,7 +11932,7 @@
         </is>
       </c>
       <c r="B886" t="n">
-        <v>0.004426</v>
+        <v>0.004427</v>
       </c>
       <c r="C886" t="n">
         <v>0.944186</v>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>0.004547</v>
+        <v>0.004532</v>
       </c>
       <c r="C887" t="n">
         <v>0.94186</v>
@@ -11958,7 +11958,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>0.004589</v>
+        <v>0.004575</v>
       </c>
       <c r="C888" t="n">
         <v>0.939535</v>
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>0.004644</v>
+        <v>0.004645</v>
       </c>
       <c r="C889" t="n">
         <v>0.937209</v>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>0.004737</v>
+        <v>0.004725</v>
       </c>
       <c r="C890" t="n">
         <v>0.934884</v>
@@ -11997,7 +11997,7 @@
         </is>
       </c>
       <c r="B891" t="n">
-        <v>0.004742</v>
+        <v>0.004734</v>
       </c>
       <c r="C891" t="n">
         <v>0.932558</v>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="B892" t="n">
-        <v>0.004992</v>
+        <v>0.004988</v>
       </c>
       <c r="C892" t="n">
         <v>0.930233</v>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="B893" t="n">
-        <v>0.005061</v>
+        <v>0.005065</v>
       </c>
       <c r="C893" t="n">
         <v>0.927907</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>0.005345</v>
+        <v>0.005351</v>
       </c>
       <c r="C894" t="n">
         <v>0.925581</v>
@@ -12049,7 +12049,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>0.005415</v>
+        <v>0.005414</v>
       </c>
       <c r="C895" t="n">
         <v>0.923256</v>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>0.005468</v>
+        <v>0.005465</v>
       </c>
       <c r="C896" t="n">
         <v>0.92093</v>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="B897" t="n">
-        <v>0.005587</v>
+        <v>0.005589</v>
       </c>
       <c r="C897" t="n">
         <v>0.918605</v>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="B898" t="n">
-        <v>0.007033</v>
+        <v>0.00702</v>
       </c>
       <c r="C898" t="n">
         <v>0.916279</v>
@@ -12101,7 +12101,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>0.007354</v>
+        <v>0.007351</v>
       </c>
       <c r="C899" t="n">
         <v>0.913953</v>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>0.007759</v>
+        <v>0.007751</v>
       </c>
       <c r="C900" t="n">
         <v>0.911628</v>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>0.007871</v>
+        <v>0.007868999999999999</v>
       </c>
       <c r="C901" t="n">
         <v>0.9093020000000001</v>
@@ -12140,7 +12140,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>0.008085</v>
+        <v>0.008088</v>
       </c>
       <c r="C902" t="n">
         <v>0.906977</v>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>0.008521000000000001</v>
+        <v>0.008525</v>
       </c>
       <c r="C903" t="n">
         <v>0.904651</v>
@@ -12166,7 +12166,7 @@
         </is>
       </c>
       <c r="B904" t="n">
-        <v>0.008895</v>
+        <v>0.0089</v>
       </c>
       <c r="C904" t="n">
         <v>0.902326</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="B905" t="n">
-        <v>0.008919</v>
+        <v>0.008906000000000001</v>
       </c>
       <c r="C905" t="n">
         <v>0.9</v>
@@ -12192,7 +12192,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>0.009057000000000001</v>
+        <v>0.009050000000000001</v>
       </c>
       <c r="C906" t="n">
         <v>0.897674</v>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>0.009175000000000001</v>
+        <v>0.009178</v>
       </c>
       <c r="C907" t="n">
         <v>0.895349</v>
@@ -12218,7 +12218,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>0.009462999999999999</v>
+        <v>0.009414</v>
       </c>
       <c r="C908" t="n">
         <v>0.893023</v>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="B909" t="n">
-        <v>0.009521</v>
+        <v>0.009528</v>
       </c>
       <c r="C909" t="n">
         <v>0.890698</v>
@@ -12244,7 +12244,7 @@
         </is>
       </c>
       <c r="B910" t="n">
-        <v>0.009549</v>
+        <v>0.009557</v>
       </c>
       <c r="C910" t="n">
         <v>0.8883720000000001</v>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>0.009606</v>
+        <v>0.009592</v>
       </c>
       <c r="C911" t="n">
         <v>0.886047</v>
@@ -12270,7 +12270,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>0.009627999999999999</v>
+        <v>0.009596</v>
       </c>
       <c r="C912" t="n">
         <v>0.883721</v>
@@ -12283,7 +12283,7 @@
         </is>
       </c>
       <c r="B913" t="n">
-        <v>0.010004</v>
+        <v>0.010006</v>
       </c>
       <c r="C913" t="n">
         <v>0.881395</v>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B914" t="n">
-        <v>0.010256</v>
+        <v>0.010262</v>
       </c>
       <c r="C914" t="n">
         <v>0.87907</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="B915" t="n">
-        <v>0.010437</v>
+        <v>0.010433</v>
       </c>
       <c r="C915" t="n">
         <v>0.876744</v>
@@ -12322,7 +12322,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>0.01046</v>
+        <v>0.010481</v>
       </c>
       <c r="C916" t="n">
         <v>0.8744189999999999</v>
@@ -12335,7 +12335,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>0.010546</v>
+        <v>0.010547</v>
       </c>
       <c r="C917" t="n">
         <v>0.872093</v>
@@ -12348,7 +12348,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>0.010685</v>
+        <v>0.01069</v>
       </c>
       <c r="C918" t="n">
         <v>0.869767</v>
@@ -12361,7 +12361,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>0.010813</v>
+        <v>0.010821</v>
       </c>
       <c r="C919" t="n">
         <v>0.867442</v>
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="B920" t="n">
-        <v>0.011192</v>
+        <v>0.011204</v>
       </c>
       <c r="C920" t="n">
         <v>0.865116</v>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>0.011271</v>
+        <v>0.011277</v>
       </c>
       <c r="C921" t="n">
         <v>0.862791</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>0.011462</v>
+        <v>0.011431</v>
       </c>
       <c r="C922" t="n">
         <v>0.860465</v>
@@ -12413,7 +12413,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>0.011595</v>
+        <v>0.011587</v>
       </c>
       <c r="C923" t="n">
         <v>0.85814</v>
@@ -12426,7 +12426,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>0.01179</v>
+        <v>0.01178</v>
       </c>
       <c r="C924" t="n">
         <v>0.855814</v>
@@ -12439,7 +12439,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>0.012211</v>
+        <v>0.012214</v>
       </c>
       <c r="C925" t="n">
         <v>0.853488</v>
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>0.01229</v>
+        <v>0.01228</v>
       </c>
       <c r="C926" t="n">
         <v>0.851163</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>0.012414</v>
+        <v>0.012399</v>
       </c>
       <c r="C927" t="n">
         <v>0.848837</v>
@@ -12491,7 +12491,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>0.012559</v>
+        <v>0.01251</v>
       </c>
       <c r="C929" t="n">
         <v>0.844186</v>
@@ -12504,7 +12504,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>0.012766</v>
+        <v>0.012785</v>
       </c>
       <c r="C930" t="n">
         <v>0.8418600000000001</v>
@@ -12530,7 +12530,7 @@
         </is>
       </c>
       <c r="B932" t="n">
-        <v>0.013125</v>
+        <v>0.013141</v>
       </c>
       <c r="C932" t="n">
         <v>0.837209</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>0.013582</v>
+        <v>0.013555</v>
       </c>
       <c r="C933" t="n">
         <v>0.834884</v>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>0.014132</v>
+        <v>0.014116</v>
       </c>
       <c r="C934" t="n">
         <v>0.832558</v>
@@ -12569,7 +12569,7 @@
         </is>
       </c>
       <c r="B935" t="n">
-        <v>0.014159</v>
+        <v>0.014173</v>
       </c>
       <c r="C935" t="n">
         <v>0.830233</v>
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>0.014531</v>
+        <v>0.014532</v>
       </c>
       <c r="C936" t="n">
         <v>0.8279069999999999</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="B937" t="n">
-        <v>0.014673</v>
+        <v>0.01466</v>
       </c>
       <c r="C937" t="n">
         <v>0.825581</v>
@@ -12608,7 +12608,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>0.014781</v>
+        <v>0.014787</v>
       </c>
       <c r="C938" t="n">
         <v>0.823256</v>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>0.014782</v>
+        <v>0.014794</v>
       </c>
       <c r="C939" t="n">
         <v>0.82093</v>
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="B941" t="n">
-        <v>0.015021</v>
+        <v>0.015034</v>
       </c>
       <c r="C941" t="n">
         <v>0.816279</v>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="B942" t="n">
-        <v>0.015054</v>
+        <v>0.015042</v>
       </c>
       <c r="C942" t="n">
         <v>0.813953</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="B943" t="n">
-        <v>0.015211</v>
+        <v>0.015226</v>
       </c>
       <c r="C943" t="n">
         <v>0.811628</v>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>0.015281</v>
+        <v>0.015285</v>
       </c>
       <c r="C944" t="n">
         <v>0.809302</v>
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>0.015302</v>
+        <v>0.015296</v>
       </c>
       <c r="C945" t="n">
         <v>0.8069770000000001</v>
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>0.015465</v>
+        <v>0.015467</v>
       </c>
       <c r="C946" t="n">
         <v>0.804651</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>0.016047</v>
+        <v>0.016035</v>
       </c>
       <c r="C947" t="n">
         <v>0.802326</v>
@@ -12738,7 +12738,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>0.016428</v>
+        <v>0.01643</v>
       </c>
       <c r="C948" t="n">
         <v>0.8</v>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>0.016592</v>
+        <v>0.016608</v>
       </c>
       <c r="C949" t="n">
         <v>0.797674</v>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="B950" t="n">
-        <v>0.016771</v>
+        <v>0.016758</v>
       </c>
       <c r="C950" t="n">
         <v>0.795349</v>
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>0.016995</v>
+        <v>0.017018</v>
       </c>
       <c r="C951" t="n">
         <v>0.793023</v>
@@ -12790,7 +12790,7 @@
         </is>
       </c>
       <c r="B952" t="n">
-        <v>0.017611</v>
+        <v>0.017597</v>
       </c>
       <c r="C952" t="n">
         <v>0.790698</v>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>0.017763</v>
+        <v>0.017737</v>
       </c>
       <c r="C953" t="n">
         <v>0.788372</v>
@@ -12816,7 +12816,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>0.0178</v>
+        <v>0.017817</v>
       </c>
       <c r="C954" t="n">
         <v>0.7860470000000001</v>
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>0.017925</v>
+        <v>0.017917</v>
       </c>
       <c r="C955" t="n">
         <v>0.783721</v>
@@ -12842,7 +12842,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>0.017949</v>
+        <v>0.017969</v>
       </c>
       <c r="C956" t="n">
         <v>0.781395</v>
@@ -12855,7 +12855,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>0.018188</v>
+        <v>0.018191</v>
       </c>
       <c r="C957" t="n">
         <v>0.77907</v>
@@ -12868,7 +12868,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>0.018478</v>
+        <v>0.01847</v>
       </c>
       <c r="C958" t="n">
         <v>0.776744</v>
@@ -12881,7 +12881,7 @@
         </is>
       </c>
       <c r="B959" t="n">
-        <v>0.018791</v>
+        <v>0.018777</v>
       </c>
       <c r="C959" t="n">
         <v>0.774419</v>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0.018828</v>
+        <v>0.01881</v>
       </c>
       <c r="C960" t="n">
         <v>0.772093</v>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>0.01891</v>
+        <v>0.018887</v>
       </c>
       <c r="C961" t="n">
         <v>0.769767</v>
@@ -12920,7 +12920,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>0.018943</v>
+        <v>0.018935</v>
       </c>
       <c r="C962" t="n">
         <v>0.767442</v>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>0.019278</v>
+        <v>0.019287</v>
       </c>
       <c r="C963" t="n">
         <v>0.765116</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>0.019714</v>
+        <v>0.019722</v>
       </c>
       <c r="C964" t="n">
         <v>0.762791</v>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>0.019856</v>
+        <v>0.019844</v>
       </c>
       <c r="C965" t="n">
         <v>0.7604649999999999</v>
@@ -12972,7 +12972,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>0.020328</v>
+        <v>0.020171</v>
       </c>
       <c r="C966" t="n">
         <v>0.75814</v>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="B967" t="n">
-        <v>0.020666</v>
+        <v>0.020603</v>
       </c>
       <c r="C967" t="n">
         <v>0.755814</v>
@@ -12998,7 +12998,7 @@
         </is>
       </c>
       <c r="B968" t="n">
-        <v>0.020785</v>
+        <v>0.020764</v>
       </c>
       <c r="C968" t="n">
         <v>0.753488</v>
@@ -13011,7 +13011,7 @@
         </is>
       </c>
       <c r="B969" t="n">
-        <v>0.020931</v>
+        <v>0.020928</v>
       </c>
       <c r="C969" t="n">
         <v>0.751163</v>
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="B970" t="n">
-        <v>0.021628</v>
+        <v>0.021644</v>
       </c>
       <c r="C970" t="n">
         <v>0.748837</v>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>0.021707</v>
+        <v>0.021728</v>
       </c>
       <c r="C971" t="n">
         <v>0.746512</v>
@@ -13050,7 +13050,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>0.021947</v>
+        <v>0.021962</v>
       </c>
       <c r="C972" t="n">
         <v>0.744186</v>
@@ -13063,7 +13063,7 @@
         </is>
       </c>
       <c r="B973" t="n">
-        <v>0.023154</v>
+        <v>0.023161</v>
       </c>
       <c r="C973" t="n">
         <v>0.74186</v>
@@ -13076,7 +13076,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>0.023261</v>
+        <v>0.023282</v>
       </c>
       <c r="C974" t="n">
         <v>0.7395350000000001</v>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>0.023481</v>
+        <v>0.023476</v>
       </c>
       <c r="C975" t="n">
         <v>0.737209</v>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>0.023497</v>
+        <v>0.023498</v>
       </c>
       <c r="C976" t="n">
         <v>0.734884</v>
@@ -13115,7 +13115,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>0.023854</v>
+        <v>0.02388</v>
       </c>
       <c r="C977" t="n">
         <v>0.732558</v>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>0.023961</v>
+        <v>0.023968</v>
       </c>
       <c r="C978" t="n">
         <v>0.730233</v>
@@ -13141,7 +13141,7 @@
         </is>
       </c>
       <c r="B979" t="n">
-        <v>0.024358</v>
+        <v>0.024355</v>
       </c>
       <c r="C979" t="n">
         <v>0.727907</v>
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="B980" t="n">
-        <v>0.024372</v>
+        <v>0.024361</v>
       </c>
       <c r="C980" t="n">
         <v>0.725581</v>
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>0.024807</v>
+        <v>0.024785</v>
       </c>
       <c r="C981" t="n">
         <v>0.723256</v>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="B982" t="n">
-        <v>0.024817</v>
+        <v>0.024825</v>
       </c>
       <c r="C982" t="n">
         <v>0.72093</v>
@@ -13193,7 +13193,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>0.02501</v>
+        <v>0.025034</v>
       </c>
       <c r="C983" t="n">
         <v>0.718605</v>
@@ -13206,7 +13206,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>0.025093</v>
+        <v>0.025091</v>
       </c>
       <c r="C984" t="n">
         <v>0.716279</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>0.025358</v>
+        <v>0.025381</v>
       </c>
       <c r="C985" t="n">
         <v>0.7139529999999999</v>
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>0.02595</v>
+        <v>0.025945</v>
       </c>
       <c r="C986" t="n">
         <v>0.711628</v>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>0.026288</v>
+        <v>0.026194</v>
       </c>
       <c r="C987" t="n">
         <v>0.709302</v>
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>0.026402</v>
+        <v>0.026403</v>
       </c>
       <c r="C988" t="n">
         <v>0.706977</v>
@@ -13271,7 +13271,7 @@
         </is>
       </c>
       <c r="B989" t="n">
-        <v>0.02671</v>
+        <v>0.026735</v>
       </c>
       <c r="C989" t="n">
         <v>0.704651</v>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>0.02678</v>
+        <v>0.026766</v>
       </c>
       <c r="C990" t="n">
         <v>0.702326</v>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>0.02683</v>
+        <v>0.026796</v>
       </c>
       <c r="C991" t="n">
         <v>0.7</v>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="B992" t="n">
-        <v>0.026832</v>
+        <v>0.026843</v>
       </c>
       <c r="C992" t="n">
         <v>0.697674</v>
@@ -13323,7 +13323,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>0.026859</v>
+        <v>0.026888</v>
       </c>
       <c r="C993" t="n">
         <v>0.695349</v>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>0.026939</v>
+        <v>0.026926</v>
       </c>
       <c r="C994" t="n">
         <v>0.6930229999999999</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="B995" t="n">
-        <v>0.027304</v>
+        <v>0.027308</v>
       </c>
       <c r="C995" t="n">
         <v>0.690698</v>
@@ -13362,7 +13362,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>0.027371</v>
+        <v>0.027389</v>
       </c>
       <c r="C996" t="n">
         <v>0.688372</v>
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="B997" t="n">
-        <v>0.027868</v>
+        <v>0.02788</v>
       </c>
       <c r="C997" t="n">
         <v>0.686047</v>
@@ -13388,7 +13388,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>0.028135</v>
+        <v>0.02815</v>
       </c>
       <c r="C998" t="n">
         <v>0.683721</v>
@@ -13401,7 +13401,7 @@
         </is>
       </c>
       <c r="B999" t="n">
-        <v>0.028404</v>
+        <v>0.028423</v>
       </c>
       <c r="C999" t="n">
         <v>0.681395</v>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>0.028626</v>
+        <v>0.028614</v>
       </c>
       <c r="C1000" t="n">
         <v>0.67907</v>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="B1001" t="n">
-        <v>0.028733</v>
+        <v>0.028738</v>
       </c>
       <c r="C1001" t="n">
         <v>0.676744</v>
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="B1002" t="n">
-        <v>0.028761</v>
+        <v>0.028767</v>
       </c>
       <c r="C1002" t="n">
         <v>0.674419</v>
@@ -13453,7 +13453,7 @@
         </is>
       </c>
       <c r="B1003" t="n">
-        <v>0.029412</v>
+        <v>0.029346</v>
       </c>
       <c r="C1003" t="n">
         <v>0.6720930000000001</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>0.029545</v>
+        <v>0.029519</v>
       </c>
       <c r="C1004" t="n">
         <v>0.669767</v>
@@ -13479,7 +13479,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>0.029833</v>
+        <v>0.029842</v>
       </c>
       <c r="C1005" t="n">
         <v>0.667442</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B1006" t="n">
-        <v>0.029904</v>
+        <v>0.029847</v>
       </c>
       <c r="C1006" t="n">
         <v>0.665116</v>
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>0.030043</v>
+        <v>0.030042</v>
       </c>
       <c r="C1007" t="n">
         <v>0.662791</v>
@@ -13518,7 +13518,7 @@
         </is>
       </c>
       <c r="B1008" t="n">
-        <v>0.030241</v>
+        <v>0.030185</v>
       </c>
       <c r="C1008" t="n">
         <v>0.660465</v>
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="B1009" t="n">
-        <v>0.030304</v>
+        <v>0.03034</v>
       </c>
       <c r="C1009" t="n">
         <v>0.6581399999999999</v>
@@ -13544,7 +13544,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>0.030494</v>
+        <v>0.030511</v>
       </c>
       <c r="C1010" t="n">
         <v>0.655814</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>0.030649</v>
+        <v>0.030652</v>
       </c>
       <c r="C1011" t="n">
         <v>0.653488</v>
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="B1012" t="n">
-        <v>0.031017</v>
+        <v>0.031014</v>
       </c>
       <c r="C1012" t="n">
         <v>0.651163</v>
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="B1013" t="n">
-        <v>0.031525</v>
+        <v>0.03148</v>
       </c>
       <c r="C1013" t="n">
         <v>0.648837</v>
@@ -13596,7 +13596,7 @@
         </is>
       </c>
       <c r="B1014" t="n">
-        <v>0.031598</v>
+        <v>0.031532</v>
       </c>
       <c r="C1014" t="n">
         <v>0.646512</v>
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>0.031809</v>
+        <v>0.031825</v>
       </c>
       <c r="C1015" t="n">
         <v>0.644186</v>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>0.032044</v>
+        <v>0.032074</v>
       </c>
       <c r="C1016" t="n">
         <v>0.64186</v>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>0.032099</v>
+        <v>0.032102</v>
       </c>
       <c r="C1017" t="n">
         <v>0.639535</v>
@@ -13648,7 +13648,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>0.032409</v>
+        <v>0.032381</v>
       </c>
       <c r="C1018" t="n">
         <v>0.637209</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>0.032857</v>
+        <v>0.032889</v>
       </c>
       <c r="C1019" t="n">
         <v>0.634884</v>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>0.033216</v>
+        <v>0.033239</v>
       </c>
       <c r="C1020" t="n">
         <v>0.632558</v>
@@ -13687,7 +13687,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>0.033227</v>
+        <v>0.033268</v>
       </c>
       <c r="C1021" t="n">
         <v>0.630233</v>
@@ -13700,7 +13700,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>0.033507</v>
+        <v>0.033495</v>
       </c>
       <c r="C1022" t="n">
         <v>0.627907</v>
@@ -13713,7 +13713,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>0.033908</v>
+        <v>0.033854</v>
       </c>
       <c r="C1023" t="n">
         <v>0.6255810000000001</v>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>0.034223</v>
+        <v>0.034189</v>
       </c>
       <c r="C1024" t="n">
         <v>0.623256</v>
@@ -13739,7 +13739,7 @@
         </is>
       </c>
       <c r="B1025" t="n">
-        <v>0.034438</v>
+        <v>0.034457</v>
       </c>
       <c r="C1025" t="n">
         <v>0.62093</v>
@@ -13752,7 +13752,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>0.034623</v>
+        <v>0.03466</v>
       </c>
       <c r="C1026" t="n">
         <v>0.618605</v>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>0.034722</v>
+        <v>0.034721</v>
       </c>
       <c r="C1027" t="n">
         <v>0.616279</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="B1028" t="n">
-        <v>0.034808</v>
+        <v>0.034804</v>
       </c>
       <c r="C1028" t="n">
         <v>0.613953</v>
@@ -13791,7 +13791,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>0.035256</v>
+        <v>0.035279</v>
       </c>
       <c r="C1029" t="n">
         <v>0.6116279999999999</v>
@@ -13804,7 +13804,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>0.035504</v>
+        <v>0.03547</v>
       </c>
       <c r="C1030" t="n">
         <v>0.609302</v>
@@ -13817,7 +13817,7 @@
         </is>
       </c>
       <c r="B1031" t="n">
-        <v>0.035541</v>
+        <v>0.035559</v>
       </c>
       <c r="C1031" t="n">
         <v>0.606977</v>
@@ -13830,7 +13830,7 @@
         </is>
       </c>
       <c r="B1032" t="n">
-        <v>0.035574</v>
+        <v>0.03559</v>
       </c>
       <c r="C1032" t="n">
         <v>0.604651</v>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="B1033" t="n">
-        <v>0.035854</v>
+        <v>0.035805</v>
       </c>
       <c r="C1033" t="n">
         <v>0.602326</v>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>0.03594</v>
+        <v>0.035956</v>
       </c>
       <c r="C1034" t="n">
         <v>0.6</v>
@@ -13869,7 +13869,7 @@
         </is>
       </c>
       <c r="B1035" t="n">
-        <v>0.036161</v>
+        <v>0.036173</v>
       </c>
       <c r="C1035" t="n">
         <v>0.597674</v>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>0.036342</v>
+        <v>0.036286</v>
       </c>
       <c r="C1036" t="n">
         <v>0.595349</v>
@@ -13895,7 +13895,7 @@
         </is>
       </c>
       <c r="B1037" t="n">
-        <v>0.036369</v>
+        <v>0.036372</v>
       </c>
       <c r="C1037" t="n">
         <v>0.593023</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>0.036436</v>
+        <v>0.036429</v>
       </c>
       <c r="C1038" t="n">
         <v>0.5906979999999999</v>
@@ -13921,7 +13921,7 @@
         </is>
       </c>
       <c r="B1039" t="n">
-        <v>0.036845</v>
+        <v>0.036742</v>
       </c>
       <c r="C1039" t="n">
         <v>0.588372</v>
@@ -13934,7 +13934,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>0.037136</v>
+        <v>0.037161</v>
       </c>
       <c r="C1040" t="n">
         <v>0.586047</v>
@@ -13947,7 +13947,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>0.037684</v>
+        <v>0.037672</v>
       </c>
       <c r="C1041" t="n">
         <v>0.583721</v>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="B1042" t="n">
-        <v>0.037916</v>
+        <v>0.037787</v>
       </c>
       <c r="C1042" t="n">
         <v>0.581395</v>
@@ -13973,7 +13973,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>0.037948</v>
+        <v>0.037924</v>
       </c>
       <c r="C1043" t="n">
         <v>0.57907</v>
@@ -13986,7 +13986,7 @@
         </is>
       </c>
       <c r="B1044" t="n">
-        <v>0.038036</v>
+        <v>0.037967</v>
       </c>
       <c r="C1044" t="n">
         <v>0.576744</v>
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>0.038039</v>
+        <v>0.038026</v>
       </c>
       <c r="C1045" t="n">
         <v>0.574419</v>
@@ -14012,7 +14012,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>0.038478</v>
+        <v>0.03848</v>
       </c>
       <c r="C1046" t="n">
         <v>0.572093</v>
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>0.038753</v>
+        <v>0.038766</v>
       </c>
       <c r="C1047" t="n">
         <v>0.569767</v>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>0.038864</v>
+        <v>0.038795</v>
       </c>
       <c r="C1048" t="n">
         <v>0.567442</v>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="B1049" t="n">
-        <v>0.039221</v>
+        <v>0.039133</v>
       </c>
       <c r="C1049" t="n">
         <v>0.565116</v>
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="B1050" t="n">
-        <v>0.039405</v>
+        <v>0.039366</v>
       </c>
       <c r="C1050" t="n">
         <v>0.562791</v>
@@ -14077,7 +14077,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>0.039714</v>
+        <v>0.039713</v>
       </c>
       <c r="C1051" t="n">
         <v>0.560465</v>
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="B1052" t="n">
-        <v>0.039728</v>
+        <v>0.039759</v>
       </c>
       <c r="C1052" t="n">
         <v>0.55814</v>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>0.040041</v>
+        <v>0.040082</v>
       </c>
       <c r="C1053" t="n">
         <v>0.555814</v>
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>0.040373</v>
+        <v>0.040431</v>
       </c>
       <c r="C1054" t="n">
         <v>0.553488</v>
@@ -14129,7 +14129,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>0.040449</v>
+        <v>0.040435</v>
       </c>
       <c r="C1055" t="n">
         <v>0.551163</v>
@@ -14142,7 +14142,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>0.040507</v>
+        <v>0.040591</v>
       </c>
       <c r="C1056" t="n">
         <v>0.548837</v>
@@ -14155,7 +14155,7 @@
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>0.040751</v>
+        <v>0.040792</v>
       </c>
       <c r="C1057" t="n">
         <v>0.546512</v>
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>0.040921</v>
+        <v>0.040884</v>
       </c>
       <c r="C1058" t="n">
         <v>0.5441859999999999</v>
@@ -14181,7 +14181,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>0.040921</v>
+        <v>0.040898</v>
       </c>
       <c r="C1059" t="n">
         <v>0.54186</v>
@@ -14194,7 +14194,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>0.041757</v>
+        <v>0.041769</v>
       </c>
       <c r="C1060" t="n">
         <v>0.539535</v>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="B1061" t="n">
-        <v>0.042078</v>
+        <v>0.042099</v>
       </c>
       <c r="C1061" t="n">
         <v>0.537209</v>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>0.042375</v>
+        <v>0.042349</v>
       </c>
       <c r="C1062" t="n">
         <v>0.534884</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="B1063" t="n">
-        <v>0.043178</v>
+        <v>0.043128</v>
       </c>
       <c r="C1063" t="n">
         <v>0.532558</v>
@@ -14246,7 +14246,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>0.043395</v>
+        <v>0.043299</v>
       </c>
       <c r="C1064" t="n">
         <v>0.530233</v>
@@ -14259,7 +14259,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>0.043414</v>
+        <v>0.043423</v>
       </c>
       <c r="C1065" t="n">
         <v>0.527907</v>
@@ -14272,7 +14272,7 @@
         </is>
       </c>
       <c r="B1066" t="n">
-        <v>0.043702</v>
+        <v>0.043616</v>
       </c>
       <c r="C1066" t="n">
         <v>0.525581</v>
@@ -14285,7 +14285,7 @@
         </is>
       </c>
       <c r="B1067" t="n">
-        <v>0.04451</v>
+        <v>0.044492</v>
       </c>
       <c r="C1067" t="n">
         <v>0.5232560000000001</v>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>0.045224</v>
+        <v>0.04517</v>
       </c>
       <c r="C1068" t="n">
         <v>0.52093</v>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>0.045285</v>
+        <v>0.045293</v>
       </c>
       <c r="C1069" t="n">
         <v>0.518605</v>
@@ -14324,7 +14324,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>0.045621</v>
+        <v>0.045617</v>
       </c>
       <c r="C1070" t="n">
         <v>0.516279</v>
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>0.046017</v>
+        <v>0.046058</v>
       </c>
       <c r="C1071" t="n">
         <v>0.513953</v>
@@ -14350,7 +14350,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>0.046099</v>
+        <v>0.046123</v>
       </c>
       <c r="C1072" t="n">
         <v>0.511628</v>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>0.046872</v>
+        <v>0.046839</v>
       </c>
       <c r="C1073" t="n">
         <v>0.509302</v>
@@ -14376,7 +14376,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>0.047164</v>
+        <v>0.047201</v>
       </c>
       <c r="C1074" t="n">
         <v>0.506977</v>
@@ -14389,7 +14389,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>0.047611</v>
+        <v>0.04756</v>
       </c>
       <c r="C1075" t="n">
         <v>0.504651</v>
@@ -14402,7 +14402,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>0.04764</v>
+        <v>0.0476</v>
       </c>
       <c r="C1076" t="n">
         <v>0.5023260000000001</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>0.047645</v>
+        <v>0.047686</v>
       </c>
       <c r="C1077" t="n">
         <v>0.5</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="B1078" t="n">
-        <v>0.047978</v>
+        <v>0.047906</v>
       </c>
       <c r="C1078" t="n">
         <v>0.497674</v>
@@ -14441,7 +14441,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>0.048177</v>
+        <v>0.048154</v>
       </c>
       <c r="C1079" t="n">
         <v>0.495349</v>
@@ -14454,7 +14454,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>0.049404</v>
+        <v>0.049419</v>
       </c>
       <c r="C1080" t="n">
         <v>0.493023</v>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>0.049466</v>
+        <v>0.049465</v>
       </c>
       <c r="C1081" t="n">
         <v>0.490698</v>
@@ -14480,7 +14480,7 @@
         </is>
       </c>
       <c r="B1082" t="n">
-        <v>0.05028</v>
+        <v>0.050146</v>
       </c>
       <c r="C1082" t="n">
         <v>0.488372</v>
@@ -14493,7 +14493,7 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>0.05049</v>
+        <v>0.05051</v>
       </c>
       <c r="C1083" t="n">
         <v>0.486047</v>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="B1084" t="n">
-        <v>0.05051</v>
+        <v>0.050541</v>
       </c>
       <c r="C1084" t="n">
         <v>0.483721</v>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>0.050772</v>
+        <v>0.050804</v>
       </c>
       <c r="C1085" t="n">
         <v>0.481395</v>
@@ -14532,7 +14532,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>0.050866</v>
+        <v>0.050879</v>
       </c>
       <c r="C1086" t="n">
         <v>0.47907</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>0.051924</v>
+        <v>0.051934</v>
       </c>
       <c r="C1087" t="n">
         <v>0.476744</v>
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="B1088" t="n">
-        <v>0.051951</v>
+        <v>0.052003</v>
       </c>
       <c r="C1088" t="n">
         <v>0.474419</v>
@@ -14571,7 +14571,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>0.052241</v>
+        <v>0.052271</v>
       </c>
       <c r="C1089" t="n">
         <v>0.472093</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="B1090" t="n">
-        <v>0.052608</v>
+        <v>0.05268</v>
       </c>
       <c r="C1090" t="n">
         <v>0.469767</v>
@@ -14597,7 +14597,7 @@
         </is>
       </c>
       <c r="B1091" t="n">
-        <v>0.052736</v>
+        <v>0.052809</v>
       </c>
       <c r="C1091" t="n">
         <v>0.467442</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>0.053673</v>
+        <v>0.053691</v>
       </c>
       <c r="C1092" t="n">
         <v>0.465116</v>
@@ -14623,7 +14623,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>0.053868</v>
+        <v>0.053921</v>
       </c>
       <c r="C1093" t="n">
         <v>0.462791</v>
@@ -14636,7 +14636,7 @@
         </is>
       </c>
       <c r="B1094" t="n">
-        <v>0.054075</v>
+        <v>0.054135</v>
       </c>
       <c r="C1094" t="n">
         <v>0.460465</v>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>0.054853</v>
+        <v>0.054844</v>
       </c>
       <c r="C1095" t="n">
         <v>0.45814</v>
@@ -14662,7 +14662,7 @@
         </is>
       </c>
       <c r="B1096" t="n">
-        <v>0.056376</v>
+        <v>0.056431</v>
       </c>
       <c r="C1096" t="n">
         <v>0.455814</v>
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="B1097" t="n">
-        <v>0.056627</v>
+        <v>0.05667</v>
       </c>
       <c r="C1097" t="n">
         <v>0.453488</v>
@@ -14688,7 +14688,7 @@
         </is>
       </c>
       <c r="B1098" t="n">
-        <v>0.057187</v>
+        <v>0.057091</v>
       </c>
       <c r="C1098" t="n">
         <v>0.451163</v>
@@ -14701,7 +14701,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>0.057275</v>
+        <v>0.057323</v>
       </c>
       <c r="C1099" t="n">
         <v>0.448837</v>
@@ -14714,7 +14714,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>0.05769</v>
+        <v>0.057661</v>
       </c>
       <c r="C1100" t="n">
         <v>0.446512</v>
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1101" t="n">
-        <v>0.057937</v>
+        <v>0.058003</v>
       </c>
       <c r="C1101" t="n">
         <v>0.444186</v>
@@ -14740,7 +14740,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>0.058254</v>
+        <v>0.058224</v>
       </c>
       <c r="C1102" t="n">
         <v>0.44186</v>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>0.058349</v>
+        <v>0.058328</v>
       </c>
       <c r="C1103" t="n">
         <v>0.439535</v>
@@ -14766,7 +14766,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>0.058633</v>
+        <v>0.058596</v>
       </c>
       <c r="C1104" t="n">
         <v>0.437209</v>
@@ -14779,7 +14779,7 @@
         </is>
       </c>
       <c r="B1105" t="n">
-        <v>0.059022</v>
+        <v>0.058895</v>
       </c>
       <c r="C1105" t="n">
         <v>0.434884</v>
@@ -14792,7 +14792,7 @@
         </is>
       </c>
       <c r="B1106" t="n">
-        <v>0.059707</v>
+        <v>0.059695</v>
       </c>
       <c r="C1106" t="n">
         <v>0.432558</v>
@@ -14805,7 +14805,7 @@
         </is>
       </c>
       <c r="B1107" t="n">
-        <v>0.059937</v>
+        <v>0.059895</v>
       </c>
       <c r="C1107" t="n">
         <v>0.430233</v>
@@ -14818,7 +14818,7 @@
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>0.060448</v>
+        <v>0.06047</v>
       </c>
       <c r="C1108" t="n">
         <v>0.427907</v>
@@ -14831,7 +14831,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>0.060543</v>
+        <v>0.060613</v>
       </c>
       <c r="C1109" t="n">
         <v>0.425581</v>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B1111" t="n">
-        <v>0.061043</v>
+        <v>0.061023</v>
       </c>
       <c r="C1111" t="n">
         <v>0.42093</v>
@@ -14870,7 +14870,7 @@
         </is>
       </c>
       <c r="B1112" t="n">
-        <v>0.061383</v>
+        <v>0.061348</v>
       </c>
       <c r="C1112" t="n">
         <v>0.418605</v>
@@ -14883,7 +14883,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>0.061393</v>
+        <v>0.06142</v>
       </c>
       <c r="C1113" t="n">
         <v>0.416279</v>
@@ -14896,7 +14896,7 @@
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>0.061415</v>
+        <v>0.061446</v>
       </c>
       <c r="C1114" t="n">
         <v>0.413953</v>
@@ -14909,7 +14909,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>0.061497</v>
+        <v>0.061549</v>
       </c>
       <c r="C1115" t="n">
         <v>0.411628</v>
@@ -14922,7 +14922,7 @@
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>0.061977</v>
+        <v>0.061969</v>
       </c>
       <c r="C1116" t="n">
         <v>0.409302</v>
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>0.06254899999999999</v>
+        <v>0.062607</v>
       </c>
       <c r="C1117" t="n">
         <v>0.406977</v>
@@ -14948,7 +14948,7 @@
         </is>
       </c>
       <c r="B1118" t="n">
-        <v>0.062832</v>
+        <v>0.06267499999999999</v>
       </c>
       <c r="C1118" t="n">
         <v>0.404651</v>
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="B1119" t="n">
-        <v>0.063594</v>
+        <v>0.06361700000000001</v>
       </c>
       <c r="C1119" t="n">
         <v>0.402326</v>
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="B1120" t="n">
-        <v>0.06378399999999999</v>
+        <v>0.063679</v>
       </c>
       <c r="C1120" t="n">
         <v>0.4</v>
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>0.06458899999999999</v>
+        <v>0.06457300000000001</v>
       </c>
       <c r="C1121" t="n">
         <v>0.397674</v>
@@ -15000,7 +15000,7 @@
         </is>
       </c>
       <c r="B1122" t="n">
-        <v>0.064705</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="C1122" t="n">
         <v>0.395349</v>
@@ -15013,7 +15013,7 @@
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>0.064752</v>
+        <v>0.064808</v>
       </c>
       <c r="C1123" t="n">
         <v>0.393023</v>
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>0.06483999999999999</v>
+        <v>0.06485200000000001</v>
       </c>
       <c r="C1124" t="n">
         <v>0.390698</v>
@@ -15039,7 +15039,7 @@
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>0.065245</v>
+        <v>0.065082</v>
       </c>
       <c r="C1125" t="n">
         <v>0.388372</v>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="B1126" t="n">
-        <v>0.065679</v>
+        <v>0.065757</v>
       </c>
       <c r="C1126" t="n">
         <v>0.386047</v>
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="B1127" t="n">
-        <v>0.06621</v>
+        <v>0.066228</v>
       </c>
       <c r="C1127" t="n">
         <v>0.383721</v>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="B1128" t="n">
-        <v>0.06646000000000001</v>
+        <v>0.06644600000000001</v>
       </c>
       <c r="C1128" t="n">
         <v>0.381395</v>
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="B1129" t="n">
-        <v>0.066607</v>
+        <v>0.066604</v>
       </c>
       <c r="C1129" t="n">
         <v>0.37907</v>
@@ -15104,7 +15104,7 @@
         </is>
       </c>
       <c r="B1130" t="n">
-        <v>0.066805</v>
+        <v>0.06676600000000001</v>
       </c>
       <c r="C1130" t="n">
         <v>0.376744</v>
@@ -15117,7 +15117,7 @@
         </is>
       </c>
       <c r="B1131" t="n">
-        <v>0.066867</v>
+        <v>0.066895</v>
       </c>
       <c r="C1131" t="n">
         <v>0.374419</v>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="B1132" t="n">
-        <v>0.06704599999999999</v>
+        <v>0.06703199999999999</v>
       </c>
       <c r="C1132" t="n">
         <v>0.372093</v>
@@ -15143,7 +15143,7 @@
         </is>
       </c>
       <c r="B1133" t="n">
-        <v>0.067721</v>
+        <v>0.067427</v>
       </c>
       <c r="C1133" t="n">
         <v>0.369767</v>
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="B1134" t="n">
-        <v>0.068076</v>
+        <v>0.068148</v>
       </c>
       <c r="C1134" t="n">
         <v>0.367442</v>
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="B1135" t="n">
-        <v>0.068118</v>
+        <v>0.068178</v>
       </c>
       <c r="C1135" t="n">
         <v>0.365116</v>
@@ -15182,7 +15182,7 @@
         </is>
       </c>
       <c r="B1136" t="n">
-        <v>0.068246</v>
+        <v>0.068312</v>
       </c>
       <c r="C1136" t="n">
         <v>0.362791</v>
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="B1137" t="n">
-        <v>0.06838900000000001</v>
+        <v>0.06843200000000001</v>
       </c>
       <c r="C1137" t="n">
         <v>0.360465</v>
@@ -15208,7 +15208,7 @@
         </is>
       </c>
       <c r="B1138" t="n">
-        <v>0.068513</v>
+        <v>0.068456</v>
       </c>
       <c r="C1138" t="n">
         <v>0.35814</v>
@@ -15221,7 +15221,7 @@
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>0.06858599999999999</v>
+        <v>0.068538</v>
       </c>
       <c r="C1139" t="n">
         <v>0.355814</v>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="B1140" t="n">
-        <v>0.068939</v>
+        <v>0.068927</v>
       </c>
       <c r="C1140" t="n">
         <v>0.353488</v>
@@ -15247,7 +15247,7 @@
         </is>
       </c>
       <c r="B1141" t="n">
-        <v>0.069396</v>
+        <v>0.069462</v>
       </c>
       <c r="C1141" t="n">
         <v>0.351163</v>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="B1142" t="n">
-        <v>0.069895</v>
+        <v>0.069867</v>
       </c>
       <c r="C1142" t="n">
         <v>0.348837</v>
@@ -15273,7 +15273,7 @@
         </is>
       </c>
       <c r="B1143" t="n">
-        <v>0.070284</v>
+        <v>0.070364</v>
       </c>
       <c r="C1143" t="n">
         <v>0.346512</v>
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="B1144" t="n">
-        <v>0.07062400000000001</v>
+        <v>0.070573</v>
       </c>
       <c r="C1144" t="n">
         <v>0.344186</v>
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>0.07063800000000001</v>
+        <v>0.07063999999999999</v>
       </c>
       <c r="C1145" t="n">
         <v>0.34186</v>
@@ -15312,7 +15312,7 @@
         </is>
       </c>
       <c r="B1146" t="n">
-        <v>0.070716</v>
+        <v>0.070785</v>
       </c>
       <c r="C1146" t="n">
         <v>0.339535</v>
@@ -15325,7 +15325,7 @@
         </is>
       </c>
       <c r="B1147" t="n">
-        <v>0.07135</v>
+        <v>0.071313</v>
       </c>
       <c r="C1147" t="n">
         <v>0.337209</v>
@@ -15338,7 +15338,7 @@
         </is>
       </c>
       <c r="B1148" t="n">
-        <v>0.071398</v>
+        <v>0.071394</v>
       </c>
       <c r="C1148" t="n">
         <v>0.334884</v>
@@ -15351,7 +15351,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>0.07162499999999999</v>
+        <v>0.07164</v>
       </c>
       <c r="C1149" t="n">
         <v>0.332558</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="B1150" t="n">
-        <v>0.07163</v>
+        <v>0.071658</v>
       </c>
       <c r="C1150" t="n">
         <v>0.330233</v>
@@ -15377,7 +15377,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>0.071657</v>
+        <v>0.07170600000000001</v>
       </c>
       <c r="C1151" t="n">
         <v>0.327907</v>
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>0.071769</v>
+        <v>0.071815</v>
       </c>
       <c r="C1152" t="n">
         <v>0.325581</v>
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="B1153" t="n">
-        <v>0.073934</v>
+        <v>0.07387100000000001</v>
       </c>
       <c r="C1153" t="n">
         <v>0.323256</v>
@@ -15416,7 +15416,7 @@
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>0.075345</v>
+        <v>0.07537099999999999</v>
       </c>
       <c r="C1154" t="n">
         <v>0.32093</v>
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>0.07546600000000001</v>
+        <v>0.075573</v>
       </c>
       <c r="C1155" t="n">
         <v>0.318605</v>
@@ -15442,7 +15442,7 @@
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>0.075722</v>
+        <v>0.075752</v>
       </c>
       <c r="C1156" t="n">
         <v>0.316279</v>
@@ -15455,7 +15455,7 @@
         </is>
       </c>
       <c r="B1157" t="n">
-        <v>0.07586900000000001</v>
+        <v>0.07578799999999999</v>
       </c>
       <c r="C1157" t="n">
         <v>0.313953</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>0.07642500000000001</v>
+        <v>0.076461</v>
       </c>
       <c r="C1158" t="n">
         <v>0.311628</v>
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="B1159" t="n">
-        <v>0.07675</v>
+        <v>0.07687099999999999</v>
       </c>
       <c r="C1159" t="n">
         <v>0.309302</v>
@@ -15494,7 +15494,7 @@
         </is>
       </c>
       <c r="B1160" t="n">
-        <v>0.077096</v>
+        <v>0.076929</v>
       </c>
       <c r="C1160" t="n">
         <v>0.306977</v>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="B1161" t="n">
-        <v>0.07813000000000001</v>
+        <v>0.078099</v>
       </c>
       <c r="C1161" t="n">
         <v>0.304651</v>
@@ -15520,7 +15520,7 @@
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>0.078259</v>
+        <v>0.07821699999999999</v>
       </c>
       <c r="C1162" t="n">
         <v>0.302326</v>
@@ -15533,7 +15533,7 @@
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>0.079052</v>
+        <v>0.078584</v>
       </c>
       <c r="C1163" t="n">
         <v>0.3</v>
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="B1164" t="n">
-        <v>0.079071</v>
+        <v>0.07896300000000001</v>
       </c>
       <c r="C1164" t="n">
         <v>0.297674</v>
@@ -15559,7 +15559,7 @@
         </is>
       </c>
       <c r="B1165" t="n">
-        <v>0.08006000000000001</v>
+        <v>0.079832</v>
       </c>
       <c r="C1165" t="n">
         <v>0.295349</v>
@@ -15572,7 +15572,7 @@
         </is>
       </c>
       <c r="B1166" t="n">
-        <v>0.080167</v>
+        <v>0.08010100000000001</v>
       </c>
       <c r="C1166" t="n">
         <v>0.293023</v>
@@ -15585,7 +15585,7 @@
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>0.080291</v>
+        <v>0.080236</v>
       </c>
       <c r="C1167" t="n">
         <v>0.290698</v>
@@ -15598,7 +15598,7 @@
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>0.080932</v>
+        <v>0.08092000000000001</v>
       </c>
       <c r="C1168" t="n">
         <v>0.288372</v>
@@ -15611,7 +15611,7 @@
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>0.080993</v>
+        <v>0.081078</v>
       </c>
       <c r="C1169" t="n">
         <v>0.286047</v>
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="B1170" t="n">
-        <v>0.081452</v>
+        <v>0.081326</v>
       </c>
       <c r="C1170" t="n">
         <v>0.283721</v>
@@ -15637,7 +15637,7 @@
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>0.08160299999999999</v>
+        <v>0.081646</v>
       </c>
       <c r="C1171" t="n">
         <v>0.281395</v>
@@ -15650,7 +15650,7 @@
         </is>
       </c>
       <c r="B1172" t="n">
-        <v>0.08237700000000001</v>
+        <v>0.082381</v>
       </c>
       <c r="C1172" t="n">
         <v>0.27907</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>0.082567</v>
+        <v>0.08251600000000001</v>
       </c>
       <c r="C1173" t="n">
         <v>0.276744</v>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="B1174" t="n">
-        <v>0.08272599999999999</v>
+        <v>0.082662</v>
       </c>
       <c r="C1174" t="n">
         <v>0.274419</v>
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="B1175" t="n">
-        <v>0.083299</v>
+        <v>0.083207</v>
       </c>
       <c r="C1175" t="n">
         <v>0.272093</v>
@@ -15702,7 +15702,7 @@
         </is>
       </c>
       <c r="B1176" t="n">
-        <v>0.08364000000000001</v>
+        <v>0.083438</v>
       </c>
       <c r="C1176" t="n">
         <v>0.269767</v>
@@ -15715,7 +15715,7 @@
         </is>
       </c>
       <c r="B1177" t="n">
-        <v>0.08430700000000001</v>
+        <v>0.08444400000000001</v>
       </c>
       <c r="C1177" t="n">
         <v>0.267442</v>
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="B1178" t="n">
-        <v>0.084885</v>
+        <v>0.08486399999999999</v>
       </c>
       <c r="C1178" t="n">
         <v>0.265116</v>
@@ -15741,7 +15741,7 @@
         </is>
       </c>
       <c r="B1179" t="n">
-        <v>0.084926</v>
+        <v>0.08498699999999999</v>
       </c>
       <c r="C1179" t="n">
         <v>0.262791</v>
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>0.085187</v>
+        <v>0.08502800000000001</v>
       </c>
       <c r="C1180" t="n">
         <v>0.260465</v>
@@ -15767,7 +15767,7 @@
         </is>
       </c>
       <c r="B1181" t="n">
-        <v>0.086253</v>
+        <v>0.086109</v>
       </c>
       <c r="C1181" t="n">
         <v>0.25814</v>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="B1182" t="n">
-        <v>0.08630400000000001</v>
+        <v>0.086245</v>
       </c>
       <c r="C1182" t="n">
         <v>0.255814</v>
@@ -15793,7 +15793,7 @@
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>0.087284</v>
+        <v>0.087336</v>
       </c>
       <c r="C1183" t="n">
         <v>0.253488</v>
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>0.087615</v>
+        <v>0.087461</v>
       </c>
       <c r="C1184" t="n">
         <v>0.251163</v>
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="B1185" t="n">
-        <v>0.088129</v>
+        <v>0.08815199999999999</v>
       </c>
       <c r="C1185" t="n">
         <v>0.248837</v>
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="B1186" t="n">
-        <v>0.088542</v>
+        <v>0.088535</v>
       </c>
       <c r="C1186" t="n">
         <v>0.246512</v>
@@ -15845,7 +15845,7 @@
         </is>
       </c>
       <c r="B1187" t="n">
-        <v>0.088571</v>
+        <v>0.088694</v>
       </c>
       <c r="C1187" t="n">
         <v>0.244186</v>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="B1188" t="n">
-        <v>0.08958000000000001</v>
+        <v>0.089681</v>
       </c>
       <c r="C1188" t="n">
         <v>0.24186</v>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="B1189" t="n">
-        <v>0.090041</v>
+        <v>0.090007</v>
       </c>
       <c r="C1189" t="n">
         <v>0.239535</v>
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="B1190" t="n">
-        <v>0.090333</v>
+        <v>0.090391</v>
       </c>
       <c r="C1190" t="n">
         <v>0.237209</v>
@@ -15897,7 +15897,7 @@
         </is>
       </c>
       <c r="B1191" t="n">
-        <v>0.091407</v>
+        <v>0.09148100000000001</v>
       </c>
       <c r="C1191" t="n">
         <v>0.234884</v>
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="B1192" t="n">
-        <v>0.092527</v>
+        <v>0.092658</v>
       </c>
       <c r="C1192" t="n">
         <v>0.232558</v>
@@ -15923,7 +15923,7 @@
         </is>
       </c>
       <c r="B1193" t="n">
-        <v>0.092941</v>
+        <v>0.092974</v>
       </c>
       <c r="C1193" t="n">
         <v>0.230233</v>
@@ -15936,7 +15936,7 @@
         </is>
       </c>
       <c r="B1194" t="n">
-        <v>0.09385</v>
+        <v>0.093735</v>
       </c>
       <c r="C1194" t="n">
         <v>0.227907</v>
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>0.094317</v>
+        <v>0.094372</v>
       </c>
       <c r="C1195" t="n">
         <v>0.225581</v>
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="B1196" t="n">
-        <v>0.094474</v>
+        <v>0.094568</v>
       </c>
       <c r="C1196" t="n">
         <v>0.223256</v>
@@ -15975,7 +15975,7 @@
         </is>
       </c>
       <c r="B1197" t="n">
-        <v>0.094517</v>
+        <v>0.094651</v>
       </c>
       <c r="C1197" t="n">
         <v>0.22093</v>
@@ -15988,7 +15988,7 @@
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>0.095793</v>
+        <v>0.095842</v>
       </c>
       <c r="C1198" t="n">
         <v>0.218605</v>
@@ -16001,7 +16001,7 @@
         </is>
       </c>
       <c r="B1199" t="n">
-        <v>0.09664399999999999</v>
+        <v>0.096651</v>
       </c>
       <c r="C1199" t="n">
         <v>0.216279</v>
@@ -16014,7 +16014,7 @@
         </is>
       </c>
       <c r="B1200" t="n">
-        <v>0.096821</v>
+        <v>0.09692000000000001</v>
       </c>
       <c r="C1200" t="n">
         <v>0.213953</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="B1201" t="n">
-        <v>0.09710199999999999</v>
+        <v>0.09712</v>
       </c>
       <c r="C1201" t="n">
         <v>0.211628</v>
@@ -16040,7 +16040,7 @@
         </is>
       </c>
       <c r="B1202" t="n">
-        <v>0.100715</v>
+        <v>0.10072</v>
       </c>
       <c r="C1202" t="n">
         <v>0.209302</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>0.101393</v>
+        <v>0.101422</v>
       </c>
       <c r="C1203" t="n">
         <v>0.206977</v>
@@ -16066,7 +16066,7 @@
         </is>
       </c>
       <c r="B1204" t="n">
-        <v>0.10261</v>
+        <v>0.102665</v>
       </c>
       <c r="C1204" t="n">
         <v>0.204651</v>
@@ -16079,7 +16079,7 @@
         </is>
       </c>
       <c r="B1205" t="n">
-        <v>0.102956</v>
+        <v>0.103071</v>
       </c>
       <c r="C1205" t="n">
         <v>0.202326</v>
@@ -16092,7 +16092,7 @@
         </is>
       </c>
       <c r="B1206" t="n">
-        <v>0.106812</v>
+        <v>0.106918</v>
       </c>
       <c r="C1206" t="n">
         <v>0.2</v>
@@ -16105,7 +16105,7 @@
         </is>
       </c>
       <c r="B1207" t="n">
-        <v>0.107278</v>
+        <v>0.107247</v>
       </c>
       <c r="C1207" t="n">
         <v>0.197674</v>
@@ -16118,7 +16118,7 @@
         </is>
       </c>
       <c r="B1208" t="n">
-        <v>0.107889</v>
+        <v>0.107843</v>
       </c>
       <c r="C1208" t="n">
         <v>0.195349</v>
@@ -16131,7 +16131,7 @@
         </is>
       </c>
       <c r="B1209" t="n">
-        <v>0.109915</v>
+        <v>0.110024</v>
       </c>
       <c r="C1209" t="n">
         <v>0.193023</v>
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="B1210" t="n">
-        <v>0.111153</v>
+        <v>0.111142</v>
       </c>
       <c r="C1210" t="n">
         <v>0.190698</v>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="B1211" t="n">
-        <v>0.111254</v>
+        <v>0.111205</v>
       </c>
       <c r="C1211" t="n">
         <v>0.188372</v>
@@ -16170,7 +16170,7 @@
         </is>
       </c>
       <c r="B1212" t="n">
-        <v>0.11346</v>
+        <v>0.113364</v>
       </c>
       <c r="C1212" t="n">
         <v>0.186047</v>
@@ -16183,7 +16183,7 @@
         </is>
       </c>
       <c r="B1213" t="n">
-        <v>0.113492</v>
+        <v>0.113561</v>
       </c>
       <c r="C1213" t="n">
         <v>0.183721</v>
@@ -16196,7 +16196,7 @@
         </is>
       </c>
       <c r="B1214" t="n">
-        <v>0.114915</v>
+        <v>0.114914</v>
       </c>
       <c r="C1214" t="n">
         <v>0.181395</v>
@@ -16209,7 +16209,7 @@
         </is>
       </c>
       <c r="B1215" t="n">
-        <v>0.116033</v>
+        <v>0.116063</v>
       </c>
       <c r="C1215" t="n">
         <v>0.17907</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="B1216" t="n">
-        <v>0.118052</v>
+        <v>0.118008</v>
       </c>
       <c r="C1216" t="n">
         <v>0.176744</v>
@@ -16235,7 +16235,7 @@
         </is>
       </c>
       <c r="B1217" t="n">
-        <v>0.118093</v>
+        <v>0.118021</v>
       </c>
       <c r="C1217" t="n">
         <v>0.174419</v>
@@ -16248,7 +16248,7 @@
         </is>
       </c>
       <c r="B1218" t="n">
-        <v>0.118199</v>
+        <v>0.118223</v>
       </c>
       <c r="C1218" t="n">
         <v>0.172093</v>
@@ -16261,7 +16261,7 @@
         </is>
       </c>
       <c r="B1219" t="n">
-        <v>0.1192</v>
+        <v>0.11896</v>
       </c>
       <c r="C1219" t="n">
         <v>0.169767</v>
@@ -16274,7 +16274,7 @@
         </is>
       </c>
       <c r="B1220" t="n">
-        <v>0.119749</v>
+        <v>0.119786</v>
       </c>
       <c r="C1220" t="n">
         <v>0.167442</v>
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="B1221" t="n">
-        <v>0.120593</v>
+        <v>0.12057</v>
       </c>
       <c r="C1221" t="n">
         <v>0.165116</v>
@@ -16300,7 +16300,7 @@
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>0.120781</v>
+        <v>0.120618</v>
       </c>
       <c r="C1222" t="n">
         <v>0.162791</v>
@@ -16313,7 +16313,7 @@
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>0.121555</v>
+        <v>0.121329</v>
       </c>
       <c r="C1223" t="n">
         <v>0.160465</v>
@@ -16326,7 +16326,7 @@
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>0.122014</v>
+        <v>0.122045</v>
       </c>
       <c r="C1224" t="n">
         <v>0.15814</v>
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="B1225" t="n">
-        <v>0.122337</v>
+        <v>0.122419</v>
       </c>
       <c r="C1225" t="n">
         <v>0.155814</v>
@@ -16352,7 +16352,7 @@
         </is>
       </c>
       <c r="B1226" t="n">
-        <v>0.122883</v>
+        <v>0.122861</v>
       </c>
       <c r="C1226" t="n">
         <v>0.153488</v>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="B1227" t="n">
-        <v>0.124119</v>
+        <v>0.12385</v>
       </c>
       <c r="C1227" t="n">
         <v>0.151163</v>
@@ -16378,7 +16378,7 @@
         </is>
       </c>
       <c r="B1228" t="n">
-        <v>0.126755</v>
+        <v>0.126702</v>
       </c>
       <c r="C1228" t="n">
         <v>0.148837</v>
@@ -16391,7 +16391,7 @@
         </is>
       </c>
       <c r="B1229" t="n">
-        <v>0.126827</v>
+        <v>0.126819</v>
       </c>
       <c r="C1229" t="n">
         <v>0.146512</v>
@@ -16404,7 +16404,7 @@
         </is>
       </c>
       <c r="B1230" t="n">
-        <v>0.128145</v>
+        <v>0.128165</v>
       </c>
       <c r="C1230" t="n">
         <v>0.144186</v>
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="B1231" t="n">
-        <v>0.128165</v>
+        <v>0.12817</v>
       </c>
       <c r="C1231" t="n">
         <v>0.14186</v>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="B1232" t="n">
-        <v>0.128227</v>
+        <v>0.128324</v>
       </c>
       <c r="C1232" t="n">
         <v>0.139535</v>
@@ -16443,7 +16443,7 @@
         </is>
       </c>
       <c r="B1233" t="n">
-        <v>0.128639</v>
+        <v>0.128737</v>
       </c>
       <c r="C1233" t="n">
         <v>0.137209</v>
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="B1234" t="n">
-        <v>0.129739</v>
+        <v>0.129923</v>
       </c>
       <c r="C1234" t="n">
         <v>0.134884</v>
@@ -16469,7 +16469,7 @@
         </is>
       </c>
       <c r="B1235" t="n">
-        <v>0.131321</v>
+        <v>0.131596</v>
       </c>
       <c r="C1235" t="n">
         <v>0.132558</v>
@@ -16482,7 +16482,7 @@
         </is>
       </c>
       <c r="B1236" t="n">
-        <v>0.131931</v>
+        <v>0.131873</v>
       </c>
       <c r="C1236" t="n">
         <v>0.130233</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="B1237" t="n">
-        <v>0.135192</v>
+        <v>0.135332</v>
       </c>
       <c r="C1237" t="n">
         <v>0.127907</v>
@@ -16508,7 +16508,7 @@
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>0.138192</v>
+        <v>0.137969</v>
       </c>
       <c r="C1238" t="n">
         <v>0.125581</v>
@@ -16521,7 +16521,7 @@
         </is>
       </c>
       <c r="B1239" t="n">
-        <v>0.139189</v>
+        <v>0.139335</v>
       </c>
       <c r="C1239" t="n">
         <v>0.123256</v>
@@ -16534,7 +16534,7 @@
         </is>
       </c>
       <c r="B1240" t="n">
-        <v>0.139952</v>
+        <v>0.139728</v>
       </c>
       <c r="C1240" t="n">
         <v>0.12093</v>
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>0.145551</v>
+        <v>0.145552</v>
       </c>
       <c r="C1241" t="n">
         <v>0.118605</v>
@@ -16560,7 +16560,7 @@
         </is>
       </c>
       <c r="B1242" t="n">
-        <v>0.147019</v>
+        <v>0.14705</v>
       </c>
       <c r="C1242" t="n">
         <v>0.116279</v>
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="B1243" t="n">
-        <v>0.148035</v>
+        <v>0.147759</v>
       </c>
       <c r="C1243" t="n">
         <v>0.113953</v>
@@ -16586,7 +16586,7 @@
         </is>
       </c>
       <c r="B1244" t="n">
-        <v>0.148391</v>
+        <v>0.147932</v>
       </c>
       <c r="C1244" t="n">
         <v>0.111628</v>
@@ -16599,7 +16599,7 @@
         </is>
       </c>
       <c r="B1245" t="n">
-        <v>0.150252</v>
+        <v>0.150244</v>
       </c>
       <c r="C1245" t="n">
         <v>0.109302</v>
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>0.152017</v>
+        <v>0.151884</v>
       </c>
       <c r="C1246" t="n">
         <v>0.106977</v>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="B1247" t="n">
-        <v>0.155679</v>
+        <v>0.155762</v>
       </c>
       <c r="C1247" t="n">
         <v>0.104651</v>
@@ -16638,7 +16638,7 @@
         </is>
       </c>
       <c r="B1248" t="n">
-        <v>0.155886</v>
+        <v>0.155928</v>
       </c>
       <c r="C1248" t="n">
         <v>0.102326</v>
@@ -16651,7 +16651,7 @@
         </is>
       </c>
       <c r="B1249" t="n">
-        <v>0.158519</v>
+        <v>0.158134</v>
       </c>
       <c r="C1249" t="n">
         <v>0.1</v>
@@ -16664,7 +16664,7 @@
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>0.160276</v>
+        <v>0.160184</v>
       </c>
       <c r="C1250" t="n">
         <v>0.097674</v>
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="B1251" t="n">
-        <v>0.161992</v>
+        <v>0.162267</v>
       </c>
       <c r="C1251" t="n">
         <v>0.095349</v>
@@ -16690,7 +16690,7 @@
         </is>
       </c>
       <c r="B1252" t="n">
-        <v>0.162376</v>
+        <v>0.162311</v>
       </c>
       <c r="C1252" t="n">
         <v>0.09302299999999999</v>
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="B1253" t="n">
-        <v>0.165092</v>
+        <v>0.164649</v>
       </c>
       <c r="C1253" t="n">
         <v>0.090698</v>
@@ -16716,7 +16716,7 @@
         </is>
       </c>
       <c r="B1254" t="n">
-        <v>0.165092</v>
+        <v>0.164649</v>
       </c>
       <c r="C1254" t="n">
         <v>0.08837200000000001</v>
@@ -16729,7 +16729,7 @@
         </is>
       </c>
       <c r="B1255" t="n">
-        <v>0.165092</v>
+        <v>0.164649</v>
       </c>
       <c r="C1255" t="n">
         <v>0.086047</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="B1256" t="n">
-        <v>0.165358</v>
+        <v>0.165526</v>
       </c>
       <c r="C1256" t="n">
         <v>0.083721</v>
@@ -16755,7 +16755,7 @@
         </is>
       </c>
       <c r="B1257" t="n">
-        <v>0.171346</v>
+        <v>0.171259</v>
       </c>
       <c r="C1257" t="n">
         <v>0.081395</v>
@@ -16768,7 +16768,7 @@
         </is>
       </c>
       <c r="B1258" t="n">
-        <v>0.174244</v>
+        <v>0.174027</v>
       </c>
       <c r="C1258" t="n">
         <v>0.07907</v>
@@ -16781,7 +16781,7 @@
         </is>
       </c>
       <c r="B1259" t="n">
-        <v>0.17581</v>
+        <v>0.175688</v>
       </c>
       <c r="C1259" t="n">
         <v>0.07674400000000001</v>
@@ -16794,7 +16794,7 @@
         </is>
       </c>
       <c r="B1260" t="n">
-        <v>0.175894</v>
+        <v>0.175962</v>
       </c>
       <c r="C1260" t="n">
         <v>0.074419</v>
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>0.181561</v>
+        <v>0.181526</v>
       </c>
       <c r="C1261" t="n">
         <v>0.072093</v>
@@ -16820,7 +16820,7 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>0.18539</v>
+        <v>0.185494</v>
       </c>
       <c r="C1262" t="n">
         <v>0.069767</v>
@@ -16833,7 +16833,7 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>0.186765</v>
+        <v>0.186951</v>
       </c>
       <c r="C1263" t="n">
         <v>0.067442</v>
@@ -16846,7 +16846,7 @@
         </is>
       </c>
       <c r="B1264" t="n">
-        <v>0.188423</v>
+        <v>0.18861</v>
       </c>
       <c r="C1264" t="n">
         <v>0.06511599999999999</v>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="B1265" t="n">
-        <v>0.201627</v>
+        <v>0.201732</v>
       </c>
       <c r="C1265" t="n">
         <v>0.062791</v>
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>0.202206</v>
+        <v>0.202331</v>
       </c>
       <c r="C1266" t="n">
         <v>0.060465</v>
@@ -16885,7 +16885,7 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>0.2098</v>
+        <v>0.209694</v>
       </c>
       <c r="C1267" t="n">
         <v>0.05814</v>
@@ -16898,7 +16898,7 @@
         </is>
       </c>
       <c r="B1268" t="n">
-        <v>0.211072</v>
+        <v>0.210971</v>
       </c>
       <c r="C1268" t="n">
         <v>0.055814</v>
@@ -16911,7 +16911,7 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>0.211387</v>
+        <v>0.211605</v>
       </c>
       <c r="C1269" t="n">
         <v>0.053488</v>
@@ -16924,7 +16924,7 @@
         </is>
       </c>
       <c r="B1270" t="n">
-        <v>0.212991</v>
+        <v>0.212594</v>
       </c>
       <c r="C1270" t="n">
         <v>0.051163</v>
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="B1271" t="n">
-        <v>0.213062</v>
+        <v>0.213012</v>
       </c>
       <c r="C1271" t="n">
         <v>0.048837</v>
@@ -16950,7 +16950,7 @@
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>0.217167</v>
+        <v>0.216378</v>
       </c>
       <c r="C1272" t="n">
         <v>0.046512</v>
@@ -16963,7 +16963,7 @@
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>0.242948</v>
+        <v>0.243198</v>
       </c>
       <c r="C1273" t="n">
         <v>0.044186</v>
@@ -16976,7 +16976,7 @@
         </is>
       </c>
       <c r="B1274" t="n">
-        <v>0.251714</v>
+        <v>0.251848</v>
       </c>
       <c r="C1274" t="n">
         <v>0.04186</v>
@@ -16989,7 +16989,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>0.259913</v>
+        <v>0.259946</v>
       </c>
       <c r="C1275" t="n">
         <v>0.039535</v>
@@ -17002,7 +17002,7 @@
         </is>
       </c>
       <c r="B1276" t="n">
-        <v>0.267092</v>
+        <v>0.266561</v>
       </c>
       <c r="C1276" t="n">
         <v>0.037209</v>
@@ -17015,7 +17015,7 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>0.295254</v>
+        <v>0.2952</v>
       </c>
       <c r="C1277" t="n">
         <v>0.034884</v>
@@ -17028,7 +17028,7 @@
         </is>
       </c>
       <c r="B1278" t="n">
-        <v>0.296146</v>
+        <v>0.296484</v>
       </c>
       <c r="C1278" t="n">
         <v>0.032558</v>
@@ -17041,7 +17041,7 @@
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>0.298085</v>
+        <v>0.297889</v>
       </c>
       <c r="C1279" t="n">
         <v>0.030233</v>
@@ -17054,7 +17054,7 @@
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>0.330482</v>
+        <v>0.330004</v>
       </c>
       <c r="C1280" t="n">
         <v>0.027907</v>
@@ -17067,7 +17067,7 @@
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>0.341267</v>
+        <v>0.341648</v>
       </c>
       <c r="C1281" t="n">
         <v>0.025581</v>
@@ -17080,7 +17080,7 @@
         </is>
       </c>
       <c r="B1282" t="n">
-        <v>0.345762</v>
+        <v>0.346154</v>
       </c>
       <c r="C1282" t="n">
         <v>0.023256</v>
@@ -17093,7 +17093,7 @@
         </is>
       </c>
       <c r="B1283" t="n">
-        <v>0.359376</v>
+        <v>0.358762</v>
       </c>
       <c r="C1283" t="n">
         <v>0.02093</v>
@@ -17106,7 +17106,7 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>0.369058</v>
+        <v>0.368777</v>
       </c>
       <c r="C1284" t="n">
         <v>0.018605</v>
@@ -17119,7 +17119,7 @@
         </is>
       </c>
       <c r="B1285" t="n">
-        <v>0.380207</v>
+        <v>0.380415</v>
       </c>
       <c r="C1285" t="n">
         <v>0.016279</v>
@@ -17132,7 +17132,7 @@
         </is>
       </c>
       <c r="B1286" t="n">
-        <v>0.514106</v>
+        <v>0.513174</v>
       </c>
       <c r="C1286" t="n">
         <v>0.013953</v>
@@ -17145,7 +17145,7 @@
         </is>
       </c>
       <c r="B1287" t="n">
-        <v>0.523933</v>
+        <v>0.523991</v>
       </c>
       <c r="C1287" t="n">
         <v>0.011628</v>
@@ -17158,7 +17158,7 @@
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>0.649128</v>
+        <v>0.649783</v>
       </c>
       <c r="C1288" t="n">
         <v>0.009302</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>0.667596</v>
+        <v>0.667816</v>
       </c>
       <c r="C1289" t="n">
         <v>0.006977</v>
@@ -17184,7 +17184,7 @@
         </is>
       </c>
       <c r="B1290" t="n">
-        <v>0.995848</v>
+        <v>0.996833</v>
       </c>
       <c r="C1290" t="n">
         <v>0.004651</v>
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>1.278464</v>
+        <v>1.280967</v>
       </c>
       <c r="C1291" t="n">
         <v>0.002326</v>
